--- a/assets/nuclear_physics_calculator.xlsx
+++ b/assets/nuclear_physics_calculator.xlsx
@@ -10,6 +10,7 @@
     <sheet state="visible" name="q_value_calculator" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="stellar_temperature_calculator" sheetId="6" r:id="rId10"/>
     <sheet state="visible" name="gamow_window_calculator" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="resonance_calculator" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="164">
   <si>
     <t>Lab inputs</t>
   </si>
@@ -319,12 +320,15 @@
     <t>0.122(Z1^2*Z2^2*mu)^(1/3)</t>
   </si>
   <si>
+    <t>Beam energy (keV/U)</t>
+  </si>
+  <si>
+    <t>Stellar temperature (GK)</t>
+  </si>
+  <si>
     <t>Beam energy (MeV/U)</t>
   </si>
   <si>
-    <t>Stellar temperature (GK)</t>
-  </si>
-  <si>
     <t>T9</t>
   </si>
   <si>
@@ -346,39 +350,39 @@
     <t>k</t>
   </si>
   <si>
+    <t>Energies</t>
+  </si>
+  <si>
     <t>Step size</t>
   </si>
   <si>
-    <t>Energies</t>
+    <t>MeV</t>
+  </si>
+  <si>
+    <t>keV</t>
+  </si>
+  <si>
+    <t>Maxwell-Boltzmann</t>
+  </si>
+  <si>
+    <t>Maxwell-Boltzmann Normalised</t>
+  </si>
+  <si>
+    <t>Tunneling</t>
+  </si>
+  <si>
+    <t>Tunneling Normalised</t>
+  </si>
+  <si>
+    <t>Gamow</t>
+  </si>
+  <si>
+    <t>Gamow Normalised</t>
   </si>
   <si>
     <t>f(e)=E^(1/2)e^(-E/kT)</t>
   </si>
   <si>
-    <t>MeV</t>
-  </si>
-  <si>
-    <t>keV</t>
-  </si>
-  <si>
-    <t>Maxwell-Boltzmann</t>
-  </si>
-  <si>
-    <t>Maxwell-Boltzmann Normalised</t>
-  </si>
-  <si>
-    <t>Tunneling</t>
-  </si>
-  <si>
-    <t>Tunneling Normalised</t>
-  </si>
-  <si>
-    <t>Gamow</t>
-  </si>
-  <si>
-    <t>Gamow Normalised</t>
-  </si>
-  <si>
     <t>P(E)=e^(-2*pi*nu)</t>
   </si>
   <si>
@@ -412,14 +416,110 @@
     <t>Ehigh (MeV)</t>
   </si>
   <si>
+    <t>Ecm (keV)</t>
+  </si>
+  <si>
+    <t>Elow (keV)</t>
+  </si>
+  <si>
+    <t>Ehigh (keV)</t>
+  </si>
+  <si>
     <t>dE = 0.237(Z1^2*Z2^2mu)^(1/6)*T9^(5/6)</t>
+  </si>
+  <si>
+    <t>Calculation results</t>
+  </si>
+  <si>
+    <t>Resonance J</t>
+  </si>
+  <si>
+    <t>Projectile parameters</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Target n</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>j = l + s</t>
+  </si>
+  <si>
+    <t>Proton</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Projectile n</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>J = I + j</t>
+  </si>
+  <si>
+    <t>Neutron</t>
+  </si>
+  <si>
+    <t>Projectile j1</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>Target I</t>
+  </si>
+  <si>
+    <t>Projectile j2</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Deuteron</t>
+  </si>
+  <si>
+    <t>Projectile</t>
+  </si>
+  <si>
+    <t>Target parity</t>
+  </si>
+  <si>
+    <t>Triton</t>
+  </si>
+  <si>
+    <t>Projectile mass</t>
+  </si>
+  <si>
+    <t>3He</t>
+  </si>
+  <si>
+    <t>Projectile Z</t>
+  </si>
+  <si>
+    <t>Intrinsic spin, s</t>
+  </si>
+  <si>
+    <t>Angular momentum relative to target, l</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="?/?"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -437,8 +537,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +573,12 @@
         <bgColor rgb="FFA4C2F4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -476,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -486,7 +596,7 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -508,6 +618,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -542,7 +655,25 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -612,11 +743,11 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="2063780558"/>
-        <c:axId val="332423064"/>
+        <c:axId val="1433655725"/>
+        <c:axId val="319703094"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2063780558"/>
+        <c:axId val="1433655725"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -672,10 +803,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="332423064"/>
+        <c:crossAx val="319703094"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="332423064"/>
+        <c:axId val="319703094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -752,7 +883,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2063780558"/>
+        <c:crossAx val="1433655725"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -789,7 +920,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>gamow_window_calculator!$I$5</c:f>
+              <c:f>gamow_window_calculator!$I$4</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -804,12 +935,12 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>gamow_window_calculator!$F$6:$F$15</c:f>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>gamow_window_calculator!$I$6:$I$15</c:f>
+              <c:f>gamow_window_calculator!$I$5:$I$14</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -820,7 +951,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>gamow_window_calculator!$K$5</c:f>
+              <c:f>gamow_window_calculator!$K$4</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -835,12 +966,12 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>gamow_window_calculator!$F$6:$F$15</c:f>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>gamow_window_calculator!$K$6:$K$15</c:f>
+              <c:f>gamow_window_calculator!$K$5:$K$14</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
@@ -851,7 +982,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>gamow_window_calculator!$M$5</c:f>
+              <c:f>gamow_window_calculator!$M$4</c:f>
             </c:strRef>
           </c:tx>
           <c:spPr>
@@ -866,22 +997,22 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>gamow_window_calculator!$F$6:$F$15</c:f>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>gamow_window_calculator!$M$6:$M$15</c:f>
+              <c:f>gamow_window_calculator!$M$5:$M$14</c:f>
               <c:numCache/>
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="1891802482"/>
-        <c:axId val="1498213234"/>
+        <c:axId val="424541484"/>
+        <c:axId val="904885870"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1891802482"/>
+        <c:axId val="424541484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -937,10 +1068,10 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1498213234"/>
+        <c:crossAx val="904885870"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1498213234"/>
+        <c:axId val="904885870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1017,7 +1148,272 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1891802482"/>
+        <c:crossAx val="424541484"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0">
+            <a:defRPr b="0">
+              <a:solidFill>
+                <a:srgbClr val="1A1A1A"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$H$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="4285F4"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>gamow_window_calculator!$H$5:$H$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$J$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="EA4335"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>gamow_window_calculator!$J$5:$J$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$L$4</c:f>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln cmpd="sng">
+              <a:solidFill>
+                <a:srgbClr val="FBBC04"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>gamow_window_calculator!$F$5:$F$14</c:f>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>gamow_window_calculator!$L$5:$L$14</c:f>
+              <c:numCache/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:axId val="817752864"/>
+        <c:axId val="495809322"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="817752864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="495809322"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="495809322"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="B7B7B7"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC">
+                  <a:alpha val="0"/>
+                </a:srgbClr>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr lvl="0">
+                  <a:defRPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                  </a:rPr>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr lvl="0">
+              <a:defRPr b="0">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="817752864"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1097,10 +1493,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>742950</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5715000" cy="3533775"/>
     <xdr:graphicFrame>
@@ -1120,7 +1516,36 @@
     </xdr:graphicFrame>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5715000" cy="3533775"/>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 3" title="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1369,7 +1794,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>12.78</v>
+        <v>8.82</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -1388,7 +1813,7 @@
       </c>
       <c r="B6" s="5">
         <f>B4*(B3/(B2+B3))</f>
-        <v>0.6726315789</v>
+        <v>0.4642105263</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -1674,13 +2099,13 @@
       <c r="F2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="11">
         <v>1000.0</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="11">
         <v>0.1861702128</v>
       </c>
     </row>
@@ -1717,19 +2142,19 @@
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>1.75E-5</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="11">
         <v>2.64</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="11">
         <v>0.94</v>
       </c>
     </row>
@@ -1835,14 +2260,14 @@
       <c r="B2" s="6">
         <v>9.0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>56</v>
       </c>
       <c r="D2" s="5">
         <f>1.602176634*10^-19</f>
         <v>0</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>57</v>
       </c>
       <c r="F2" s="5">
@@ -1856,7 +2281,7 @@
         <f>B6*(PI()/180)</f>
         <v>0.0221656815</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>59</v>
       </c>
       <c r="J2" s="5">
@@ -1871,7 +2296,7 @@
       <c r="B3" s="6">
         <v>6.0</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="5">
@@ -1892,7 +2317,7 @@
         <f>SIN(H2/2)</f>
         <v>0.01108261387</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>64</v>
       </c>
       <c r="J3" s="5">
@@ -1907,7 +2332,7 @@
       <c r="B4" s="6">
         <v>12.78</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="9">
@@ -1928,7 +2353,7 @@
         <f>H3^4</f>
         <v>0.00000001508581608</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12" t="s">
         <v>68</v>
       </c>
       <c r="J4" s="5">
@@ -1944,7 +2369,7 @@
         <f>B4*D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>70</v>
       </c>
       <c r="D5" s="5">
@@ -1967,13 +2392,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>73</v>
       </c>
       <c r="B6" s="6">
         <v>1.27</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>74</v>
       </c>
       <c r="D6" s="9">
@@ -1994,7 +2419,7 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="H7" s="12"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8">
       <c r="A8" s="10"/>
@@ -2052,15 +2477,15 @@
         <f t="shared" ref="E10:E190" si="4">1/D10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F10" s="12" t="str">
+      <c r="F10" s="13" t="str">
         <f t="shared" ref="F10:F190" si="5">$F$6*E10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G10" s="12" t="str">
+      <c r="G10" s="13" t="str">
         <f t="shared" ref="G10:G190" si="6">F10/$D$6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H10" s="12" t="str">
+      <c r="H10" s="13" t="str">
         <f t="shared" ref="H10:H190" si="7">G10*1000</f>
         <v>#DIV/0!</v>
       </c>
@@ -8006,4069 +8431,4069 @@
       </c>
     </row>
     <row r="191">
-      <c r="F191" s="12"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="12"/>
+      <c r="F191" s="13"/>
+      <c r="G191" s="13"/>
+      <c r="H191" s="13"/>
     </row>
     <row r="192">
-      <c r="F192" s="12"/>
-      <c r="G192" s="12"/>
-      <c r="H192" s="12"/>
+      <c r="F192" s="13"/>
+      <c r="G192" s="13"/>
+      <c r="H192" s="13"/>
     </row>
     <row r="193">
-      <c r="F193" s="12"/>
-      <c r="G193" s="12"/>
-      <c r="H193" s="12"/>
+      <c r="F193" s="13"/>
+      <c r="G193" s="13"/>
+      <c r="H193" s="13"/>
     </row>
     <row r="194">
-      <c r="F194" s="12"/>
-      <c r="G194" s="12"/>
-      <c r="H194" s="12"/>
+      <c r="F194" s="13"/>
+      <c r="G194" s="13"/>
+      <c r="H194" s="13"/>
     </row>
     <row r="195">
-      <c r="F195" s="12"/>
-      <c r="G195" s="12"/>
-      <c r="H195" s="12"/>
+      <c r="F195" s="13"/>
+      <c r="G195" s="13"/>
+      <c r="H195" s="13"/>
     </row>
     <row r="196">
-      <c r="F196" s="12"/>
-      <c r="G196" s="12"/>
-      <c r="H196" s="12"/>
+      <c r="F196" s="13"/>
+      <c r="G196" s="13"/>
+      <c r="H196" s="13"/>
     </row>
     <row r="197">
-      <c r="F197" s="12"/>
-      <c r="G197" s="12"/>
-      <c r="H197" s="12"/>
+      <c r="F197" s="13"/>
+      <c r="G197" s="13"/>
+      <c r="H197" s="13"/>
     </row>
     <row r="198">
-      <c r="F198" s="12"/>
-      <c r="G198" s="12"/>
-      <c r="H198" s="12"/>
+      <c r="F198" s="13"/>
+      <c r="G198" s="13"/>
+      <c r="H198" s="13"/>
     </row>
     <row r="199">
-      <c r="F199" s="12"/>
-      <c r="G199" s="12"/>
-      <c r="H199" s="12"/>
+      <c r="F199" s="13"/>
+      <c r="G199" s="13"/>
+      <c r="H199" s="13"/>
     </row>
     <row r="200">
-      <c r="F200" s="12"/>
-      <c r="G200" s="12"/>
-      <c r="H200" s="12"/>
+      <c r="F200" s="13"/>
+      <c r="G200" s="13"/>
+      <c r="H200" s="13"/>
     </row>
     <row r="201">
-      <c r="F201" s="12"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="12"/>
+      <c r="F201" s="13"/>
+      <c r="G201" s="13"/>
+      <c r="H201" s="13"/>
     </row>
     <row r="202">
-      <c r="F202" s="12"/>
-      <c r="G202" s="12"/>
-      <c r="H202" s="12"/>
+      <c r="F202" s="13"/>
+      <c r="G202" s="13"/>
+      <c r="H202" s="13"/>
     </row>
     <row r="203">
-      <c r="F203" s="12"/>
-      <c r="G203" s="12"/>
-      <c r="H203" s="12"/>
+      <c r="F203" s="13"/>
+      <c r="G203" s="13"/>
+      <c r="H203" s="13"/>
     </row>
     <row r="204">
-      <c r="F204" s="12"/>
-      <c r="G204" s="12"/>
-      <c r="H204" s="12"/>
+      <c r="F204" s="13"/>
+      <c r="G204" s="13"/>
+      <c r="H204" s="13"/>
     </row>
     <row r="205">
-      <c r="F205" s="12"/>
-      <c r="G205" s="12"/>
-      <c r="H205" s="12"/>
+      <c r="F205" s="13"/>
+      <c r="G205" s="13"/>
+      <c r="H205" s="13"/>
     </row>
     <row r="206">
-      <c r="F206" s="12"/>
-      <c r="G206" s="12"/>
-      <c r="H206" s="12"/>
+      <c r="F206" s="13"/>
+      <c r="G206" s="13"/>
+      <c r="H206" s="13"/>
     </row>
     <row r="207">
-      <c r="F207" s="12"/>
-      <c r="G207" s="12"/>
-      <c r="H207" s="12"/>
+      <c r="F207" s="13"/>
+      <c r="G207" s="13"/>
+      <c r="H207" s="13"/>
     </row>
     <row r="208">
-      <c r="F208" s="12"/>
-      <c r="G208" s="12"/>
-      <c r="H208" s="12"/>
+      <c r="F208" s="13"/>
+      <c r="G208" s="13"/>
+      <c r="H208" s="13"/>
     </row>
     <row r="209">
-      <c r="F209" s="12"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="12"/>
+      <c r="F209" s="13"/>
+      <c r="G209" s="13"/>
+      <c r="H209" s="13"/>
     </row>
     <row r="210">
-      <c r="F210" s="12"/>
-      <c r="G210" s="12"/>
-      <c r="H210" s="12"/>
+      <c r="F210" s="13"/>
+      <c r="G210" s="13"/>
+      <c r="H210" s="13"/>
     </row>
     <row r="211">
-      <c r="F211" s="12"/>
-      <c r="G211" s="12"/>
-      <c r="H211" s="12"/>
+      <c r="F211" s="13"/>
+      <c r="G211" s="13"/>
+      <c r="H211" s="13"/>
     </row>
     <row r="212">
-      <c r="F212" s="12"/>
-      <c r="G212" s="12"/>
-      <c r="H212" s="12"/>
+      <c r="F212" s="13"/>
+      <c r="G212" s="13"/>
+      <c r="H212" s="13"/>
     </row>
     <row r="213">
-      <c r="F213" s="12"/>
-      <c r="G213" s="12"/>
-      <c r="H213" s="12"/>
+      <c r="F213" s="13"/>
+      <c r="G213" s="13"/>
+      <c r="H213" s="13"/>
     </row>
     <row r="214">
-      <c r="F214" s="12"/>
-      <c r="G214" s="12"/>
-      <c r="H214" s="12"/>
+      <c r="F214" s="13"/>
+      <c r="G214" s="13"/>
+      <c r="H214" s="13"/>
     </row>
     <row r="215">
-      <c r="F215" s="12"/>
-      <c r="G215" s="12"/>
-      <c r="H215" s="12"/>
+      <c r="F215" s="13"/>
+      <c r="G215" s="13"/>
+      <c r="H215" s="13"/>
     </row>
     <row r="216">
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
+      <c r="F216" s="13"/>
+      <c r="G216" s="13"/>
+      <c r="H216" s="13"/>
     </row>
     <row r="217">
-      <c r="F217" s="12"/>
-      <c r="G217" s="12"/>
-      <c r="H217" s="12"/>
+      <c r="F217" s="13"/>
+      <c r="G217" s="13"/>
+      <c r="H217" s="13"/>
     </row>
     <row r="218">
-      <c r="F218" s="12"/>
-      <c r="G218" s="12"/>
-      <c r="H218" s="12"/>
+      <c r="F218" s="13"/>
+      <c r="G218" s="13"/>
+      <c r="H218" s="13"/>
     </row>
     <row r="219">
-      <c r="F219" s="12"/>
-      <c r="G219" s="12"/>
-      <c r="H219" s="12"/>
+      <c r="F219" s="13"/>
+      <c r="G219" s="13"/>
+      <c r="H219" s="13"/>
     </row>
     <row r="220">
-      <c r="F220" s="12"/>
-      <c r="G220" s="12"/>
-      <c r="H220" s="12"/>
+      <c r="F220" s="13"/>
+      <c r="G220" s="13"/>
+      <c r="H220" s="13"/>
     </row>
     <row r="221">
-      <c r="F221" s="12"/>
-      <c r="G221" s="12"/>
-      <c r="H221" s="12"/>
+      <c r="F221" s="13"/>
+      <c r="G221" s="13"/>
+      <c r="H221" s="13"/>
     </row>
     <row r="222">
-      <c r="F222" s="12"/>
-      <c r="G222" s="12"/>
-      <c r="H222" s="12"/>
+      <c r="F222" s="13"/>
+      <c r="G222" s="13"/>
+      <c r="H222" s="13"/>
     </row>
     <row r="223">
-      <c r="F223" s="12"/>
-      <c r="G223" s="12"/>
-      <c r="H223" s="12"/>
+      <c r="F223" s="13"/>
+      <c r="G223" s="13"/>
+      <c r="H223" s="13"/>
     </row>
     <row r="224">
-      <c r="F224" s="12"/>
-      <c r="G224" s="12"/>
-      <c r="H224" s="12"/>
+      <c r="F224" s="13"/>
+      <c r="G224" s="13"/>
+      <c r="H224" s="13"/>
     </row>
     <row r="225">
-      <c r="F225" s="12"/>
-      <c r="G225" s="12"/>
-      <c r="H225" s="12"/>
+      <c r="F225" s="13"/>
+      <c r="G225" s="13"/>
+      <c r="H225" s="13"/>
     </row>
     <row r="226">
-      <c r="F226" s="12"/>
-      <c r="G226" s="12"/>
-      <c r="H226" s="12"/>
+      <c r="F226" s="13"/>
+      <c r="G226" s="13"/>
+      <c r="H226" s="13"/>
     </row>
     <row r="227">
-      <c r="F227" s="12"/>
-      <c r="G227" s="12"/>
-      <c r="H227" s="12"/>
+      <c r="F227" s="13"/>
+      <c r="G227" s="13"/>
+      <c r="H227" s="13"/>
     </row>
     <row r="228">
-      <c r="F228" s="12"/>
-      <c r="G228" s="12"/>
-      <c r="H228" s="12"/>
+      <c r="F228" s="13"/>
+      <c r="G228" s="13"/>
+      <c r="H228" s="13"/>
     </row>
     <row r="229">
-      <c r="F229" s="12"/>
-      <c r="G229" s="12"/>
-      <c r="H229" s="12"/>
+      <c r="F229" s="13"/>
+      <c r="G229" s="13"/>
+      <c r="H229" s="13"/>
     </row>
     <row r="230">
-      <c r="F230" s="12"/>
-      <c r="G230" s="12"/>
-      <c r="H230" s="12"/>
+      <c r="F230" s="13"/>
+      <c r="G230" s="13"/>
+      <c r="H230" s="13"/>
     </row>
     <row r="231">
-      <c r="F231" s="12"/>
-      <c r="G231" s="12"/>
-      <c r="H231" s="12"/>
+      <c r="F231" s="13"/>
+      <c r="G231" s="13"/>
+      <c r="H231" s="13"/>
     </row>
     <row r="232">
-      <c r="F232" s="12"/>
-      <c r="G232" s="12"/>
-      <c r="H232" s="12"/>
+      <c r="F232" s="13"/>
+      <c r="G232" s="13"/>
+      <c r="H232" s="13"/>
     </row>
     <row r="233">
-      <c r="F233" s="12"/>
-      <c r="G233" s="12"/>
-      <c r="H233" s="12"/>
+      <c r="F233" s="13"/>
+      <c r="G233" s="13"/>
+      <c r="H233" s="13"/>
     </row>
     <row r="234">
-      <c r="F234" s="12"/>
-      <c r="G234" s="12"/>
-      <c r="H234" s="12"/>
+      <c r="F234" s="13"/>
+      <c r="G234" s="13"/>
+      <c r="H234" s="13"/>
     </row>
     <row r="235">
-      <c r="F235" s="12"/>
-      <c r="G235" s="12"/>
-      <c r="H235" s="12"/>
+      <c r="F235" s="13"/>
+      <c r="G235" s="13"/>
+      <c r="H235" s="13"/>
     </row>
     <row r="236">
-      <c r="F236" s="12"/>
-      <c r="G236" s="12"/>
-      <c r="H236" s="12"/>
+      <c r="F236" s="13"/>
+      <c r="G236" s="13"/>
+      <c r="H236" s="13"/>
     </row>
     <row r="237">
-      <c r="F237" s="12"/>
-      <c r="G237" s="12"/>
-      <c r="H237" s="12"/>
+      <c r="F237" s="13"/>
+      <c r="G237" s="13"/>
+      <c r="H237" s="13"/>
     </row>
     <row r="238">
-      <c r="F238" s="12"/>
-      <c r="G238" s="12"/>
-      <c r="H238" s="12"/>
+      <c r="F238" s="13"/>
+      <c r="G238" s="13"/>
+      <c r="H238" s="13"/>
     </row>
     <row r="239">
-      <c r="F239" s="12"/>
-      <c r="G239" s="12"/>
-      <c r="H239" s="12"/>
+      <c r="F239" s="13"/>
+      <c r="G239" s="13"/>
+      <c r="H239" s="13"/>
     </row>
     <row r="240">
-      <c r="F240" s="12"/>
-      <c r="G240" s="12"/>
-      <c r="H240" s="12"/>
+      <c r="F240" s="13"/>
+      <c r="G240" s="13"/>
+      <c r="H240" s="13"/>
     </row>
     <row r="241">
-      <c r="F241" s="12"/>
-      <c r="G241" s="12"/>
-      <c r="H241" s="12"/>
+      <c r="F241" s="13"/>
+      <c r="G241" s="13"/>
+      <c r="H241" s="13"/>
     </row>
     <row r="242">
-      <c r="F242" s="12"/>
-      <c r="G242" s="12"/>
-      <c r="H242" s="12"/>
+      <c r="F242" s="13"/>
+      <c r="G242" s="13"/>
+      <c r="H242" s="13"/>
     </row>
     <row r="243">
-      <c r="F243" s="12"/>
-      <c r="G243" s="12"/>
-      <c r="H243" s="12"/>
+      <c r="F243" s="13"/>
+      <c r="G243" s="13"/>
+      <c r="H243" s="13"/>
     </row>
     <row r="244">
-      <c r="F244" s="12"/>
-      <c r="G244" s="12"/>
-      <c r="H244" s="12"/>
+      <c r="F244" s="13"/>
+      <c r="G244" s="13"/>
+      <c r="H244" s="13"/>
     </row>
     <row r="245">
-      <c r="F245" s="12"/>
-      <c r="G245" s="12"/>
-      <c r="H245" s="12"/>
+      <c r="F245" s="13"/>
+      <c r="G245" s="13"/>
+      <c r="H245" s="13"/>
     </row>
     <row r="246">
-      <c r="F246" s="12"/>
-      <c r="G246" s="12"/>
-      <c r="H246" s="12"/>
+      <c r="F246" s="13"/>
+      <c r="G246" s="13"/>
+      <c r="H246" s="13"/>
     </row>
     <row r="247">
-      <c r="F247" s="12"/>
-      <c r="G247" s="12"/>
-      <c r="H247" s="12"/>
+      <c r="F247" s="13"/>
+      <c r="G247" s="13"/>
+      <c r="H247" s="13"/>
     </row>
     <row r="248">
-      <c r="F248" s="12"/>
-      <c r="G248" s="12"/>
-      <c r="H248" s="12"/>
+      <c r="F248" s="13"/>
+      <c r="G248" s="13"/>
+      <c r="H248" s="13"/>
     </row>
     <row r="249">
-      <c r="F249" s="12"/>
-      <c r="G249" s="12"/>
-      <c r="H249" s="12"/>
+      <c r="F249" s="13"/>
+      <c r="G249" s="13"/>
+      <c r="H249" s="13"/>
     </row>
     <row r="250">
-      <c r="F250" s="12"/>
-      <c r="G250" s="12"/>
-      <c r="H250" s="12"/>
+      <c r="F250" s="13"/>
+      <c r="G250" s="13"/>
+      <c r="H250" s="13"/>
     </row>
     <row r="251">
-      <c r="F251" s="12"/>
-      <c r="G251" s="12"/>
-      <c r="H251" s="12"/>
+      <c r="F251" s="13"/>
+      <c r="G251" s="13"/>
+      <c r="H251" s="13"/>
     </row>
     <row r="252">
-      <c r="F252" s="12"/>
-      <c r="G252" s="12"/>
-      <c r="H252" s="12"/>
+      <c r="F252" s="13"/>
+      <c r="G252" s="13"/>
+      <c r="H252" s="13"/>
     </row>
     <row r="253">
-      <c r="F253" s="12"/>
-      <c r="G253" s="12"/>
-      <c r="H253" s="12"/>
+      <c r="F253" s="13"/>
+      <c r="G253" s="13"/>
+      <c r="H253" s="13"/>
     </row>
     <row r="254">
-      <c r="F254" s="12"/>
-      <c r="G254" s="12"/>
-      <c r="H254" s="12"/>
+      <c r="F254" s="13"/>
+      <c r="G254" s="13"/>
+      <c r="H254" s="13"/>
     </row>
     <row r="255">
-      <c r="F255" s="12"/>
-      <c r="G255" s="12"/>
-      <c r="H255" s="12"/>
+      <c r="F255" s="13"/>
+      <c r="G255" s="13"/>
+      <c r="H255" s="13"/>
     </row>
     <row r="256">
-      <c r="F256" s="12"/>
-      <c r="G256" s="12"/>
-      <c r="H256" s="12"/>
+      <c r="F256" s="13"/>
+      <c r="G256" s="13"/>
+      <c r="H256" s="13"/>
     </row>
     <row r="257">
-      <c r="F257" s="12"/>
-      <c r="G257" s="12"/>
-      <c r="H257" s="12"/>
+      <c r="F257" s="13"/>
+      <c r="G257" s="13"/>
+      <c r="H257" s="13"/>
     </row>
     <row r="258">
-      <c r="F258" s="12"/>
-      <c r="G258" s="12"/>
-      <c r="H258" s="12"/>
+      <c r="F258" s="13"/>
+      <c r="G258" s="13"/>
+      <c r="H258" s="13"/>
     </row>
     <row r="259">
-      <c r="F259" s="12"/>
-      <c r="G259" s="12"/>
-      <c r="H259" s="12"/>
+      <c r="F259" s="13"/>
+      <c r="G259" s="13"/>
+      <c r="H259" s="13"/>
     </row>
     <row r="260">
-      <c r="F260" s="12"/>
-      <c r="G260" s="12"/>
-      <c r="H260" s="12"/>
+      <c r="F260" s="13"/>
+      <c r="G260" s="13"/>
+      <c r="H260" s="13"/>
     </row>
     <row r="261">
-      <c r="F261" s="12"/>
-      <c r="G261" s="12"/>
-      <c r="H261" s="12"/>
+      <c r="F261" s="13"/>
+      <c r="G261" s="13"/>
+      <c r="H261" s="13"/>
     </row>
     <row r="262">
-      <c r="F262" s="12"/>
-      <c r="G262" s="12"/>
-      <c r="H262" s="12"/>
+      <c r="F262" s="13"/>
+      <c r="G262" s="13"/>
+      <c r="H262" s="13"/>
     </row>
     <row r="263">
-      <c r="F263" s="12"/>
-      <c r="G263" s="12"/>
-      <c r="H263" s="12"/>
+      <c r="F263" s="13"/>
+      <c r="G263" s="13"/>
+      <c r="H263" s="13"/>
     </row>
     <row r="264">
-      <c r="F264" s="12"/>
-      <c r="G264" s="12"/>
-      <c r="H264" s="12"/>
+      <c r="F264" s="13"/>
+      <c r="G264" s="13"/>
+      <c r="H264" s="13"/>
     </row>
     <row r="265">
-      <c r="F265" s="12"/>
-      <c r="G265" s="12"/>
-      <c r="H265" s="12"/>
+      <c r="F265" s="13"/>
+      <c r="G265" s="13"/>
+      <c r="H265" s="13"/>
     </row>
     <row r="266">
-      <c r="F266" s="12"/>
-      <c r="G266" s="12"/>
-      <c r="H266" s="12"/>
+      <c r="F266" s="13"/>
+      <c r="G266" s="13"/>
+      <c r="H266" s="13"/>
     </row>
     <row r="267">
-      <c r="F267" s="12"/>
-      <c r="G267" s="12"/>
-      <c r="H267" s="12"/>
+      <c r="F267" s="13"/>
+      <c r="G267" s="13"/>
+      <c r="H267" s="13"/>
     </row>
     <row r="268">
-      <c r="F268" s="12"/>
-      <c r="G268" s="12"/>
-      <c r="H268" s="12"/>
+      <c r="F268" s="13"/>
+      <c r="G268" s="13"/>
+      <c r="H268" s="13"/>
     </row>
     <row r="269">
-      <c r="F269" s="12"/>
-      <c r="G269" s="12"/>
-      <c r="H269" s="12"/>
+      <c r="F269" s="13"/>
+      <c r="G269" s="13"/>
+      <c r="H269" s="13"/>
     </row>
     <row r="270">
-      <c r="F270" s="12"/>
-      <c r="G270" s="12"/>
-      <c r="H270" s="12"/>
+      <c r="F270" s="13"/>
+      <c r="G270" s="13"/>
+      <c r="H270" s="13"/>
     </row>
     <row r="271">
-      <c r="F271" s="12"/>
-      <c r="G271" s="12"/>
-      <c r="H271" s="12"/>
+      <c r="F271" s="13"/>
+      <c r="G271" s="13"/>
+      <c r="H271" s="13"/>
     </row>
     <row r="272">
-      <c r="F272" s="12"/>
-      <c r="G272" s="12"/>
-      <c r="H272" s="12"/>
+      <c r="F272" s="13"/>
+      <c r="G272" s="13"/>
+      <c r="H272" s="13"/>
     </row>
     <row r="273">
-      <c r="F273" s="12"/>
-      <c r="G273" s="12"/>
-      <c r="H273" s="12"/>
+      <c r="F273" s="13"/>
+      <c r="G273" s="13"/>
+      <c r="H273" s="13"/>
     </row>
     <row r="274">
-      <c r="F274" s="12"/>
-      <c r="G274" s="12"/>
-      <c r="H274" s="12"/>
+      <c r="F274" s="13"/>
+      <c r="G274" s="13"/>
+      <c r="H274" s="13"/>
     </row>
     <row r="275">
-      <c r="F275" s="12"/>
-      <c r="G275" s="12"/>
-      <c r="H275" s="12"/>
+      <c r="F275" s="13"/>
+      <c r="G275" s="13"/>
+      <c r="H275" s="13"/>
     </row>
     <row r="276">
-      <c r="F276" s="12"/>
-      <c r="G276" s="12"/>
-      <c r="H276" s="12"/>
+      <c r="F276" s="13"/>
+      <c r="G276" s="13"/>
+      <c r="H276" s="13"/>
     </row>
     <row r="277">
-      <c r="F277" s="12"/>
-      <c r="G277" s="12"/>
-      <c r="H277" s="12"/>
+      <c r="F277" s="13"/>
+      <c r="G277" s="13"/>
+      <c r="H277" s="13"/>
     </row>
     <row r="278">
-      <c r="F278" s="12"/>
-      <c r="G278" s="12"/>
-      <c r="H278" s="12"/>
+      <c r="F278" s="13"/>
+      <c r="G278" s="13"/>
+      <c r="H278" s="13"/>
     </row>
     <row r="279">
-      <c r="F279" s="12"/>
-      <c r="G279" s="12"/>
-      <c r="H279" s="12"/>
+      <c r="F279" s="13"/>
+      <c r="G279" s="13"/>
+      <c r="H279" s="13"/>
     </row>
     <row r="280">
-      <c r="F280" s="12"/>
-      <c r="G280" s="12"/>
-      <c r="H280" s="12"/>
+      <c r="F280" s="13"/>
+      <c r="G280" s="13"/>
+      <c r="H280" s="13"/>
     </row>
     <row r="281">
-      <c r="F281" s="12"/>
-      <c r="G281" s="12"/>
-      <c r="H281" s="12"/>
+      <c r="F281" s="13"/>
+      <c r="G281" s="13"/>
+      <c r="H281" s="13"/>
     </row>
     <row r="282">
-      <c r="F282" s="12"/>
-      <c r="G282" s="12"/>
-      <c r="H282" s="12"/>
+      <c r="F282" s="13"/>
+      <c r="G282" s="13"/>
+      <c r="H282" s="13"/>
     </row>
     <row r="283">
-      <c r="F283" s="12"/>
-      <c r="G283" s="12"/>
-      <c r="H283" s="12"/>
+      <c r="F283" s="13"/>
+      <c r="G283" s="13"/>
+      <c r="H283" s="13"/>
     </row>
     <row r="284">
-      <c r="F284" s="12"/>
-      <c r="G284" s="12"/>
-      <c r="H284" s="12"/>
+      <c r="F284" s="13"/>
+      <c r="G284" s="13"/>
+      <c r="H284" s="13"/>
     </row>
     <row r="285">
-      <c r="F285" s="12"/>
-      <c r="G285" s="12"/>
-      <c r="H285" s="12"/>
+      <c r="F285" s="13"/>
+      <c r="G285" s="13"/>
+      <c r="H285" s="13"/>
     </row>
     <row r="286">
-      <c r="F286" s="12"/>
-      <c r="G286" s="12"/>
-      <c r="H286" s="12"/>
+      <c r="F286" s="13"/>
+      <c r="G286" s="13"/>
+      <c r="H286" s="13"/>
     </row>
     <row r="287">
-      <c r="F287" s="12"/>
-      <c r="G287" s="12"/>
-      <c r="H287" s="12"/>
+      <c r="F287" s="13"/>
+      <c r="G287" s="13"/>
+      <c r="H287" s="13"/>
     </row>
     <row r="288">
-      <c r="F288" s="12"/>
-      <c r="G288" s="12"/>
-      <c r="H288" s="12"/>
+      <c r="F288" s="13"/>
+      <c r="G288" s="13"/>
+      <c r="H288" s="13"/>
     </row>
     <row r="289">
-      <c r="F289" s="12"/>
-      <c r="G289" s="12"/>
-      <c r="H289" s="12"/>
+      <c r="F289" s="13"/>
+      <c r="G289" s="13"/>
+      <c r="H289" s="13"/>
     </row>
     <row r="290">
-      <c r="F290" s="12"/>
-      <c r="G290" s="12"/>
-      <c r="H290" s="12"/>
+      <c r="F290" s="13"/>
+      <c r="G290" s="13"/>
+      <c r="H290" s="13"/>
     </row>
     <row r="291">
-      <c r="F291" s="12"/>
-      <c r="G291" s="12"/>
-      <c r="H291" s="12"/>
+      <c r="F291" s="13"/>
+      <c r="G291" s="13"/>
+      <c r="H291" s="13"/>
     </row>
     <row r="292">
-      <c r="F292" s="12"/>
-      <c r="G292" s="12"/>
-      <c r="H292" s="12"/>
+      <c r="F292" s="13"/>
+      <c r="G292" s="13"/>
+      <c r="H292" s="13"/>
     </row>
     <row r="293">
-      <c r="F293" s="12"/>
-      <c r="G293" s="12"/>
-      <c r="H293" s="12"/>
+      <c r="F293" s="13"/>
+      <c r="G293" s="13"/>
+      <c r="H293" s="13"/>
     </row>
     <row r="294">
-      <c r="F294" s="12"/>
-      <c r="G294" s="12"/>
-      <c r="H294" s="12"/>
+      <c r="F294" s="13"/>
+      <c r="G294" s="13"/>
+      <c r="H294" s="13"/>
     </row>
     <row r="295">
-      <c r="F295" s="12"/>
-      <c r="G295" s="12"/>
-      <c r="H295" s="12"/>
+      <c r="F295" s="13"/>
+      <c r="G295" s="13"/>
+      <c r="H295" s="13"/>
     </row>
     <row r="296">
-      <c r="F296" s="12"/>
-      <c r="G296" s="12"/>
-      <c r="H296" s="12"/>
+      <c r="F296" s="13"/>
+      <c r="G296" s="13"/>
+      <c r="H296" s="13"/>
     </row>
     <row r="297">
-      <c r="F297" s="12"/>
-      <c r="G297" s="12"/>
-      <c r="H297" s="12"/>
+      <c r="F297" s="13"/>
+      <c r="G297" s="13"/>
+      <c r="H297" s="13"/>
     </row>
     <row r="298">
-      <c r="F298" s="12"/>
-      <c r="G298" s="12"/>
-      <c r="H298" s="12"/>
+      <c r="F298" s="13"/>
+      <c r="G298" s="13"/>
+      <c r="H298" s="13"/>
     </row>
     <row r="299">
-      <c r="F299" s="12"/>
-      <c r="G299" s="12"/>
-      <c r="H299" s="12"/>
+      <c r="F299" s="13"/>
+      <c r="G299" s="13"/>
+      <c r="H299" s="13"/>
     </row>
     <row r="300">
-      <c r="F300" s="12"/>
-      <c r="G300" s="12"/>
-      <c r="H300" s="12"/>
+      <c r="F300" s="13"/>
+      <c r="G300" s="13"/>
+      <c r="H300" s="13"/>
     </row>
     <row r="301">
-      <c r="F301" s="12"/>
-      <c r="G301" s="12"/>
-      <c r="H301" s="12"/>
+      <c r="F301" s="13"/>
+      <c r="G301" s="13"/>
+      <c r="H301" s="13"/>
     </row>
     <row r="302">
-      <c r="F302" s="12"/>
-      <c r="G302" s="12"/>
-      <c r="H302" s="12"/>
+      <c r="F302" s="13"/>
+      <c r="G302" s="13"/>
+      <c r="H302" s="13"/>
     </row>
     <row r="303">
-      <c r="F303" s="12"/>
-      <c r="G303" s="12"/>
-      <c r="H303" s="12"/>
+      <c r="F303" s="13"/>
+      <c r="G303" s="13"/>
+      <c r="H303" s="13"/>
     </row>
     <row r="304">
-      <c r="F304" s="12"/>
-      <c r="G304" s="12"/>
-      <c r="H304" s="12"/>
+      <c r="F304" s="13"/>
+      <c r="G304" s="13"/>
+      <c r="H304" s="13"/>
     </row>
     <row r="305">
-      <c r="F305" s="12"/>
-      <c r="G305" s="12"/>
-      <c r="H305" s="12"/>
+      <c r="F305" s="13"/>
+      <c r="G305" s="13"/>
+      <c r="H305" s="13"/>
     </row>
     <row r="306">
-      <c r="F306" s="12"/>
-      <c r="G306" s="12"/>
-      <c r="H306" s="12"/>
+      <c r="F306" s="13"/>
+      <c r="G306" s="13"/>
+      <c r="H306" s="13"/>
     </row>
     <row r="307">
-      <c r="F307" s="12"/>
-      <c r="G307" s="12"/>
-      <c r="H307" s="12"/>
+      <c r="F307" s="13"/>
+      <c r="G307" s="13"/>
+      <c r="H307" s="13"/>
     </row>
     <row r="308">
-      <c r="F308" s="12"/>
-      <c r="G308" s="12"/>
-      <c r="H308" s="12"/>
+      <c r="F308" s="13"/>
+      <c r="G308" s="13"/>
+      <c r="H308" s="13"/>
     </row>
     <row r="309">
-      <c r="F309" s="12"/>
-      <c r="G309" s="12"/>
-      <c r="H309" s="12"/>
+      <c r="F309" s="13"/>
+      <c r="G309" s="13"/>
+      <c r="H309" s="13"/>
     </row>
     <row r="310">
-      <c r="F310" s="12"/>
-      <c r="G310" s="12"/>
-      <c r="H310" s="12"/>
+      <c r="F310" s="13"/>
+      <c r="G310" s="13"/>
+      <c r="H310" s="13"/>
     </row>
     <row r="311">
-      <c r="F311" s="12"/>
-      <c r="G311" s="12"/>
-      <c r="H311" s="12"/>
+      <c r="F311" s="13"/>
+      <c r="G311" s="13"/>
+      <c r="H311" s="13"/>
     </row>
     <row r="312">
-      <c r="F312" s="12"/>
-      <c r="G312" s="12"/>
-      <c r="H312" s="12"/>
+      <c r="F312" s="13"/>
+      <c r="G312" s="13"/>
+      <c r="H312" s="13"/>
     </row>
     <row r="313">
-      <c r="F313" s="12"/>
-      <c r="G313" s="12"/>
-      <c r="H313" s="12"/>
+      <c r="F313" s="13"/>
+      <c r="G313" s="13"/>
+      <c r="H313" s="13"/>
     </row>
     <row r="314">
-      <c r="F314" s="12"/>
-      <c r="G314" s="12"/>
-      <c r="H314" s="12"/>
+      <c r="F314" s="13"/>
+      <c r="G314" s="13"/>
+      <c r="H314" s="13"/>
     </row>
     <row r="315">
-      <c r="F315" s="12"/>
-      <c r="G315" s="12"/>
-      <c r="H315" s="12"/>
+      <c r="F315" s="13"/>
+      <c r="G315" s="13"/>
+      <c r="H315" s="13"/>
     </row>
     <row r="316">
-      <c r="F316" s="12"/>
-      <c r="G316" s="12"/>
-      <c r="H316" s="12"/>
+      <c r="F316" s="13"/>
+      <c r="G316" s="13"/>
+      <c r="H316" s="13"/>
     </row>
     <row r="317">
-      <c r="F317" s="12"/>
-      <c r="G317" s="12"/>
-      <c r="H317" s="12"/>
+      <c r="F317" s="13"/>
+      <c r="G317" s="13"/>
+      <c r="H317" s="13"/>
     </row>
     <row r="318">
-      <c r="F318" s="12"/>
-      <c r="G318" s="12"/>
-      <c r="H318" s="12"/>
+      <c r="F318" s="13"/>
+      <c r="G318" s="13"/>
+      <c r="H318" s="13"/>
     </row>
     <row r="319">
-      <c r="F319" s="12"/>
-      <c r="G319" s="12"/>
-      <c r="H319" s="12"/>
+      <c r="F319" s="13"/>
+      <c r="G319" s="13"/>
+      <c r="H319" s="13"/>
     </row>
     <row r="320">
-      <c r="F320" s="12"/>
-      <c r="G320" s="12"/>
-      <c r="H320" s="12"/>
+      <c r="F320" s="13"/>
+      <c r="G320" s="13"/>
+      <c r="H320" s="13"/>
     </row>
     <row r="321">
-      <c r="F321" s="12"/>
-      <c r="G321" s="12"/>
-      <c r="H321" s="12"/>
+      <c r="F321" s="13"/>
+      <c r="G321" s="13"/>
+      <c r="H321" s="13"/>
     </row>
     <row r="322">
-      <c r="F322" s="12"/>
-      <c r="G322" s="12"/>
-      <c r="H322" s="12"/>
+      <c r="F322" s="13"/>
+      <c r="G322" s="13"/>
+      <c r="H322" s="13"/>
     </row>
     <row r="323">
-      <c r="F323" s="12"/>
-      <c r="G323" s="12"/>
-      <c r="H323" s="12"/>
+      <c r="F323" s="13"/>
+      <c r="G323" s="13"/>
+      <c r="H323" s="13"/>
     </row>
     <row r="324">
-      <c r="F324" s="12"/>
-      <c r="G324" s="12"/>
-      <c r="H324" s="12"/>
+      <c r="F324" s="13"/>
+      <c r="G324" s="13"/>
+      <c r="H324" s="13"/>
     </row>
     <row r="325">
-      <c r="F325" s="12"/>
-      <c r="G325" s="12"/>
-      <c r="H325" s="12"/>
+      <c r="F325" s="13"/>
+      <c r="G325" s="13"/>
+      <c r="H325" s="13"/>
     </row>
     <row r="326">
-      <c r="F326" s="12"/>
-      <c r="G326" s="12"/>
-      <c r="H326" s="12"/>
+      <c r="F326" s="13"/>
+      <c r="G326" s="13"/>
+      <c r="H326" s="13"/>
     </row>
     <row r="327">
-      <c r="F327" s="12"/>
-      <c r="G327" s="12"/>
-      <c r="H327" s="12"/>
+      <c r="F327" s="13"/>
+      <c r="G327" s="13"/>
+      <c r="H327" s="13"/>
     </row>
     <row r="328">
-      <c r="F328" s="12"/>
-      <c r="G328" s="12"/>
-      <c r="H328" s="12"/>
+      <c r="F328" s="13"/>
+      <c r="G328" s="13"/>
+      <c r="H328" s="13"/>
     </row>
     <row r="329">
-      <c r="F329" s="12"/>
-      <c r="G329" s="12"/>
-      <c r="H329" s="12"/>
+      <c r="F329" s="13"/>
+      <c r="G329" s="13"/>
+      <c r="H329" s="13"/>
     </row>
     <row r="330">
-      <c r="F330" s="12"/>
-      <c r="G330" s="12"/>
-      <c r="H330" s="12"/>
+      <c r="F330" s="13"/>
+      <c r="G330" s="13"/>
+      <c r="H330" s="13"/>
     </row>
     <row r="331">
-      <c r="F331" s="12"/>
-      <c r="G331" s="12"/>
-      <c r="H331" s="12"/>
+      <c r="F331" s="13"/>
+      <c r="G331" s="13"/>
+      <c r="H331" s="13"/>
     </row>
     <row r="332">
-      <c r="F332" s="12"/>
-      <c r="G332" s="12"/>
-      <c r="H332" s="12"/>
+      <c r="F332" s="13"/>
+      <c r="G332" s="13"/>
+      <c r="H332" s="13"/>
     </row>
     <row r="333">
-      <c r="F333" s="12"/>
-      <c r="G333" s="12"/>
-      <c r="H333" s="12"/>
+      <c r="F333" s="13"/>
+      <c r="G333" s="13"/>
+      <c r="H333" s="13"/>
     </row>
     <row r="334">
-      <c r="F334" s="12"/>
-      <c r="G334" s="12"/>
-      <c r="H334" s="12"/>
+      <c r="F334" s="13"/>
+      <c r="G334" s="13"/>
+      <c r="H334" s="13"/>
     </row>
     <row r="335">
-      <c r="F335" s="12"/>
-      <c r="G335" s="12"/>
-      <c r="H335" s="12"/>
+      <c r="F335" s="13"/>
+      <c r="G335" s="13"/>
+      <c r="H335" s="13"/>
     </row>
     <row r="336">
-      <c r="F336" s="12"/>
-      <c r="G336" s="12"/>
-      <c r="H336" s="12"/>
+      <c r="F336" s="13"/>
+      <c r="G336" s="13"/>
+      <c r="H336" s="13"/>
     </row>
     <row r="337">
-      <c r="F337" s="12"/>
-      <c r="G337" s="12"/>
-      <c r="H337" s="12"/>
+      <c r="F337" s="13"/>
+      <c r="G337" s="13"/>
+      <c r="H337" s="13"/>
     </row>
     <row r="338">
-      <c r="F338" s="12"/>
-      <c r="G338" s="12"/>
-      <c r="H338" s="12"/>
+      <c r="F338" s="13"/>
+      <c r="G338" s="13"/>
+      <c r="H338" s="13"/>
     </row>
     <row r="339">
-      <c r="F339" s="12"/>
-      <c r="G339" s="12"/>
-      <c r="H339" s="12"/>
+      <c r="F339" s="13"/>
+      <c r="G339" s="13"/>
+      <c r="H339" s="13"/>
     </row>
     <row r="340">
-      <c r="F340" s="12"/>
-      <c r="G340" s="12"/>
-      <c r="H340" s="12"/>
+      <c r="F340" s="13"/>
+      <c r="G340" s="13"/>
+      <c r="H340" s="13"/>
     </row>
     <row r="341">
-      <c r="F341" s="12"/>
-      <c r="G341" s="12"/>
-      <c r="H341" s="12"/>
+      <c r="F341" s="13"/>
+      <c r="G341" s="13"/>
+      <c r="H341" s="13"/>
     </row>
     <row r="342">
-      <c r="F342" s="12"/>
-      <c r="G342" s="12"/>
-      <c r="H342" s="12"/>
+      <c r="F342" s="13"/>
+      <c r="G342" s="13"/>
+      <c r="H342" s="13"/>
     </row>
     <row r="343">
-      <c r="F343" s="12"/>
-      <c r="G343" s="12"/>
-      <c r="H343" s="12"/>
+      <c r="F343" s="13"/>
+      <c r="G343" s="13"/>
+      <c r="H343" s="13"/>
     </row>
     <row r="344">
-      <c r="F344" s="12"/>
-      <c r="G344" s="12"/>
-      <c r="H344" s="12"/>
+      <c r="F344" s="13"/>
+      <c r="G344" s="13"/>
+      <c r="H344" s="13"/>
     </row>
     <row r="345">
-      <c r="F345" s="12"/>
-      <c r="G345" s="12"/>
-      <c r="H345" s="12"/>
+      <c r="F345" s="13"/>
+      <c r="G345" s="13"/>
+      <c r="H345" s="13"/>
     </row>
     <row r="346">
-      <c r="F346" s="12"/>
-      <c r="G346" s="12"/>
-      <c r="H346" s="12"/>
+      <c r="F346" s="13"/>
+      <c r="G346" s="13"/>
+      <c r="H346" s="13"/>
     </row>
     <row r="347">
-      <c r="F347" s="12"/>
-      <c r="G347" s="12"/>
-      <c r="H347" s="12"/>
+      <c r="F347" s="13"/>
+      <c r="G347" s="13"/>
+      <c r="H347" s="13"/>
     </row>
     <row r="348">
-      <c r="F348" s="12"/>
-      <c r="G348" s="12"/>
-      <c r="H348" s="12"/>
+      <c r="F348" s="13"/>
+      <c r="G348" s="13"/>
+      <c r="H348" s="13"/>
     </row>
     <row r="349">
-      <c r="F349" s="12"/>
-      <c r="G349" s="12"/>
-      <c r="H349" s="12"/>
+      <c r="F349" s="13"/>
+      <c r="G349" s="13"/>
+      <c r="H349" s="13"/>
     </row>
     <row r="350">
-      <c r="F350" s="12"/>
-      <c r="G350" s="12"/>
-      <c r="H350" s="12"/>
+      <c r="F350" s="13"/>
+      <c r="G350" s="13"/>
+      <c r="H350" s="13"/>
     </row>
     <row r="351">
-      <c r="F351" s="12"/>
-      <c r="G351" s="12"/>
-      <c r="H351" s="12"/>
+      <c r="F351" s="13"/>
+      <c r="G351" s="13"/>
+      <c r="H351" s="13"/>
     </row>
     <row r="352">
-      <c r="F352" s="12"/>
-      <c r="G352" s="12"/>
-      <c r="H352" s="12"/>
+      <c r="F352" s="13"/>
+      <c r="G352" s="13"/>
+      <c r="H352" s="13"/>
     </row>
     <row r="353">
-      <c r="F353" s="12"/>
-      <c r="G353" s="12"/>
-      <c r="H353" s="12"/>
+      <c r="F353" s="13"/>
+      <c r="G353" s="13"/>
+      <c r="H353" s="13"/>
     </row>
     <row r="354">
-      <c r="F354" s="12"/>
-      <c r="G354" s="12"/>
-      <c r="H354" s="12"/>
+      <c r="F354" s="13"/>
+      <c r="G354" s="13"/>
+      <c r="H354" s="13"/>
     </row>
     <row r="355">
-      <c r="F355" s="12"/>
-      <c r="G355" s="12"/>
-      <c r="H355" s="12"/>
+      <c r="F355" s="13"/>
+      <c r="G355" s="13"/>
+      <c r="H355" s="13"/>
     </row>
     <row r="356">
-      <c r="F356" s="12"/>
-      <c r="G356" s="12"/>
-      <c r="H356" s="12"/>
+      <c r="F356" s="13"/>
+      <c r="G356" s="13"/>
+      <c r="H356" s="13"/>
     </row>
     <row r="357">
-      <c r="F357" s="12"/>
-      <c r="G357" s="12"/>
-      <c r="H357" s="12"/>
+      <c r="F357" s="13"/>
+      <c r="G357" s="13"/>
+      <c r="H357" s="13"/>
     </row>
     <row r="358">
-      <c r="F358" s="12"/>
-      <c r="G358" s="12"/>
-      <c r="H358" s="12"/>
+      <c r="F358" s="13"/>
+      <c r="G358" s="13"/>
+      <c r="H358" s="13"/>
     </row>
     <row r="359">
-      <c r="F359" s="12"/>
-      <c r="G359" s="12"/>
-      <c r="H359" s="12"/>
+      <c r="F359" s="13"/>
+      <c r="G359" s="13"/>
+      <c r="H359" s="13"/>
     </row>
     <row r="360">
-      <c r="F360" s="12"/>
-      <c r="G360" s="12"/>
-      <c r="H360" s="12"/>
+      <c r="F360" s="13"/>
+      <c r="G360" s="13"/>
+      <c r="H360" s="13"/>
     </row>
     <row r="361">
-      <c r="F361" s="12"/>
-      <c r="G361" s="12"/>
-      <c r="H361" s="12"/>
+      <c r="F361" s="13"/>
+      <c r="G361" s="13"/>
+      <c r="H361" s="13"/>
     </row>
     <row r="362">
-      <c r="F362" s="12"/>
-      <c r="G362" s="12"/>
-      <c r="H362" s="12"/>
+      <c r="F362" s="13"/>
+      <c r="G362" s="13"/>
+      <c r="H362" s="13"/>
     </row>
     <row r="363">
-      <c r="F363" s="12"/>
-      <c r="G363" s="12"/>
-      <c r="H363" s="12"/>
+      <c r="F363" s="13"/>
+      <c r="G363" s="13"/>
+      <c r="H363" s="13"/>
     </row>
     <row r="364">
-      <c r="F364" s="12"/>
-      <c r="G364" s="12"/>
-      <c r="H364" s="12"/>
+      <c r="F364" s="13"/>
+      <c r="G364" s="13"/>
+      <c r="H364" s="13"/>
     </row>
     <row r="365">
-      <c r="F365" s="12"/>
-      <c r="G365" s="12"/>
-      <c r="H365" s="12"/>
+      <c r="F365" s="13"/>
+      <c r="G365" s="13"/>
+      <c r="H365" s="13"/>
     </row>
     <row r="366">
-      <c r="F366" s="12"/>
-      <c r="G366" s="12"/>
-      <c r="H366" s="12"/>
+      <c r="F366" s="13"/>
+      <c r="G366" s="13"/>
+      <c r="H366" s="13"/>
     </row>
     <row r="367">
-      <c r="F367" s="12"/>
-      <c r="G367" s="12"/>
-      <c r="H367" s="12"/>
+      <c r="F367" s="13"/>
+      <c r="G367" s="13"/>
+      <c r="H367" s="13"/>
     </row>
     <row r="368">
-      <c r="F368" s="12"/>
-      <c r="G368" s="12"/>
-      <c r="H368" s="12"/>
+      <c r="F368" s="13"/>
+      <c r="G368" s="13"/>
+      <c r="H368" s="13"/>
     </row>
     <row r="369">
-      <c r="F369" s="12"/>
-      <c r="G369" s="12"/>
-      <c r="H369" s="12"/>
+      <c r="F369" s="13"/>
+      <c r="G369" s="13"/>
+      <c r="H369" s="13"/>
     </row>
     <row r="370">
-      <c r="F370" s="12"/>
-      <c r="G370" s="12"/>
-      <c r="H370" s="12"/>
+      <c r="F370" s="13"/>
+      <c r="G370" s="13"/>
+      <c r="H370" s="13"/>
     </row>
     <row r="371">
-      <c r="F371" s="12"/>
-      <c r="G371" s="12"/>
-      <c r="H371" s="12"/>
+      <c r="F371" s="13"/>
+      <c r="G371" s="13"/>
+      <c r="H371" s="13"/>
     </row>
     <row r="372">
-      <c r="F372" s="12"/>
-      <c r="G372" s="12"/>
-      <c r="H372" s="12"/>
+      <c r="F372" s="13"/>
+      <c r="G372" s="13"/>
+      <c r="H372" s="13"/>
     </row>
     <row r="373">
-      <c r="F373" s="12"/>
-      <c r="G373" s="12"/>
-      <c r="H373" s="12"/>
+      <c r="F373" s="13"/>
+      <c r="G373" s="13"/>
+      <c r="H373" s="13"/>
     </row>
     <row r="374">
-      <c r="F374" s="12"/>
-      <c r="G374" s="12"/>
-      <c r="H374" s="12"/>
+      <c r="F374" s="13"/>
+      <c r="G374" s="13"/>
+      <c r="H374" s="13"/>
     </row>
     <row r="375">
-      <c r="F375" s="12"/>
-      <c r="G375" s="12"/>
-      <c r="H375" s="12"/>
+      <c r="F375" s="13"/>
+      <c r="G375" s="13"/>
+      <c r="H375" s="13"/>
     </row>
     <row r="376">
-      <c r="F376" s="12"/>
-      <c r="G376" s="12"/>
-      <c r="H376" s="12"/>
+      <c r="F376" s="13"/>
+      <c r="G376" s="13"/>
+      <c r="H376" s="13"/>
     </row>
     <row r="377">
-      <c r="F377" s="12"/>
-      <c r="G377" s="12"/>
-      <c r="H377" s="12"/>
+      <c r="F377" s="13"/>
+      <c r="G377" s="13"/>
+      <c r="H377" s="13"/>
     </row>
     <row r="378">
-      <c r="F378" s="12"/>
-      <c r="G378" s="12"/>
-      <c r="H378" s="12"/>
+      <c r="F378" s="13"/>
+      <c r="G378" s="13"/>
+      <c r="H378" s="13"/>
     </row>
     <row r="379">
-      <c r="F379" s="12"/>
-      <c r="G379" s="12"/>
-      <c r="H379" s="12"/>
+      <c r="F379" s="13"/>
+      <c r="G379" s="13"/>
+      <c r="H379" s="13"/>
     </row>
     <row r="380">
-      <c r="F380" s="12"/>
-      <c r="G380" s="12"/>
-      <c r="H380" s="12"/>
+      <c r="F380" s="13"/>
+      <c r="G380" s="13"/>
+      <c r="H380" s="13"/>
     </row>
     <row r="381">
-      <c r="F381" s="12"/>
-      <c r="G381" s="12"/>
-      <c r="H381" s="12"/>
+      <c r="F381" s="13"/>
+      <c r="G381" s="13"/>
+      <c r="H381" s="13"/>
     </row>
     <row r="382">
-      <c r="F382" s="12"/>
-      <c r="G382" s="12"/>
-      <c r="H382" s="12"/>
+      <c r="F382" s="13"/>
+      <c r="G382" s="13"/>
+      <c r="H382" s="13"/>
     </row>
     <row r="383">
-      <c r="F383" s="12"/>
-      <c r="G383" s="12"/>
-      <c r="H383" s="12"/>
+      <c r="F383" s="13"/>
+      <c r="G383" s="13"/>
+      <c r="H383" s="13"/>
     </row>
     <row r="384">
-      <c r="F384" s="12"/>
-      <c r="G384" s="12"/>
-      <c r="H384" s="12"/>
+      <c r="F384" s="13"/>
+      <c r="G384" s="13"/>
+      <c r="H384" s="13"/>
     </row>
     <row r="385">
-      <c r="F385" s="12"/>
-      <c r="G385" s="12"/>
-      <c r="H385" s="12"/>
+      <c r="F385" s="13"/>
+      <c r="G385" s="13"/>
+      <c r="H385" s="13"/>
     </row>
     <row r="386">
-      <c r="F386" s="12"/>
-      <c r="G386" s="12"/>
-      <c r="H386" s="12"/>
+      <c r="F386" s="13"/>
+      <c r="G386" s="13"/>
+      <c r="H386" s="13"/>
     </row>
     <row r="387">
-      <c r="F387" s="12"/>
-      <c r="G387" s="12"/>
-      <c r="H387" s="12"/>
+      <c r="F387" s="13"/>
+      <c r="G387" s="13"/>
+      <c r="H387" s="13"/>
     </row>
     <row r="388">
-      <c r="F388" s="12"/>
-      <c r="G388" s="12"/>
-      <c r="H388" s="12"/>
+      <c r="F388" s="13"/>
+      <c r="G388" s="13"/>
+      <c r="H388" s="13"/>
     </row>
     <row r="389">
-      <c r="F389" s="12"/>
-      <c r="G389" s="12"/>
-      <c r="H389" s="12"/>
+      <c r="F389" s="13"/>
+      <c r="G389" s="13"/>
+      <c r="H389" s="13"/>
     </row>
     <row r="390">
-      <c r="F390" s="12"/>
-      <c r="G390" s="12"/>
-      <c r="H390" s="12"/>
+      <c r="F390" s="13"/>
+      <c r="G390" s="13"/>
+      <c r="H390" s="13"/>
     </row>
     <row r="391">
-      <c r="F391" s="12"/>
-      <c r="G391" s="12"/>
-      <c r="H391" s="12"/>
+      <c r="F391" s="13"/>
+      <c r="G391" s="13"/>
+      <c r="H391" s="13"/>
     </row>
     <row r="392">
-      <c r="F392" s="12"/>
-      <c r="G392" s="12"/>
-      <c r="H392" s="12"/>
+      <c r="F392" s="13"/>
+      <c r="G392" s="13"/>
+      <c r="H392" s="13"/>
     </row>
     <row r="393">
-      <c r="F393" s="12"/>
-      <c r="G393" s="12"/>
-      <c r="H393" s="12"/>
+      <c r="F393" s="13"/>
+      <c r="G393" s="13"/>
+      <c r="H393" s="13"/>
     </row>
     <row r="394">
-      <c r="F394" s="12"/>
-      <c r="G394" s="12"/>
-      <c r="H394" s="12"/>
+      <c r="F394" s="13"/>
+      <c r="G394" s="13"/>
+      <c r="H394" s="13"/>
     </row>
     <row r="395">
-      <c r="F395" s="12"/>
-      <c r="G395" s="12"/>
-      <c r="H395" s="12"/>
+      <c r="F395" s="13"/>
+      <c r="G395" s="13"/>
+      <c r="H395" s="13"/>
     </row>
     <row r="396">
-      <c r="F396" s="12"/>
-      <c r="G396" s="12"/>
-      <c r="H396" s="12"/>
+      <c r="F396" s="13"/>
+      <c r="G396" s="13"/>
+      <c r="H396" s="13"/>
     </row>
     <row r="397">
-      <c r="F397" s="12"/>
-      <c r="G397" s="12"/>
-      <c r="H397" s="12"/>
+      <c r="F397" s="13"/>
+      <c r="G397" s="13"/>
+      <c r="H397" s="13"/>
     </row>
     <row r="398">
-      <c r="F398" s="12"/>
-      <c r="G398" s="12"/>
-      <c r="H398" s="12"/>
+      <c r="F398" s="13"/>
+      <c r="G398" s="13"/>
+      <c r="H398" s="13"/>
     </row>
     <row r="399">
-      <c r="F399" s="12"/>
-      <c r="G399" s="12"/>
-      <c r="H399" s="12"/>
+      <c r="F399" s="13"/>
+      <c r="G399" s="13"/>
+      <c r="H399" s="13"/>
     </row>
     <row r="400">
-      <c r="F400" s="12"/>
-      <c r="G400" s="12"/>
-      <c r="H400" s="12"/>
+      <c r="F400" s="13"/>
+      <c r="G400" s="13"/>
+      <c r="H400" s="13"/>
     </row>
     <row r="401">
-      <c r="F401" s="12"/>
-      <c r="G401" s="12"/>
-      <c r="H401" s="12"/>
+      <c r="F401" s="13"/>
+      <c r="G401" s="13"/>
+      <c r="H401" s="13"/>
     </row>
     <row r="402">
-      <c r="F402" s="12"/>
-      <c r="G402" s="12"/>
-      <c r="H402" s="12"/>
+      <c r="F402" s="13"/>
+      <c r="G402" s="13"/>
+      <c r="H402" s="13"/>
     </row>
     <row r="403">
-      <c r="F403" s="12"/>
-      <c r="G403" s="12"/>
-      <c r="H403" s="12"/>
+      <c r="F403" s="13"/>
+      <c r="G403" s="13"/>
+      <c r="H403" s="13"/>
     </row>
     <row r="404">
-      <c r="F404" s="12"/>
-      <c r="G404" s="12"/>
-      <c r="H404" s="12"/>
+      <c r="F404" s="13"/>
+      <c r="G404" s="13"/>
+      <c r="H404" s="13"/>
     </row>
     <row r="405">
-      <c r="F405" s="12"/>
-      <c r="G405" s="12"/>
-      <c r="H405" s="12"/>
+      <c r="F405" s="13"/>
+      <c r="G405" s="13"/>
+      <c r="H405" s="13"/>
     </row>
     <row r="406">
-      <c r="F406" s="12"/>
-      <c r="G406" s="12"/>
-      <c r="H406" s="12"/>
+      <c r="F406" s="13"/>
+      <c r="G406" s="13"/>
+      <c r="H406" s="13"/>
     </row>
     <row r="407">
-      <c r="F407" s="12"/>
-      <c r="G407" s="12"/>
-      <c r="H407" s="12"/>
+      <c r="F407" s="13"/>
+      <c r="G407" s="13"/>
+      <c r="H407" s="13"/>
     </row>
     <row r="408">
-      <c r="F408" s="12"/>
-      <c r="G408" s="12"/>
-      <c r="H408" s="12"/>
+      <c r="F408" s="13"/>
+      <c r="G408" s="13"/>
+      <c r="H408" s="13"/>
     </row>
     <row r="409">
-      <c r="F409" s="12"/>
-      <c r="G409" s="12"/>
-      <c r="H409" s="12"/>
+      <c r="F409" s="13"/>
+      <c r="G409" s="13"/>
+      <c r="H409" s="13"/>
     </row>
     <row r="410">
-      <c r="F410" s="12"/>
-      <c r="G410" s="12"/>
-      <c r="H410" s="12"/>
+      <c r="F410" s="13"/>
+      <c r="G410" s="13"/>
+      <c r="H410" s="13"/>
     </row>
     <row r="411">
-      <c r="F411" s="12"/>
-      <c r="G411" s="12"/>
-      <c r="H411" s="12"/>
+      <c r="F411" s="13"/>
+      <c r="G411" s="13"/>
+      <c r="H411" s="13"/>
     </row>
     <row r="412">
-      <c r="F412" s="12"/>
-      <c r="G412" s="12"/>
-      <c r="H412" s="12"/>
+      <c r="F412" s="13"/>
+      <c r="G412" s="13"/>
+      <c r="H412" s="13"/>
     </row>
     <row r="413">
-      <c r="F413" s="12"/>
-      <c r="G413" s="12"/>
-      <c r="H413" s="12"/>
+      <c r="F413" s="13"/>
+      <c r="G413" s="13"/>
+      <c r="H413" s="13"/>
     </row>
     <row r="414">
-      <c r="F414" s="12"/>
-      <c r="G414" s="12"/>
-      <c r="H414" s="12"/>
+      <c r="F414" s="13"/>
+      <c r="G414" s="13"/>
+      <c r="H414" s="13"/>
     </row>
     <row r="415">
-      <c r="F415" s="12"/>
-      <c r="G415" s="12"/>
-      <c r="H415" s="12"/>
+      <c r="F415" s="13"/>
+      <c r="G415" s="13"/>
+      <c r="H415" s="13"/>
     </row>
     <row r="416">
-      <c r="F416" s="12"/>
-      <c r="G416" s="12"/>
-      <c r="H416" s="12"/>
+      <c r="F416" s="13"/>
+      <c r="G416" s="13"/>
+      <c r="H416" s="13"/>
     </row>
     <row r="417">
-      <c r="F417" s="12"/>
-      <c r="G417" s="12"/>
-      <c r="H417" s="12"/>
+      <c r="F417" s="13"/>
+      <c r="G417" s="13"/>
+      <c r="H417" s="13"/>
     </row>
     <row r="418">
-      <c r="F418" s="12"/>
-      <c r="G418" s="12"/>
-      <c r="H418" s="12"/>
+      <c r="F418" s="13"/>
+      <c r="G418" s="13"/>
+      <c r="H418" s="13"/>
     </row>
     <row r="419">
-      <c r="F419" s="12"/>
-      <c r="G419" s="12"/>
-      <c r="H419" s="12"/>
+      <c r="F419" s="13"/>
+      <c r="G419" s="13"/>
+      <c r="H419" s="13"/>
     </row>
     <row r="420">
-      <c r="F420" s="12"/>
-      <c r="G420" s="12"/>
-      <c r="H420" s="12"/>
+      <c r="F420" s="13"/>
+      <c r="G420" s="13"/>
+      <c r="H420" s="13"/>
     </row>
     <row r="421">
-      <c r="F421" s="12"/>
-      <c r="G421" s="12"/>
-      <c r="H421" s="12"/>
+      <c r="F421" s="13"/>
+      <c r="G421" s="13"/>
+      <c r="H421" s="13"/>
     </row>
     <row r="422">
-      <c r="F422" s="12"/>
-      <c r="G422" s="12"/>
-      <c r="H422" s="12"/>
+      <c r="F422" s="13"/>
+      <c r="G422" s="13"/>
+      <c r="H422" s="13"/>
     </row>
     <row r="423">
-      <c r="F423" s="12"/>
-      <c r="G423" s="12"/>
-      <c r="H423" s="12"/>
+      <c r="F423" s="13"/>
+      <c r="G423" s="13"/>
+      <c r="H423" s="13"/>
     </row>
     <row r="424">
-      <c r="F424" s="12"/>
-      <c r="G424" s="12"/>
-      <c r="H424" s="12"/>
+      <c r="F424" s="13"/>
+      <c r="G424" s="13"/>
+      <c r="H424" s="13"/>
     </row>
     <row r="425">
-      <c r="F425" s="12"/>
-      <c r="G425" s="12"/>
-      <c r="H425" s="12"/>
+      <c r="F425" s="13"/>
+      <c r="G425" s="13"/>
+      <c r="H425" s="13"/>
     </row>
     <row r="426">
-      <c r="F426" s="12"/>
-      <c r="G426" s="12"/>
-      <c r="H426" s="12"/>
+      <c r="F426" s="13"/>
+      <c r="G426" s="13"/>
+      <c r="H426" s="13"/>
     </row>
     <row r="427">
-      <c r="F427" s="12"/>
-      <c r="G427" s="12"/>
-      <c r="H427" s="12"/>
+      <c r="F427" s="13"/>
+      <c r="G427" s="13"/>
+      <c r="H427" s="13"/>
     </row>
     <row r="428">
-      <c r="F428" s="12"/>
-      <c r="G428" s="12"/>
-      <c r="H428" s="12"/>
+      <c r="F428" s="13"/>
+      <c r="G428" s="13"/>
+      <c r="H428" s="13"/>
     </row>
     <row r="429">
-      <c r="F429" s="12"/>
-      <c r="G429" s="12"/>
-      <c r="H429" s="12"/>
+      <c r="F429" s="13"/>
+      <c r="G429" s="13"/>
+      <c r="H429" s="13"/>
     </row>
     <row r="430">
-      <c r="F430" s="12"/>
-      <c r="G430" s="12"/>
-      <c r="H430" s="12"/>
+      <c r="F430" s="13"/>
+      <c r="G430" s="13"/>
+      <c r="H430" s="13"/>
     </row>
     <row r="431">
-      <c r="F431" s="12"/>
-      <c r="G431" s="12"/>
-      <c r="H431" s="12"/>
+      <c r="F431" s="13"/>
+      <c r="G431" s="13"/>
+      <c r="H431" s="13"/>
     </row>
     <row r="432">
-      <c r="F432" s="12"/>
-      <c r="G432" s="12"/>
-      <c r="H432" s="12"/>
+      <c r="F432" s="13"/>
+      <c r="G432" s="13"/>
+      <c r="H432" s="13"/>
     </row>
     <row r="433">
-      <c r="F433" s="12"/>
-      <c r="G433" s="12"/>
-      <c r="H433" s="12"/>
+      <c r="F433" s="13"/>
+      <c r="G433" s="13"/>
+      <c r="H433" s="13"/>
     </row>
     <row r="434">
-      <c r="F434" s="12"/>
-      <c r="G434" s="12"/>
-      <c r="H434" s="12"/>
+      <c r="F434" s="13"/>
+      <c r="G434" s="13"/>
+      <c r="H434" s="13"/>
     </row>
     <row r="435">
-      <c r="F435" s="12"/>
-      <c r="G435" s="12"/>
-      <c r="H435" s="12"/>
+      <c r="F435" s="13"/>
+      <c r="G435" s="13"/>
+      <c r="H435" s="13"/>
     </row>
     <row r="436">
-      <c r="F436" s="12"/>
-      <c r="G436" s="12"/>
-      <c r="H436" s="12"/>
+      <c r="F436" s="13"/>
+      <c r="G436" s="13"/>
+      <c r="H436" s="13"/>
     </row>
     <row r="437">
-      <c r="F437" s="12"/>
-      <c r="G437" s="12"/>
-      <c r="H437" s="12"/>
+      <c r="F437" s="13"/>
+      <c r="G437" s="13"/>
+      <c r="H437" s="13"/>
     </row>
     <row r="438">
-      <c r="F438" s="12"/>
-      <c r="G438" s="12"/>
-      <c r="H438" s="12"/>
+      <c r="F438" s="13"/>
+      <c r="G438" s="13"/>
+      <c r="H438" s="13"/>
     </row>
     <row r="439">
-      <c r="F439" s="12"/>
-      <c r="G439" s="12"/>
-      <c r="H439" s="12"/>
+      <c r="F439" s="13"/>
+      <c r="G439" s="13"/>
+      <c r="H439" s="13"/>
     </row>
     <row r="440">
-      <c r="F440" s="12"/>
-      <c r="G440" s="12"/>
-      <c r="H440" s="12"/>
+      <c r="F440" s="13"/>
+      <c r="G440" s="13"/>
+      <c r="H440" s="13"/>
     </row>
     <row r="441">
-      <c r="F441" s="12"/>
-      <c r="G441" s="12"/>
-      <c r="H441" s="12"/>
+      <c r="F441" s="13"/>
+      <c r="G441" s="13"/>
+      <c r="H441" s="13"/>
     </row>
     <row r="442">
-      <c r="F442" s="12"/>
-      <c r="G442" s="12"/>
-      <c r="H442" s="12"/>
+      <c r="F442" s="13"/>
+      <c r="G442" s="13"/>
+      <c r="H442" s="13"/>
     </row>
     <row r="443">
-      <c r="F443" s="12"/>
-      <c r="G443" s="12"/>
-      <c r="H443" s="12"/>
+      <c r="F443" s="13"/>
+      <c r="G443" s="13"/>
+      <c r="H443" s="13"/>
     </row>
     <row r="444">
-      <c r="F444" s="12"/>
-      <c r="G444" s="12"/>
-      <c r="H444" s="12"/>
+      <c r="F444" s="13"/>
+      <c r="G444" s="13"/>
+      <c r="H444" s="13"/>
     </row>
     <row r="445">
-      <c r="F445" s="12"/>
-      <c r="G445" s="12"/>
-      <c r="H445" s="12"/>
+      <c r="F445" s="13"/>
+      <c r="G445" s="13"/>
+      <c r="H445" s="13"/>
     </row>
     <row r="446">
-      <c r="F446" s="12"/>
-      <c r="G446" s="12"/>
-      <c r="H446" s="12"/>
+      <c r="F446" s="13"/>
+      <c r="G446" s="13"/>
+      <c r="H446" s="13"/>
     </row>
     <row r="447">
-      <c r="F447" s="12"/>
-      <c r="G447" s="12"/>
-      <c r="H447" s="12"/>
+      <c r="F447" s="13"/>
+      <c r="G447" s="13"/>
+      <c r="H447" s="13"/>
     </row>
     <row r="448">
-      <c r="F448" s="12"/>
-      <c r="G448" s="12"/>
-      <c r="H448" s="12"/>
+      <c r="F448" s="13"/>
+      <c r="G448" s="13"/>
+      <c r="H448" s="13"/>
     </row>
     <row r="449">
-      <c r="F449" s="12"/>
-      <c r="G449" s="12"/>
-      <c r="H449" s="12"/>
+      <c r="F449" s="13"/>
+      <c r="G449" s="13"/>
+      <c r="H449" s="13"/>
     </row>
     <row r="450">
-      <c r="F450" s="12"/>
-      <c r="G450" s="12"/>
-      <c r="H450" s="12"/>
+      <c r="F450" s="13"/>
+      <c r="G450" s="13"/>
+      <c r="H450" s="13"/>
     </row>
     <row r="451">
-      <c r="F451" s="12"/>
-      <c r="G451" s="12"/>
-      <c r="H451" s="12"/>
+      <c r="F451" s="13"/>
+      <c r="G451" s="13"/>
+      <c r="H451" s="13"/>
     </row>
     <row r="452">
-      <c r="F452" s="12"/>
-      <c r="G452" s="12"/>
-      <c r="H452" s="12"/>
+      <c r="F452" s="13"/>
+      <c r="G452" s="13"/>
+      <c r="H452" s="13"/>
     </row>
     <row r="453">
-      <c r="F453" s="12"/>
-      <c r="G453" s="12"/>
-      <c r="H453" s="12"/>
+      <c r="F453" s="13"/>
+      <c r="G453" s="13"/>
+      <c r="H453" s="13"/>
     </row>
     <row r="454">
-      <c r="F454" s="12"/>
-      <c r="G454" s="12"/>
-      <c r="H454" s="12"/>
+      <c r="F454" s="13"/>
+      <c r="G454" s="13"/>
+      <c r="H454" s="13"/>
     </row>
     <row r="455">
-      <c r="F455" s="12"/>
-      <c r="G455" s="12"/>
-      <c r="H455" s="12"/>
+      <c r="F455" s="13"/>
+      <c r="G455" s="13"/>
+      <c r="H455" s="13"/>
     </row>
     <row r="456">
-      <c r="F456" s="12"/>
-      <c r="G456" s="12"/>
-      <c r="H456" s="12"/>
+      <c r="F456" s="13"/>
+      <c r="G456" s="13"/>
+      <c r="H456" s="13"/>
     </row>
     <row r="457">
-      <c r="F457" s="12"/>
-      <c r="G457" s="12"/>
-      <c r="H457" s="12"/>
+      <c r="F457" s="13"/>
+      <c r="G457" s="13"/>
+      <c r="H457" s="13"/>
     </row>
     <row r="458">
-      <c r="F458" s="12"/>
-      <c r="G458" s="12"/>
-      <c r="H458" s="12"/>
+      <c r="F458" s="13"/>
+      <c r="G458" s="13"/>
+      <c r="H458" s="13"/>
     </row>
     <row r="459">
-      <c r="F459" s="12"/>
-      <c r="G459" s="12"/>
-      <c r="H459" s="12"/>
+      <c r="F459" s="13"/>
+      <c r="G459" s="13"/>
+      <c r="H459" s="13"/>
     </row>
     <row r="460">
-      <c r="F460" s="12"/>
-      <c r="G460" s="12"/>
-      <c r="H460" s="12"/>
+      <c r="F460" s="13"/>
+      <c r="G460" s="13"/>
+      <c r="H460" s="13"/>
     </row>
     <row r="461">
-      <c r="F461" s="12"/>
-      <c r="G461" s="12"/>
-      <c r="H461" s="12"/>
+      <c r="F461" s="13"/>
+      <c r="G461" s="13"/>
+      <c r="H461" s="13"/>
     </row>
     <row r="462">
-      <c r="F462" s="12"/>
-      <c r="G462" s="12"/>
-      <c r="H462" s="12"/>
+      <c r="F462" s="13"/>
+      <c r="G462" s="13"/>
+      <c r="H462" s="13"/>
     </row>
     <row r="463">
-      <c r="F463" s="12"/>
-      <c r="G463" s="12"/>
-      <c r="H463" s="12"/>
+      <c r="F463" s="13"/>
+      <c r="G463" s="13"/>
+      <c r="H463" s="13"/>
     </row>
     <row r="464">
-      <c r="F464" s="12"/>
-      <c r="G464" s="12"/>
-      <c r="H464" s="12"/>
+      <c r="F464" s="13"/>
+      <c r="G464" s="13"/>
+      <c r="H464" s="13"/>
     </row>
     <row r="465">
-      <c r="F465" s="12"/>
-      <c r="G465" s="12"/>
-      <c r="H465" s="12"/>
+      <c r="F465" s="13"/>
+      <c r="G465" s="13"/>
+      <c r="H465" s="13"/>
     </row>
     <row r="466">
-      <c r="F466" s="12"/>
-      <c r="G466" s="12"/>
-      <c r="H466" s="12"/>
+      <c r="F466" s="13"/>
+      <c r="G466" s="13"/>
+      <c r="H466" s="13"/>
     </row>
     <row r="467">
-      <c r="F467" s="12"/>
-      <c r="G467" s="12"/>
-      <c r="H467" s="12"/>
+      <c r="F467" s="13"/>
+      <c r="G467" s="13"/>
+      <c r="H467" s="13"/>
     </row>
     <row r="468">
-      <c r="F468" s="12"/>
-      <c r="G468" s="12"/>
-      <c r="H468" s="12"/>
+      <c r="F468" s="13"/>
+      <c r="G468" s="13"/>
+      <c r="H468" s="13"/>
     </row>
     <row r="469">
-      <c r="F469" s="12"/>
-      <c r="G469" s="12"/>
-      <c r="H469" s="12"/>
+      <c r="F469" s="13"/>
+      <c r="G469" s="13"/>
+      <c r="H469" s="13"/>
     </row>
     <row r="470">
-      <c r="F470" s="12"/>
-      <c r="G470" s="12"/>
-      <c r="H470" s="12"/>
+      <c r="F470" s="13"/>
+      <c r="G470" s="13"/>
+      <c r="H470" s="13"/>
     </row>
     <row r="471">
-      <c r="F471" s="12"/>
-      <c r="G471" s="12"/>
-      <c r="H471" s="12"/>
+      <c r="F471" s="13"/>
+      <c r="G471" s="13"/>
+      <c r="H471" s="13"/>
     </row>
     <row r="472">
-      <c r="F472" s="12"/>
-      <c r="G472" s="12"/>
-      <c r="H472" s="12"/>
+      <c r="F472" s="13"/>
+      <c r="G472" s="13"/>
+      <c r="H472" s="13"/>
     </row>
     <row r="473">
-      <c r="F473" s="12"/>
-      <c r="G473" s="12"/>
-      <c r="H473" s="12"/>
+      <c r="F473" s="13"/>
+      <c r="G473" s="13"/>
+      <c r="H473" s="13"/>
     </row>
     <row r="474">
-      <c r="F474" s="12"/>
-      <c r="G474" s="12"/>
-      <c r="H474" s="12"/>
+      <c r="F474" s="13"/>
+      <c r="G474" s="13"/>
+      <c r="H474" s="13"/>
     </row>
     <row r="475">
-      <c r="F475" s="12"/>
-      <c r="G475" s="12"/>
-      <c r="H475" s="12"/>
+      <c r="F475" s="13"/>
+      <c r="G475" s="13"/>
+      <c r="H475" s="13"/>
     </row>
     <row r="476">
-      <c r="F476" s="12"/>
-      <c r="G476" s="12"/>
-      <c r="H476" s="12"/>
+      <c r="F476" s="13"/>
+      <c r="G476" s="13"/>
+      <c r="H476" s="13"/>
     </row>
     <row r="477">
-      <c r="F477" s="12"/>
-      <c r="G477" s="12"/>
-      <c r="H477" s="12"/>
+      <c r="F477" s="13"/>
+      <c r="G477" s="13"/>
+      <c r="H477" s="13"/>
     </row>
     <row r="478">
-      <c r="F478" s="12"/>
-      <c r="G478" s="12"/>
-      <c r="H478" s="12"/>
+      <c r="F478" s="13"/>
+      <c r="G478" s="13"/>
+      <c r="H478" s="13"/>
     </row>
     <row r="479">
-      <c r="F479" s="12"/>
-      <c r="G479" s="12"/>
-      <c r="H479" s="12"/>
+      <c r="F479" s="13"/>
+      <c r="G479" s="13"/>
+      <c r="H479" s="13"/>
     </row>
     <row r="480">
-      <c r="F480" s="12"/>
-      <c r="G480" s="12"/>
-      <c r="H480" s="12"/>
+      <c r="F480" s="13"/>
+      <c r="G480" s="13"/>
+      <c r="H480" s="13"/>
     </row>
     <row r="481">
-      <c r="F481" s="12"/>
-      <c r="G481" s="12"/>
-      <c r="H481" s="12"/>
+      <c r="F481" s="13"/>
+      <c r="G481" s="13"/>
+      <c r="H481" s="13"/>
     </row>
     <row r="482">
-      <c r="F482" s="12"/>
-      <c r="G482" s="12"/>
-      <c r="H482" s="12"/>
+      <c r="F482" s="13"/>
+      <c r="G482" s="13"/>
+      <c r="H482" s="13"/>
     </row>
     <row r="483">
-      <c r="F483" s="12"/>
-      <c r="G483" s="12"/>
-      <c r="H483" s="12"/>
+      <c r="F483" s="13"/>
+      <c r="G483" s="13"/>
+      <c r="H483" s="13"/>
     </row>
     <row r="484">
-      <c r="F484" s="12"/>
-      <c r="G484" s="12"/>
-      <c r="H484" s="12"/>
+      <c r="F484" s="13"/>
+      <c r="G484" s="13"/>
+      <c r="H484" s="13"/>
     </row>
     <row r="485">
-      <c r="F485" s="12"/>
-      <c r="G485" s="12"/>
-      <c r="H485" s="12"/>
+      <c r="F485" s="13"/>
+      <c r="G485" s="13"/>
+      <c r="H485" s="13"/>
     </row>
     <row r="486">
-      <c r="F486" s="12"/>
-      <c r="G486" s="12"/>
-      <c r="H486" s="12"/>
+      <c r="F486" s="13"/>
+      <c r="G486" s="13"/>
+      <c r="H486" s="13"/>
     </row>
     <row r="487">
-      <c r="F487" s="12"/>
-      <c r="G487" s="12"/>
-      <c r="H487" s="12"/>
+      <c r="F487" s="13"/>
+      <c r="G487" s="13"/>
+      <c r="H487" s="13"/>
     </row>
     <row r="488">
-      <c r="F488" s="12"/>
-      <c r="G488" s="12"/>
-      <c r="H488" s="12"/>
+      <c r="F488" s="13"/>
+      <c r="G488" s="13"/>
+      <c r="H488" s="13"/>
     </row>
     <row r="489">
-      <c r="F489" s="12"/>
-      <c r="G489" s="12"/>
-      <c r="H489" s="12"/>
+      <c r="F489" s="13"/>
+      <c r="G489" s="13"/>
+      <c r="H489" s="13"/>
     </row>
     <row r="490">
-      <c r="F490" s="12"/>
-      <c r="G490" s="12"/>
-      <c r="H490" s="12"/>
+      <c r="F490" s="13"/>
+      <c r="G490" s="13"/>
+      <c r="H490" s="13"/>
     </row>
     <row r="491">
-      <c r="F491" s="12"/>
-      <c r="G491" s="12"/>
-      <c r="H491" s="12"/>
+      <c r="F491" s="13"/>
+      <c r="G491" s="13"/>
+      <c r="H491" s="13"/>
     </row>
     <row r="492">
-      <c r="F492" s="12"/>
-      <c r="G492" s="12"/>
-      <c r="H492" s="12"/>
+      <c r="F492" s="13"/>
+      <c r="G492" s="13"/>
+      <c r="H492" s="13"/>
     </row>
     <row r="493">
-      <c r="F493" s="12"/>
-      <c r="G493" s="12"/>
-      <c r="H493" s="12"/>
+      <c r="F493" s="13"/>
+      <c r="G493" s="13"/>
+      <c r="H493" s="13"/>
     </row>
     <row r="494">
-      <c r="F494" s="12"/>
-      <c r="G494" s="12"/>
-      <c r="H494" s="12"/>
+      <c r="F494" s="13"/>
+      <c r="G494" s="13"/>
+      <c r="H494" s="13"/>
     </row>
     <row r="495">
-      <c r="F495" s="12"/>
-      <c r="G495" s="12"/>
-      <c r="H495" s="12"/>
+      <c r="F495" s="13"/>
+      <c r="G495" s="13"/>
+      <c r="H495" s="13"/>
     </row>
     <row r="496">
-      <c r="F496" s="12"/>
-      <c r="G496" s="12"/>
-      <c r="H496" s="12"/>
+      <c r="F496" s="13"/>
+      <c r="G496" s="13"/>
+      <c r="H496" s="13"/>
     </row>
     <row r="497">
-      <c r="F497" s="12"/>
-      <c r="G497" s="12"/>
-      <c r="H497" s="12"/>
+      <c r="F497" s="13"/>
+      <c r="G497" s="13"/>
+      <c r="H497" s="13"/>
     </row>
     <row r="498">
-      <c r="F498" s="12"/>
-      <c r="G498" s="12"/>
-      <c r="H498" s="12"/>
+      <c r="F498" s="13"/>
+      <c r="G498" s="13"/>
+      <c r="H498" s="13"/>
     </row>
     <row r="499">
-      <c r="F499" s="12"/>
-      <c r="G499" s="12"/>
-      <c r="H499" s="12"/>
+      <c r="F499" s="13"/>
+      <c r="G499" s="13"/>
+      <c r="H499" s="13"/>
     </row>
     <row r="500">
-      <c r="F500" s="12"/>
-      <c r="G500" s="12"/>
-      <c r="H500" s="12"/>
+      <c r="F500" s="13"/>
+      <c r="G500" s="13"/>
+      <c r="H500" s="13"/>
     </row>
     <row r="501">
-      <c r="F501" s="12"/>
-      <c r="G501" s="12"/>
-      <c r="H501" s="12"/>
+      <c r="F501" s="13"/>
+      <c r="G501" s="13"/>
+      <c r="H501" s="13"/>
     </row>
     <row r="502">
-      <c r="F502" s="12"/>
-      <c r="G502" s="12"/>
-      <c r="H502" s="12"/>
+      <c r="F502" s="13"/>
+      <c r="G502" s="13"/>
+      <c r="H502" s="13"/>
     </row>
     <row r="503">
-      <c r="F503" s="12"/>
-      <c r="G503" s="12"/>
-      <c r="H503" s="12"/>
+      <c r="F503" s="13"/>
+      <c r="G503" s="13"/>
+      <c r="H503" s="13"/>
     </row>
     <row r="504">
-      <c r="F504" s="12"/>
-      <c r="G504" s="12"/>
-      <c r="H504" s="12"/>
+      <c r="F504" s="13"/>
+      <c r="G504" s="13"/>
+      <c r="H504" s="13"/>
     </row>
     <row r="505">
-      <c r="F505" s="12"/>
-      <c r="G505" s="12"/>
-      <c r="H505" s="12"/>
+      <c r="F505" s="13"/>
+      <c r="G505" s="13"/>
+      <c r="H505" s="13"/>
     </row>
     <row r="506">
-      <c r="F506" s="12"/>
-      <c r="G506" s="12"/>
-      <c r="H506" s="12"/>
+      <c r="F506" s="13"/>
+      <c r="G506" s="13"/>
+      <c r="H506" s="13"/>
     </row>
     <row r="507">
-      <c r="F507" s="12"/>
-      <c r="G507" s="12"/>
-      <c r="H507" s="12"/>
+      <c r="F507" s="13"/>
+      <c r="G507" s="13"/>
+      <c r="H507" s="13"/>
     </row>
     <row r="508">
-      <c r="F508" s="12"/>
-      <c r="G508" s="12"/>
-      <c r="H508" s="12"/>
+      <c r="F508" s="13"/>
+      <c r="G508" s="13"/>
+      <c r="H508" s="13"/>
     </row>
     <row r="509">
-      <c r="F509" s="12"/>
-      <c r="G509" s="12"/>
-      <c r="H509" s="12"/>
+      <c r="F509" s="13"/>
+      <c r="G509" s="13"/>
+      <c r="H509" s="13"/>
     </row>
     <row r="510">
-      <c r="F510" s="12"/>
-      <c r="G510" s="12"/>
-      <c r="H510" s="12"/>
+      <c r="F510" s="13"/>
+      <c r="G510" s="13"/>
+      <c r="H510" s="13"/>
     </row>
     <row r="511">
-      <c r="F511" s="12"/>
-      <c r="G511" s="12"/>
-      <c r="H511" s="12"/>
+      <c r="F511" s="13"/>
+      <c r="G511" s="13"/>
+      <c r="H511" s="13"/>
     </row>
     <row r="512">
-      <c r="F512" s="12"/>
-      <c r="G512" s="12"/>
-      <c r="H512" s="12"/>
+      <c r="F512" s="13"/>
+      <c r="G512" s="13"/>
+      <c r="H512" s="13"/>
     </row>
     <row r="513">
-      <c r="F513" s="12"/>
-      <c r="G513" s="12"/>
-      <c r="H513" s="12"/>
+      <c r="F513" s="13"/>
+      <c r="G513" s="13"/>
+      <c r="H513" s="13"/>
     </row>
     <row r="514">
-      <c r="F514" s="12"/>
-      <c r="G514" s="12"/>
-      <c r="H514" s="12"/>
+      <c r="F514" s="13"/>
+      <c r="G514" s="13"/>
+      <c r="H514" s="13"/>
     </row>
     <row r="515">
-      <c r="F515" s="12"/>
-      <c r="G515" s="12"/>
-      <c r="H515" s="12"/>
+      <c r="F515" s="13"/>
+      <c r="G515" s="13"/>
+      <c r="H515" s="13"/>
     </row>
     <row r="516">
-      <c r="F516" s="12"/>
-      <c r="G516" s="12"/>
-      <c r="H516" s="12"/>
+      <c r="F516" s="13"/>
+      <c r="G516" s="13"/>
+      <c r="H516" s="13"/>
     </row>
     <row r="517">
-      <c r="F517" s="12"/>
-      <c r="G517" s="12"/>
-      <c r="H517" s="12"/>
+      <c r="F517" s="13"/>
+      <c r="G517" s="13"/>
+      <c r="H517" s="13"/>
     </row>
     <row r="518">
-      <c r="F518" s="12"/>
-      <c r="G518" s="12"/>
-      <c r="H518" s="12"/>
+      <c r="F518" s="13"/>
+      <c r="G518" s="13"/>
+      <c r="H518" s="13"/>
     </row>
     <row r="519">
-      <c r="F519" s="12"/>
-      <c r="G519" s="12"/>
-      <c r="H519" s="12"/>
+      <c r="F519" s="13"/>
+      <c r="G519" s="13"/>
+      <c r="H519" s="13"/>
     </row>
     <row r="520">
-      <c r="F520" s="12"/>
-      <c r="G520" s="12"/>
-      <c r="H520" s="12"/>
+      <c r="F520" s="13"/>
+      <c r="G520" s="13"/>
+      <c r="H520" s="13"/>
     </row>
     <row r="521">
-      <c r="F521" s="12"/>
-      <c r="G521" s="12"/>
-      <c r="H521" s="12"/>
+      <c r="F521" s="13"/>
+      <c r="G521" s="13"/>
+      <c r="H521" s="13"/>
     </row>
     <row r="522">
-      <c r="F522" s="12"/>
-      <c r="G522" s="12"/>
-      <c r="H522" s="12"/>
+      <c r="F522" s="13"/>
+      <c r="G522" s="13"/>
+      <c r="H522" s="13"/>
     </row>
     <row r="523">
-      <c r="F523" s="12"/>
-      <c r="G523" s="12"/>
-      <c r="H523" s="12"/>
+      <c r="F523" s="13"/>
+      <c r="G523" s="13"/>
+      <c r="H523" s="13"/>
     </row>
     <row r="524">
-      <c r="F524" s="12"/>
-      <c r="G524" s="12"/>
-      <c r="H524" s="12"/>
+      <c r="F524" s="13"/>
+      <c r="G524" s="13"/>
+      <c r="H524" s="13"/>
     </row>
     <row r="525">
-      <c r="F525" s="12"/>
-      <c r="G525" s="12"/>
-      <c r="H525" s="12"/>
+      <c r="F525" s="13"/>
+      <c r="G525" s="13"/>
+      <c r="H525" s="13"/>
     </row>
     <row r="526">
-      <c r="F526" s="12"/>
-      <c r="G526" s="12"/>
-      <c r="H526" s="12"/>
+      <c r="F526" s="13"/>
+      <c r="G526" s="13"/>
+      <c r="H526" s="13"/>
     </row>
     <row r="527">
-      <c r="F527" s="12"/>
-      <c r="G527" s="12"/>
-      <c r="H527" s="12"/>
+      <c r="F527" s="13"/>
+      <c r="G527" s="13"/>
+      <c r="H527" s="13"/>
     </row>
     <row r="528">
-      <c r="F528" s="12"/>
-      <c r="G528" s="12"/>
-      <c r="H528" s="12"/>
+      <c r="F528" s="13"/>
+      <c r="G528" s="13"/>
+      <c r="H528" s="13"/>
     </row>
     <row r="529">
-      <c r="F529" s="12"/>
-      <c r="G529" s="12"/>
-      <c r="H529" s="12"/>
+      <c r="F529" s="13"/>
+      <c r="G529" s="13"/>
+      <c r="H529" s="13"/>
     </row>
     <row r="530">
-      <c r="F530" s="12"/>
-      <c r="G530" s="12"/>
-      <c r="H530" s="12"/>
+      <c r="F530" s="13"/>
+      <c r="G530" s="13"/>
+      <c r="H530" s="13"/>
     </row>
     <row r="531">
-      <c r="F531" s="12"/>
-      <c r="G531" s="12"/>
-      <c r="H531" s="12"/>
+      <c r="F531" s="13"/>
+      <c r="G531" s="13"/>
+      <c r="H531" s="13"/>
     </row>
     <row r="532">
-      <c r="F532" s="12"/>
-      <c r="G532" s="12"/>
-      <c r="H532" s="12"/>
+      <c r="F532" s="13"/>
+      <c r="G532" s="13"/>
+      <c r="H532" s="13"/>
     </row>
     <row r="533">
-      <c r="F533" s="12"/>
-      <c r="G533" s="12"/>
-      <c r="H533" s="12"/>
+      <c r="F533" s="13"/>
+      <c r="G533" s="13"/>
+      <c r="H533" s="13"/>
     </row>
     <row r="534">
-      <c r="F534" s="12"/>
-      <c r="G534" s="12"/>
-      <c r="H534" s="12"/>
+      <c r="F534" s="13"/>
+      <c r="G534" s="13"/>
+      <c r="H534" s="13"/>
     </row>
     <row r="535">
-      <c r="F535" s="12"/>
-      <c r="G535" s="12"/>
-      <c r="H535" s="12"/>
+      <c r="F535" s="13"/>
+      <c r="G535" s="13"/>
+      <c r="H535" s="13"/>
     </row>
     <row r="536">
-      <c r="F536" s="12"/>
-      <c r="G536" s="12"/>
-      <c r="H536" s="12"/>
+      <c r="F536" s="13"/>
+      <c r="G536" s="13"/>
+      <c r="H536" s="13"/>
     </row>
     <row r="537">
-      <c r="F537" s="12"/>
-      <c r="G537" s="12"/>
-      <c r="H537" s="12"/>
+      <c r="F537" s="13"/>
+      <c r="G537" s="13"/>
+      <c r="H537" s="13"/>
     </row>
     <row r="538">
-      <c r="F538" s="12"/>
-      <c r="G538" s="12"/>
-      <c r="H538" s="12"/>
+      <c r="F538" s="13"/>
+      <c r="G538" s="13"/>
+      <c r="H538" s="13"/>
     </row>
     <row r="539">
-      <c r="F539" s="12"/>
-      <c r="G539" s="12"/>
-      <c r="H539" s="12"/>
+      <c r="F539" s="13"/>
+      <c r="G539" s="13"/>
+      <c r="H539" s="13"/>
     </row>
     <row r="540">
-      <c r="F540" s="12"/>
-      <c r="G540" s="12"/>
-      <c r="H540" s="12"/>
+      <c r="F540" s="13"/>
+      <c r="G540" s="13"/>
+      <c r="H540" s="13"/>
     </row>
     <row r="541">
-      <c r="F541" s="12"/>
-      <c r="G541" s="12"/>
-      <c r="H541" s="12"/>
+      <c r="F541" s="13"/>
+      <c r="G541" s="13"/>
+      <c r="H541" s="13"/>
     </row>
     <row r="542">
-      <c r="F542" s="12"/>
-      <c r="G542" s="12"/>
-      <c r="H542" s="12"/>
+      <c r="F542" s="13"/>
+      <c r="G542" s="13"/>
+      <c r="H542" s="13"/>
     </row>
     <row r="543">
-      <c r="F543" s="12"/>
-      <c r="G543" s="12"/>
-      <c r="H543" s="12"/>
+      <c r="F543" s="13"/>
+      <c r="G543" s="13"/>
+      <c r="H543" s="13"/>
     </row>
     <row r="544">
-      <c r="F544" s="12"/>
-      <c r="G544" s="12"/>
-      <c r="H544" s="12"/>
+      <c r="F544" s="13"/>
+      <c r="G544" s="13"/>
+      <c r="H544" s="13"/>
     </row>
     <row r="545">
-      <c r="F545" s="12"/>
-      <c r="G545" s="12"/>
-      <c r="H545" s="12"/>
+      <c r="F545" s="13"/>
+      <c r="G545" s="13"/>
+      <c r="H545" s="13"/>
     </row>
     <row r="546">
-      <c r="F546" s="12"/>
-      <c r="G546" s="12"/>
-      <c r="H546" s="12"/>
+      <c r="F546" s="13"/>
+      <c r="G546" s="13"/>
+      <c r="H546" s="13"/>
     </row>
     <row r="547">
-      <c r="F547" s="12"/>
-      <c r="G547" s="12"/>
-      <c r="H547" s="12"/>
+      <c r="F547" s="13"/>
+      <c r="G547" s="13"/>
+      <c r="H547" s="13"/>
     </row>
     <row r="548">
-      <c r="F548" s="12"/>
-      <c r="G548" s="12"/>
-      <c r="H548" s="12"/>
+      <c r="F548" s="13"/>
+      <c r="G548" s="13"/>
+      <c r="H548" s="13"/>
     </row>
     <row r="549">
-      <c r="F549" s="12"/>
-      <c r="G549" s="12"/>
-      <c r="H549" s="12"/>
+      <c r="F549" s="13"/>
+      <c r="G549" s="13"/>
+      <c r="H549" s="13"/>
     </row>
     <row r="550">
-      <c r="F550" s="12"/>
-      <c r="G550" s="12"/>
-      <c r="H550" s="12"/>
+      <c r="F550" s="13"/>
+      <c r="G550" s="13"/>
+      <c r="H550" s="13"/>
     </row>
     <row r="551">
-      <c r="F551" s="12"/>
-      <c r="G551" s="12"/>
-      <c r="H551" s="12"/>
+      <c r="F551" s="13"/>
+      <c r="G551" s="13"/>
+      <c r="H551" s="13"/>
     </row>
     <row r="552">
-      <c r="F552" s="12"/>
-      <c r="G552" s="12"/>
-      <c r="H552" s="12"/>
+      <c r="F552" s="13"/>
+      <c r="G552" s="13"/>
+      <c r="H552" s="13"/>
     </row>
     <row r="553">
-      <c r="F553" s="12"/>
-      <c r="G553" s="12"/>
-      <c r="H553" s="12"/>
+      <c r="F553" s="13"/>
+      <c r="G553" s="13"/>
+      <c r="H553" s="13"/>
     </row>
     <row r="554">
-      <c r="F554" s="12"/>
-      <c r="G554" s="12"/>
-      <c r="H554" s="12"/>
+      <c r="F554" s="13"/>
+      <c r="G554" s="13"/>
+      <c r="H554" s="13"/>
     </row>
     <row r="555">
-      <c r="F555" s="12"/>
-      <c r="G555" s="12"/>
-      <c r="H555" s="12"/>
+      <c r="F555" s="13"/>
+      <c r="G555" s="13"/>
+      <c r="H555" s="13"/>
     </row>
     <row r="556">
-      <c r="F556" s="12"/>
-      <c r="G556" s="12"/>
-      <c r="H556" s="12"/>
+      <c r="F556" s="13"/>
+      <c r="G556" s="13"/>
+      <c r="H556" s="13"/>
     </row>
     <row r="557">
-      <c r="F557" s="12"/>
-      <c r="G557" s="12"/>
-      <c r="H557" s="12"/>
+      <c r="F557" s="13"/>
+      <c r="G557" s="13"/>
+      <c r="H557" s="13"/>
     </row>
     <row r="558">
-      <c r="F558" s="12"/>
-      <c r="G558" s="12"/>
-      <c r="H558" s="12"/>
+      <c r="F558" s="13"/>
+      <c r="G558" s="13"/>
+      <c r="H558" s="13"/>
     </row>
     <row r="559">
-      <c r="F559" s="12"/>
-      <c r="G559" s="12"/>
-      <c r="H559" s="12"/>
+      <c r="F559" s="13"/>
+      <c r="G559" s="13"/>
+      <c r="H559" s="13"/>
     </row>
     <row r="560">
-      <c r="F560" s="12"/>
-      <c r="G560" s="12"/>
-      <c r="H560" s="12"/>
+      <c r="F560" s="13"/>
+      <c r="G560" s="13"/>
+      <c r="H560" s="13"/>
     </row>
     <row r="561">
-      <c r="F561" s="12"/>
-      <c r="G561" s="12"/>
-      <c r="H561" s="12"/>
+      <c r="F561" s="13"/>
+      <c r="G561" s="13"/>
+      <c r="H561" s="13"/>
     </row>
     <row r="562">
-      <c r="F562" s="12"/>
-      <c r="G562" s="12"/>
-      <c r="H562" s="12"/>
+      <c r="F562" s="13"/>
+      <c r="G562" s="13"/>
+      <c r="H562" s="13"/>
     </row>
     <row r="563">
-      <c r="F563" s="12"/>
-      <c r="G563" s="12"/>
-      <c r="H563" s="12"/>
+      <c r="F563" s="13"/>
+      <c r="G563" s="13"/>
+      <c r="H563" s="13"/>
     </row>
     <row r="564">
-      <c r="F564" s="12"/>
-      <c r="G564" s="12"/>
-      <c r="H564" s="12"/>
+      <c r="F564" s="13"/>
+      <c r="G564" s="13"/>
+      <c r="H564" s="13"/>
     </row>
     <row r="565">
-      <c r="F565" s="12"/>
-      <c r="G565" s="12"/>
-      <c r="H565" s="12"/>
+      <c r="F565" s="13"/>
+      <c r="G565" s="13"/>
+      <c r="H565" s="13"/>
     </row>
     <row r="566">
-      <c r="F566" s="12"/>
-      <c r="G566" s="12"/>
-      <c r="H566" s="12"/>
+      <c r="F566" s="13"/>
+      <c r="G566" s="13"/>
+      <c r="H566" s="13"/>
     </row>
     <row r="567">
-      <c r="F567" s="12"/>
-      <c r="G567" s="12"/>
-      <c r="H567" s="12"/>
+      <c r="F567" s="13"/>
+      <c r="G567" s="13"/>
+      <c r="H567" s="13"/>
     </row>
     <row r="568">
-      <c r="F568" s="12"/>
-      <c r="G568" s="12"/>
-      <c r="H568" s="12"/>
+      <c r="F568" s="13"/>
+      <c r="G568" s="13"/>
+      <c r="H568" s="13"/>
     </row>
     <row r="569">
-      <c r="F569" s="12"/>
-      <c r="G569" s="12"/>
-      <c r="H569" s="12"/>
+      <c r="F569" s="13"/>
+      <c r="G569" s="13"/>
+      <c r="H569" s="13"/>
     </row>
     <row r="570">
-      <c r="F570" s="12"/>
-      <c r="G570" s="12"/>
-      <c r="H570" s="12"/>
+      <c r="F570" s="13"/>
+      <c r="G570" s="13"/>
+      <c r="H570" s="13"/>
     </row>
     <row r="571">
-      <c r="F571" s="12"/>
-      <c r="G571" s="12"/>
-      <c r="H571" s="12"/>
+      <c r="F571" s="13"/>
+      <c r="G571" s="13"/>
+      <c r="H571" s="13"/>
     </row>
     <row r="572">
-      <c r="F572" s="12"/>
-      <c r="G572" s="12"/>
-      <c r="H572" s="12"/>
+      <c r="F572" s="13"/>
+      <c r="G572" s="13"/>
+      <c r="H572" s="13"/>
     </row>
     <row r="573">
-      <c r="F573" s="12"/>
-      <c r="G573" s="12"/>
-      <c r="H573" s="12"/>
+      <c r="F573" s="13"/>
+      <c r="G573" s="13"/>
+      <c r="H573" s="13"/>
     </row>
     <row r="574">
-      <c r="F574" s="12"/>
-      <c r="G574" s="12"/>
-      <c r="H574" s="12"/>
+      <c r="F574" s="13"/>
+      <c r="G574" s="13"/>
+      <c r="H574" s="13"/>
     </row>
     <row r="575">
-      <c r="F575" s="12"/>
-      <c r="G575" s="12"/>
-      <c r="H575" s="12"/>
+      <c r="F575" s="13"/>
+      <c r="G575" s="13"/>
+      <c r="H575" s="13"/>
     </row>
     <row r="576">
-      <c r="F576" s="12"/>
-      <c r="G576" s="12"/>
-      <c r="H576" s="12"/>
+      <c r="F576" s="13"/>
+      <c r="G576" s="13"/>
+      <c r="H576" s="13"/>
     </row>
     <row r="577">
-      <c r="F577" s="12"/>
-      <c r="G577" s="12"/>
-      <c r="H577" s="12"/>
+      <c r="F577" s="13"/>
+      <c r="G577" s="13"/>
+      <c r="H577" s="13"/>
     </row>
     <row r="578">
-      <c r="F578" s="12"/>
-      <c r="G578" s="12"/>
-      <c r="H578" s="12"/>
+      <c r="F578" s="13"/>
+      <c r="G578" s="13"/>
+      <c r="H578" s="13"/>
     </row>
     <row r="579">
-      <c r="F579" s="12"/>
-      <c r="G579" s="12"/>
-      <c r="H579" s="12"/>
+      <c r="F579" s="13"/>
+      <c r="G579" s="13"/>
+      <c r="H579" s="13"/>
     </row>
     <row r="580">
-      <c r="F580" s="12"/>
-      <c r="G580" s="12"/>
-      <c r="H580" s="12"/>
+      <c r="F580" s="13"/>
+      <c r="G580" s="13"/>
+      <c r="H580" s="13"/>
     </row>
     <row r="581">
-      <c r="F581" s="12"/>
-      <c r="G581" s="12"/>
-      <c r="H581" s="12"/>
+      <c r="F581" s="13"/>
+      <c r="G581" s="13"/>
+      <c r="H581" s="13"/>
     </row>
     <row r="582">
-      <c r="F582" s="12"/>
-      <c r="G582" s="12"/>
-      <c r="H582" s="12"/>
+      <c r="F582" s="13"/>
+      <c r="G582" s="13"/>
+      <c r="H582" s="13"/>
     </row>
     <row r="583">
-      <c r="F583" s="12"/>
-      <c r="G583" s="12"/>
-      <c r="H583" s="12"/>
+      <c r="F583" s="13"/>
+      <c r="G583" s="13"/>
+      <c r="H583" s="13"/>
     </row>
     <row r="584">
-      <c r="F584" s="12"/>
-      <c r="G584" s="12"/>
-      <c r="H584" s="12"/>
+      <c r="F584" s="13"/>
+      <c r="G584" s="13"/>
+      <c r="H584" s="13"/>
     </row>
     <row r="585">
-      <c r="F585" s="12"/>
-      <c r="G585" s="12"/>
-      <c r="H585" s="12"/>
+      <c r="F585" s="13"/>
+      <c r="G585" s="13"/>
+      <c r="H585" s="13"/>
     </row>
     <row r="586">
-      <c r="F586" s="12"/>
-      <c r="G586" s="12"/>
-      <c r="H586" s="12"/>
+      <c r="F586" s="13"/>
+      <c r="G586" s="13"/>
+      <c r="H586" s="13"/>
     </row>
     <row r="587">
-      <c r="F587" s="12"/>
-      <c r="G587" s="12"/>
-      <c r="H587" s="12"/>
+      <c r="F587" s="13"/>
+      <c r="G587" s="13"/>
+      <c r="H587" s="13"/>
     </row>
     <row r="588">
-      <c r="F588" s="12"/>
-      <c r="G588" s="12"/>
-      <c r="H588" s="12"/>
+      <c r="F588" s="13"/>
+      <c r="G588" s="13"/>
+      <c r="H588" s="13"/>
     </row>
     <row r="589">
-      <c r="F589" s="12"/>
-      <c r="G589" s="12"/>
-      <c r="H589" s="12"/>
+      <c r="F589" s="13"/>
+      <c r="G589" s="13"/>
+      <c r="H589" s="13"/>
     </row>
     <row r="590">
-      <c r="F590" s="12"/>
-      <c r="G590" s="12"/>
-      <c r="H590" s="12"/>
+      <c r="F590" s="13"/>
+      <c r="G590" s="13"/>
+      <c r="H590" s="13"/>
     </row>
     <row r="591">
-      <c r="F591" s="12"/>
-      <c r="G591" s="12"/>
-      <c r="H591" s="12"/>
+      <c r="F591" s="13"/>
+      <c r="G591" s="13"/>
+      <c r="H591" s="13"/>
     </row>
     <row r="592">
-      <c r="F592" s="12"/>
-      <c r="G592" s="12"/>
-      <c r="H592" s="12"/>
+      <c r="F592" s="13"/>
+      <c r="G592" s="13"/>
+      <c r="H592" s="13"/>
     </row>
     <row r="593">
-      <c r="F593" s="12"/>
-      <c r="G593" s="12"/>
-      <c r="H593" s="12"/>
+      <c r="F593" s="13"/>
+      <c r="G593" s="13"/>
+      <c r="H593" s="13"/>
     </row>
     <row r="594">
-      <c r="F594" s="12"/>
-      <c r="G594" s="12"/>
-      <c r="H594" s="12"/>
+      <c r="F594" s="13"/>
+      <c r="G594" s="13"/>
+      <c r="H594" s="13"/>
     </row>
     <row r="595">
-      <c r="F595" s="12"/>
-      <c r="G595" s="12"/>
-      <c r="H595" s="12"/>
+      <c r="F595" s="13"/>
+      <c r="G595" s="13"/>
+      <c r="H595" s="13"/>
     </row>
     <row r="596">
-      <c r="F596" s="12"/>
-      <c r="G596" s="12"/>
-      <c r="H596" s="12"/>
+      <c r="F596" s="13"/>
+      <c r="G596" s="13"/>
+      <c r="H596" s="13"/>
     </row>
     <row r="597">
-      <c r="F597" s="12"/>
-      <c r="G597" s="12"/>
-      <c r="H597" s="12"/>
+      <c r="F597" s="13"/>
+      <c r="G597" s="13"/>
+      <c r="H597" s="13"/>
     </row>
     <row r="598">
-      <c r="F598" s="12"/>
-      <c r="G598" s="12"/>
-      <c r="H598" s="12"/>
+      <c r="F598" s="13"/>
+      <c r="G598" s="13"/>
+      <c r="H598" s="13"/>
     </row>
     <row r="599">
-      <c r="F599" s="12"/>
-      <c r="G599" s="12"/>
-      <c r="H599" s="12"/>
+      <c r="F599" s="13"/>
+      <c r="G599" s="13"/>
+      <c r="H599" s="13"/>
     </row>
     <row r="600">
-      <c r="F600" s="12"/>
-      <c r="G600" s="12"/>
-      <c r="H600" s="12"/>
+      <c r="F600" s="13"/>
+      <c r="G600" s="13"/>
+      <c r="H600" s="13"/>
     </row>
     <row r="601">
-      <c r="F601" s="12"/>
-      <c r="G601" s="12"/>
-      <c r="H601" s="12"/>
+      <c r="F601" s="13"/>
+      <c r="G601" s="13"/>
+      <c r="H601" s="13"/>
     </row>
     <row r="602">
-      <c r="F602" s="12"/>
-      <c r="G602" s="12"/>
-      <c r="H602" s="12"/>
+      <c r="F602" s="13"/>
+      <c r="G602" s="13"/>
+      <c r="H602" s="13"/>
     </row>
     <row r="603">
-      <c r="F603" s="12"/>
-      <c r="G603" s="12"/>
-      <c r="H603" s="12"/>
+      <c r="F603" s="13"/>
+      <c r="G603" s="13"/>
+      <c r="H603" s="13"/>
     </row>
     <row r="604">
-      <c r="F604" s="12"/>
-      <c r="G604" s="12"/>
-      <c r="H604" s="12"/>
+      <c r="F604" s="13"/>
+      <c r="G604" s="13"/>
+      <c r="H604" s="13"/>
     </row>
     <row r="605">
-      <c r="F605" s="12"/>
-      <c r="G605" s="12"/>
-      <c r="H605" s="12"/>
+      <c r="F605" s="13"/>
+      <c r="G605" s="13"/>
+      <c r="H605" s="13"/>
     </row>
     <row r="606">
-      <c r="F606" s="12"/>
-      <c r="G606" s="12"/>
-      <c r="H606" s="12"/>
+      <c r="F606" s="13"/>
+      <c r="G606" s="13"/>
+      <c r="H606" s="13"/>
     </row>
     <row r="607">
-      <c r="F607" s="12"/>
-      <c r="G607" s="12"/>
-      <c r="H607" s="12"/>
+      <c r="F607" s="13"/>
+      <c r="G607" s="13"/>
+      <c r="H607" s="13"/>
     </row>
     <row r="608">
-      <c r="F608" s="12"/>
-      <c r="G608" s="12"/>
-      <c r="H608" s="12"/>
+      <c r="F608" s="13"/>
+      <c r="G608" s="13"/>
+      <c r="H608" s="13"/>
     </row>
     <row r="609">
-      <c r="F609" s="12"/>
-      <c r="G609" s="12"/>
-      <c r="H609" s="12"/>
+      <c r="F609" s="13"/>
+      <c r="G609" s="13"/>
+      <c r="H609" s="13"/>
     </row>
     <row r="610">
-      <c r="F610" s="12"/>
-      <c r="G610" s="12"/>
-      <c r="H610" s="12"/>
+      <c r="F610" s="13"/>
+      <c r="G610" s="13"/>
+      <c r="H610" s="13"/>
     </row>
     <row r="611">
-      <c r="F611" s="12"/>
-      <c r="G611" s="12"/>
-      <c r="H611" s="12"/>
+      <c r="F611" s="13"/>
+      <c r="G611" s="13"/>
+      <c r="H611" s="13"/>
     </row>
     <row r="612">
-      <c r="F612" s="12"/>
-      <c r="G612" s="12"/>
-      <c r="H612" s="12"/>
+      <c r="F612" s="13"/>
+      <c r="G612" s="13"/>
+      <c r="H612" s="13"/>
     </row>
     <row r="613">
-      <c r="F613" s="12"/>
-      <c r="G613" s="12"/>
-      <c r="H613" s="12"/>
+      <c r="F613" s="13"/>
+      <c r="G613" s="13"/>
+      <c r="H613" s="13"/>
     </row>
     <row r="614">
-      <c r="F614" s="12"/>
-      <c r="G614" s="12"/>
-      <c r="H614" s="12"/>
+      <c r="F614" s="13"/>
+      <c r="G614" s="13"/>
+      <c r="H614" s="13"/>
     </row>
     <row r="615">
-      <c r="F615" s="12"/>
-      <c r="G615" s="12"/>
-      <c r="H615" s="12"/>
+      <c r="F615" s="13"/>
+      <c r="G615" s="13"/>
+      <c r="H615" s="13"/>
     </row>
     <row r="616">
-      <c r="F616" s="12"/>
-      <c r="G616" s="12"/>
-      <c r="H616" s="12"/>
+      <c r="F616" s="13"/>
+      <c r="G616" s="13"/>
+      <c r="H616" s="13"/>
     </row>
     <row r="617">
-      <c r="F617" s="12"/>
-      <c r="G617" s="12"/>
-      <c r="H617" s="12"/>
+      <c r="F617" s="13"/>
+      <c r="G617" s="13"/>
+      <c r="H617" s="13"/>
     </row>
     <row r="618">
-      <c r="F618" s="12"/>
-      <c r="G618" s="12"/>
-      <c r="H618" s="12"/>
+      <c r="F618" s="13"/>
+      <c r="G618" s="13"/>
+      <c r="H618" s="13"/>
     </row>
     <row r="619">
-      <c r="F619" s="12"/>
-      <c r="G619" s="12"/>
-      <c r="H619" s="12"/>
+      <c r="F619" s="13"/>
+      <c r="G619" s="13"/>
+      <c r="H619" s="13"/>
     </row>
     <row r="620">
-      <c r="F620" s="12"/>
-      <c r="G620" s="12"/>
-      <c r="H620" s="12"/>
+      <c r="F620" s="13"/>
+      <c r="G620" s="13"/>
+      <c r="H620" s="13"/>
     </row>
     <row r="621">
-      <c r="F621" s="12"/>
-      <c r="G621" s="12"/>
-      <c r="H621" s="12"/>
+      <c r="F621" s="13"/>
+      <c r="G621" s="13"/>
+      <c r="H621" s="13"/>
     </row>
     <row r="622">
-      <c r="F622" s="12"/>
-      <c r="G622" s="12"/>
-      <c r="H622" s="12"/>
+      <c r="F622" s="13"/>
+      <c r="G622" s="13"/>
+      <c r="H622" s="13"/>
     </row>
     <row r="623">
-      <c r="F623" s="12"/>
-      <c r="G623" s="12"/>
-      <c r="H623" s="12"/>
+      <c r="F623" s="13"/>
+      <c r="G623" s="13"/>
+      <c r="H623" s="13"/>
     </row>
     <row r="624">
-      <c r="F624" s="12"/>
-      <c r="G624" s="12"/>
-      <c r="H624" s="12"/>
+      <c r="F624" s="13"/>
+      <c r="G624" s="13"/>
+      <c r="H624" s="13"/>
     </row>
     <row r="625">
-      <c r="F625" s="12"/>
-      <c r="G625" s="12"/>
-      <c r="H625" s="12"/>
+      <c r="F625" s="13"/>
+      <c r="G625" s="13"/>
+      <c r="H625" s="13"/>
     </row>
     <row r="626">
-      <c r="F626" s="12"/>
-      <c r="G626" s="12"/>
-      <c r="H626" s="12"/>
+      <c r="F626" s="13"/>
+      <c r="G626" s="13"/>
+      <c r="H626" s="13"/>
     </row>
     <row r="627">
-      <c r="F627" s="12"/>
-      <c r="G627" s="12"/>
-      <c r="H627" s="12"/>
+      <c r="F627" s="13"/>
+      <c r="G627" s="13"/>
+      <c r="H627" s="13"/>
     </row>
     <row r="628">
-      <c r="F628" s="12"/>
-      <c r="G628" s="12"/>
-      <c r="H628" s="12"/>
+      <c r="F628" s="13"/>
+      <c r="G628" s="13"/>
+      <c r="H628" s="13"/>
     </row>
     <row r="629">
-      <c r="F629" s="12"/>
-      <c r="G629" s="12"/>
-      <c r="H629" s="12"/>
+      <c r="F629" s="13"/>
+      <c r="G629" s="13"/>
+      <c r="H629" s="13"/>
     </row>
     <row r="630">
-      <c r="F630" s="12"/>
-      <c r="G630" s="12"/>
-      <c r="H630" s="12"/>
+      <c r="F630" s="13"/>
+      <c r="G630" s="13"/>
+      <c r="H630" s="13"/>
     </row>
     <row r="631">
-      <c r="F631" s="12"/>
-      <c r="G631" s="12"/>
-      <c r="H631" s="12"/>
+      <c r="F631" s="13"/>
+      <c r="G631" s="13"/>
+      <c r="H631" s="13"/>
     </row>
     <row r="632">
-      <c r="F632" s="12"/>
-      <c r="G632" s="12"/>
-      <c r="H632" s="12"/>
+      <c r="F632" s="13"/>
+      <c r="G632" s="13"/>
+      <c r="H632" s="13"/>
     </row>
     <row r="633">
-      <c r="F633" s="12"/>
-      <c r="G633" s="12"/>
-      <c r="H633" s="12"/>
+      <c r="F633" s="13"/>
+      <c r="G633" s="13"/>
+      <c r="H633" s="13"/>
     </row>
     <row r="634">
-      <c r="F634" s="12"/>
-      <c r="G634" s="12"/>
-      <c r="H634" s="12"/>
+      <c r="F634" s="13"/>
+      <c r="G634" s="13"/>
+      <c r="H634" s="13"/>
     </row>
     <row r="635">
-      <c r="F635" s="12"/>
-      <c r="G635" s="12"/>
-      <c r="H635" s="12"/>
+      <c r="F635" s="13"/>
+      <c r="G635" s="13"/>
+      <c r="H635" s="13"/>
     </row>
     <row r="636">
-      <c r="F636" s="12"/>
-      <c r="G636" s="12"/>
-      <c r="H636" s="12"/>
+      <c r="F636" s="13"/>
+      <c r="G636" s="13"/>
+      <c r="H636" s="13"/>
     </row>
     <row r="637">
-      <c r="F637" s="12"/>
-      <c r="G637" s="12"/>
-      <c r="H637" s="12"/>
+      <c r="F637" s="13"/>
+      <c r="G637" s="13"/>
+      <c r="H637" s="13"/>
     </row>
     <row r="638">
-      <c r="F638" s="12"/>
-      <c r="G638" s="12"/>
-      <c r="H638" s="12"/>
+      <c r="F638" s="13"/>
+      <c r="G638" s="13"/>
+      <c r="H638" s="13"/>
     </row>
     <row r="639">
-      <c r="F639" s="12"/>
-      <c r="G639" s="12"/>
-      <c r="H639" s="12"/>
+      <c r="F639" s="13"/>
+      <c r="G639" s="13"/>
+      <c r="H639" s="13"/>
     </row>
     <row r="640">
-      <c r="F640" s="12"/>
-      <c r="G640" s="12"/>
-      <c r="H640" s="12"/>
+      <c r="F640" s="13"/>
+      <c r="G640" s="13"/>
+      <c r="H640" s="13"/>
     </row>
     <row r="641">
-      <c r="F641" s="12"/>
-      <c r="G641" s="12"/>
-      <c r="H641" s="12"/>
+      <c r="F641" s="13"/>
+      <c r="G641" s="13"/>
+      <c r="H641" s="13"/>
     </row>
     <row r="642">
-      <c r="F642" s="12"/>
-      <c r="G642" s="12"/>
-      <c r="H642" s="12"/>
+      <c r="F642" s="13"/>
+      <c r="G642" s="13"/>
+      <c r="H642" s="13"/>
     </row>
     <row r="643">
-      <c r="F643" s="12"/>
-      <c r="G643" s="12"/>
-      <c r="H643" s="12"/>
+      <c r="F643" s="13"/>
+      <c r="G643" s="13"/>
+      <c r="H643" s="13"/>
     </row>
     <row r="644">
-      <c r="F644" s="12"/>
-      <c r="G644" s="12"/>
-      <c r="H644" s="12"/>
+      <c r="F644" s="13"/>
+      <c r="G644" s="13"/>
+      <c r="H644" s="13"/>
     </row>
     <row r="645">
-      <c r="F645" s="12"/>
-      <c r="G645" s="12"/>
-      <c r="H645" s="12"/>
+      <c r="F645" s="13"/>
+      <c r="G645" s="13"/>
+      <c r="H645" s="13"/>
     </row>
     <row r="646">
-      <c r="F646" s="12"/>
-      <c r="G646" s="12"/>
-      <c r="H646" s="12"/>
+      <c r="F646" s="13"/>
+      <c r="G646" s="13"/>
+      <c r="H646" s="13"/>
     </row>
     <row r="647">
-      <c r="F647" s="12"/>
-      <c r="G647" s="12"/>
-      <c r="H647" s="12"/>
+      <c r="F647" s="13"/>
+      <c r="G647" s="13"/>
+      <c r="H647" s="13"/>
     </row>
     <row r="648">
-      <c r="F648" s="12"/>
-      <c r="G648" s="12"/>
-      <c r="H648" s="12"/>
+      <c r="F648" s="13"/>
+      <c r="G648" s="13"/>
+      <c r="H648" s="13"/>
     </row>
     <row r="649">
-      <c r="F649" s="12"/>
-      <c r="G649" s="12"/>
-      <c r="H649" s="12"/>
+      <c r="F649" s="13"/>
+      <c r="G649" s="13"/>
+      <c r="H649" s="13"/>
     </row>
     <row r="650">
-      <c r="F650" s="12"/>
-      <c r="G650" s="12"/>
-      <c r="H650" s="12"/>
+      <c r="F650" s="13"/>
+      <c r="G650" s="13"/>
+      <c r="H650" s="13"/>
     </row>
     <row r="651">
-      <c r="F651" s="12"/>
-      <c r="G651" s="12"/>
-      <c r="H651" s="12"/>
+      <c r="F651" s="13"/>
+      <c r="G651" s="13"/>
+      <c r="H651" s="13"/>
     </row>
     <row r="652">
-      <c r="F652" s="12"/>
-      <c r="G652" s="12"/>
-      <c r="H652" s="12"/>
+      <c r="F652" s="13"/>
+      <c r="G652" s="13"/>
+      <c r="H652" s="13"/>
     </row>
     <row r="653">
-      <c r="F653" s="12"/>
-      <c r="G653" s="12"/>
-      <c r="H653" s="12"/>
+      <c r="F653" s="13"/>
+      <c r="G653" s="13"/>
+      <c r="H653" s="13"/>
     </row>
     <row r="654">
-      <c r="F654" s="12"/>
-      <c r="G654" s="12"/>
-      <c r="H654" s="12"/>
+      <c r="F654" s="13"/>
+      <c r="G654" s="13"/>
+      <c r="H654" s="13"/>
     </row>
     <row r="655">
-      <c r="F655" s="12"/>
-      <c r="G655" s="12"/>
-      <c r="H655" s="12"/>
+      <c r="F655" s="13"/>
+      <c r="G655" s="13"/>
+      <c r="H655" s="13"/>
     </row>
     <row r="656">
-      <c r="F656" s="12"/>
-      <c r="G656" s="12"/>
-      <c r="H656" s="12"/>
+      <c r="F656" s="13"/>
+      <c r="G656" s="13"/>
+      <c r="H656" s="13"/>
     </row>
     <row r="657">
-      <c r="F657" s="12"/>
-      <c r="G657" s="12"/>
-      <c r="H657" s="12"/>
+      <c r="F657" s="13"/>
+      <c r="G657" s="13"/>
+      <c r="H657" s="13"/>
     </row>
     <row r="658">
-      <c r="F658" s="12"/>
-      <c r="G658" s="12"/>
-      <c r="H658" s="12"/>
+      <c r="F658" s="13"/>
+      <c r="G658" s="13"/>
+      <c r="H658" s="13"/>
     </row>
     <row r="659">
-      <c r="F659" s="12"/>
-      <c r="G659" s="12"/>
-      <c r="H659" s="12"/>
+      <c r="F659" s="13"/>
+      <c r="G659" s="13"/>
+      <c r="H659" s="13"/>
     </row>
     <row r="660">
-      <c r="F660" s="12"/>
-      <c r="G660" s="12"/>
-      <c r="H660" s="12"/>
+      <c r="F660" s="13"/>
+      <c r="G660" s="13"/>
+      <c r="H660" s="13"/>
     </row>
     <row r="661">
-      <c r="F661" s="12"/>
-      <c r="G661" s="12"/>
-      <c r="H661" s="12"/>
+      <c r="F661" s="13"/>
+      <c r="G661" s="13"/>
+      <c r="H661" s="13"/>
     </row>
     <row r="662">
-      <c r="F662" s="12"/>
-      <c r="G662" s="12"/>
-      <c r="H662" s="12"/>
+      <c r="F662" s="13"/>
+      <c r="G662" s="13"/>
+      <c r="H662" s="13"/>
     </row>
     <row r="663">
-      <c r="F663" s="12"/>
-      <c r="G663" s="12"/>
-      <c r="H663" s="12"/>
+      <c r="F663" s="13"/>
+      <c r="G663" s="13"/>
+      <c r="H663" s="13"/>
     </row>
     <row r="664">
-      <c r="F664" s="12"/>
-      <c r="G664" s="12"/>
-      <c r="H664" s="12"/>
+      <c r="F664" s="13"/>
+      <c r="G664" s="13"/>
+      <c r="H664" s="13"/>
     </row>
     <row r="665">
-      <c r="F665" s="12"/>
-      <c r="G665" s="12"/>
-      <c r="H665" s="12"/>
+      <c r="F665" s="13"/>
+      <c r="G665" s="13"/>
+      <c r="H665" s="13"/>
     </row>
     <row r="666">
-      <c r="F666" s="12"/>
-      <c r="G666" s="12"/>
-      <c r="H666" s="12"/>
+      <c r="F666" s="13"/>
+      <c r="G666" s="13"/>
+      <c r="H666" s="13"/>
     </row>
     <row r="667">
-      <c r="F667" s="12"/>
-      <c r="G667" s="12"/>
-      <c r="H667" s="12"/>
+      <c r="F667" s="13"/>
+      <c r="G667" s="13"/>
+      <c r="H667" s="13"/>
     </row>
     <row r="668">
-      <c r="F668" s="12"/>
-      <c r="G668" s="12"/>
-      <c r="H668" s="12"/>
+      <c r="F668" s="13"/>
+      <c r="G668" s="13"/>
+      <c r="H668" s="13"/>
     </row>
     <row r="669">
-      <c r="F669" s="12"/>
-      <c r="G669" s="12"/>
-      <c r="H669" s="12"/>
+      <c r="F669" s="13"/>
+      <c r="G669" s="13"/>
+      <c r="H669" s="13"/>
     </row>
     <row r="670">
-      <c r="F670" s="12"/>
-      <c r="G670" s="12"/>
-      <c r="H670" s="12"/>
+      <c r="F670" s="13"/>
+      <c r="G670" s="13"/>
+      <c r="H670" s="13"/>
     </row>
     <row r="671">
-      <c r="F671" s="12"/>
-      <c r="G671" s="12"/>
-      <c r="H671" s="12"/>
+      <c r="F671" s="13"/>
+      <c r="G671" s="13"/>
+      <c r="H671" s="13"/>
     </row>
     <row r="672">
-      <c r="F672" s="12"/>
-      <c r="G672" s="12"/>
-      <c r="H672" s="12"/>
+      <c r="F672" s="13"/>
+      <c r="G672" s="13"/>
+      <c r="H672" s="13"/>
     </row>
     <row r="673">
-      <c r="F673" s="12"/>
-      <c r="G673" s="12"/>
-      <c r="H673" s="12"/>
+      <c r="F673" s="13"/>
+      <c r="G673" s="13"/>
+      <c r="H673" s="13"/>
     </row>
     <row r="674">
-      <c r="F674" s="12"/>
-      <c r="G674" s="12"/>
-      <c r="H674" s="12"/>
+      <c r="F674" s="13"/>
+      <c r="G674" s="13"/>
+      <c r="H674" s="13"/>
     </row>
     <row r="675">
-      <c r="F675" s="12"/>
-      <c r="G675" s="12"/>
-      <c r="H675" s="12"/>
+      <c r="F675" s="13"/>
+      <c r="G675" s="13"/>
+      <c r="H675" s="13"/>
     </row>
     <row r="676">
-      <c r="F676" s="12"/>
-      <c r="G676" s="12"/>
-      <c r="H676" s="12"/>
+      <c r="F676" s="13"/>
+      <c r="G676" s="13"/>
+      <c r="H676" s="13"/>
     </row>
     <row r="677">
-      <c r="F677" s="12"/>
-      <c r="G677" s="12"/>
-      <c r="H677" s="12"/>
+      <c r="F677" s="13"/>
+      <c r="G677" s="13"/>
+      <c r="H677" s="13"/>
     </row>
     <row r="678">
-      <c r="F678" s="12"/>
-      <c r="G678" s="12"/>
-      <c r="H678" s="12"/>
+      <c r="F678" s="13"/>
+      <c r="G678" s="13"/>
+      <c r="H678" s="13"/>
     </row>
     <row r="679">
-      <c r="F679" s="12"/>
-      <c r="G679" s="12"/>
-      <c r="H679" s="12"/>
+      <c r="F679" s="13"/>
+      <c r="G679" s="13"/>
+      <c r="H679" s="13"/>
     </row>
     <row r="680">
-      <c r="F680" s="12"/>
-      <c r="G680" s="12"/>
-      <c r="H680" s="12"/>
+      <c r="F680" s="13"/>
+      <c r="G680" s="13"/>
+      <c r="H680" s="13"/>
     </row>
     <row r="681">
-      <c r="F681" s="12"/>
-      <c r="G681" s="12"/>
-      <c r="H681" s="12"/>
+      <c r="F681" s="13"/>
+      <c r="G681" s="13"/>
+      <c r="H681" s="13"/>
     </row>
     <row r="682">
-      <c r="F682" s="12"/>
-      <c r="G682" s="12"/>
-      <c r="H682" s="12"/>
+      <c r="F682" s="13"/>
+      <c r="G682" s="13"/>
+      <c r="H682" s="13"/>
     </row>
     <row r="683">
-      <c r="F683" s="12"/>
-      <c r="G683" s="12"/>
-      <c r="H683" s="12"/>
+      <c r="F683" s="13"/>
+      <c r="G683" s="13"/>
+      <c r="H683" s="13"/>
     </row>
     <row r="684">
-      <c r="F684" s="12"/>
-      <c r="G684" s="12"/>
-      <c r="H684" s="12"/>
+      <c r="F684" s="13"/>
+      <c r="G684" s="13"/>
+      <c r="H684" s="13"/>
     </row>
     <row r="685">
-      <c r="F685" s="12"/>
-      <c r="G685" s="12"/>
-      <c r="H685" s="12"/>
+      <c r="F685" s="13"/>
+      <c r="G685" s="13"/>
+      <c r="H685" s="13"/>
     </row>
     <row r="686">
-      <c r="F686" s="12"/>
-      <c r="G686" s="12"/>
-      <c r="H686" s="12"/>
+      <c r="F686" s="13"/>
+      <c r="G686" s="13"/>
+      <c r="H686" s="13"/>
     </row>
     <row r="687">
-      <c r="F687" s="12"/>
-      <c r="G687" s="12"/>
-      <c r="H687" s="12"/>
+      <c r="F687" s="13"/>
+      <c r="G687" s="13"/>
+      <c r="H687" s="13"/>
     </row>
     <row r="688">
-      <c r="F688" s="12"/>
-      <c r="G688" s="12"/>
-      <c r="H688" s="12"/>
+      <c r="F688" s="13"/>
+      <c r="G688" s="13"/>
+      <c r="H688" s="13"/>
     </row>
     <row r="689">
-      <c r="F689" s="12"/>
-      <c r="G689" s="12"/>
-      <c r="H689" s="12"/>
+      <c r="F689" s="13"/>
+      <c r="G689" s="13"/>
+      <c r="H689" s="13"/>
     </row>
     <row r="690">
-      <c r="F690" s="12"/>
-      <c r="G690" s="12"/>
-      <c r="H690" s="12"/>
+      <c r="F690" s="13"/>
+      <c r="G690" s="13"/>
+      <c r="H690" s="13"/>
     </row>
     <row r="691">
-      <c r="F691" s="12"/>
-      <c r="G691" s="12"/>
-      <c r="H691" s="12"/>
+      <c r="F691" s="13"/>
+      <c r="G691" s="13"/>
+      <c r="H691" s="13"/>
     </row>
     <row r="692">
-      <c r="F692" s="12"/>
-      <c r="G692" s="12"/>
-      <c r="H692" s="12"/>
+      <c r="F692" s="13"/>
+      <c r="G692" s="13"/>
+      <c r="H692" s="13"/>
     </row>
     <row r="693">
-      <c r="F693" s="12"/>
-      <c r="G693" s="12"/>
-      <c r="H693" s="12"/>
+      <c r="F693" s="13"/>
+      <c r="G693" s="13"/>
+      <c r="H693" s="13"/>
     </row>
     <row r="694">
-      <c r="F694" s="12"/>
-      <c r="G694" s="12"/>
-      <c r="H694" s="12"/>
+      <c r="F694" s="13"/>
+      <c r="G694" s="13"/>
+      <c r="H694" s="13"/>
     </row>
     <row r="695">
-      <c r="F695" s="12"/>
-      <c r="G695" s="12"/>
-      <c r="H695" s="12"/>
+      <c r="F695" s="13"/>
+      <c r="G695" s="13"/>
+      <c r="H695" s="13"/>
     </row>
     <row r="696">
-      <c r="F696" s="12"/>
-      <c r="G696" s="12"/>
-      <c r="H696" s="12"/>
+      <c r="F696" s="13"/>
+      <c r="G696" s="13"/>
+      <c r="H696" s="13"/>
     </row>
     <row r="697">
-      <c r="F697" s="12"/>
-      <c r="G697" s="12"/>
-      <c r="H697" s="12"/>
+      <c r="F697" s="13"/>
+      <c r="G697" s="13"/>
+      <c r="H697" s="13"/>
     </row>
     <row r="698">
-      <c r="F698" s="12"/>
-      <c r="G698" s="12"/>
-      <c r="H698" s="12"/>
+      <c r="F698" s="13"/>
+      <c r="G698" s="13"/>
+      <c r="H698" s="13"/>
     </row>
     <row r="699">
-      <c r="F699" s="12"/>
-      <c r="G699" s="12"/>
-      <c r="H699" s="12"/>
+      <c r="F699" s="13"/>
+      <c r="G699" s="13"/>
+      <c r="H699" s="13"/>
     </row>
     <row r="700">
-      <c r="F700" s="12"/>
-      <c r="G700" s="12"/>
-      <c r="H700" s="12"/>
+      <c r="F700" s="13"/>
+      <c r="G700" s="13"/>
+      <c r="H700" s="13"/>
     </row>
     <row r="701">
-      <c r="F701" s="12"/>
-      <c r="G701" s="12"/>
-      <c r="H701" s="12"/>
+      <c r="F701" s="13"/>
+      <c r="G701" s="13"/>
+      <c r="H701" s="13"/>
     </row>
     <row r="702">
-      <c r="F702" s="12"/>
-      <c r="G702" s="12"/>
-      <c r="H702" s="12"/>
+      <c r="F702" s="13"/>
+      <c r="G702" s="13"/>
+      <c r="H702" s="13"/>
     </row>
     <row r="703">
-      <c r="F703" s="12"/>
-      <c r="G703" s="12"/>
-      <c r="H703" s="12"/>
+      <c r="F703" s="13"/>
+      <c r="G703" s="13"/>
+      <c r="H703" s="13"/>
     </row>
     <row r="704">
-      <c r="F704" s="12"/>
-      <c r="G704" s="12"/>
-      <c r="H704" s="12"/>
+      <c r="F704" s="13"/>
+      <c r="G704" s="13"/>
+      <c r="H704" s="13"/>
     </row>
     <row r="705">
-      <c r="F705" s="12"/>
-      <c r="G705" s="12"/>
-      <c r="H705" s="12"/>
+      <c r="F705" s="13"/>
+      <c r="G705" s="13"/>
+      <c r="H705" s="13"/>
     </row>
     <row r="706">
-      <c r="F706" s="12"/>
-      <c r="G706" s="12"/>
-      <c r="H706" s="12"/>
+      <c r="F706" s="13"/>
+      <c r="G706" s="13"/>
+      <c r="H706" s="13"/>
     </row>
     <row r="707">
-      <c r="F707" s="12"/>
-      <c r="G707" s="12"/>
-      <c r="H707" s="12"/>
+      <c r="F707" s="13"/>
+      <c r="G707" s="13"/>
+      <c r="H707" s="13"/>
     </row>
     <row r="708">
-      <c r="F708" s="12"/>
-      <c r="G708" s="12"/>
-      <c r="H708" s="12"/>
+      <c r="F708" s="13"/>
+      <c r="G708" s="13"/>
+      <c r="H708" s="13"/>
     </row>
     <row r="709">
-      <c r="F709" s="12"/>
-      <c r="G709" s="12"/>
-      <c r="H709" s="12"/>
+      <c r="F709" s="13"/>
+      <c r="G709" s="13"/>
+      <c r="H709" s="13"/>
     </row>
     <row r="710">
-      <c r="F710" s="12"/>
-      <c r="G710" s="12"/>
-      <c r="H710" s="12"/>
+      <c r="F710" s="13"/>
+      <c r="G710" s="13"/>
+      <c r="H710" s="13"/>
     </row>
     <row r="711">
-      <c r="F711" s="12"/>
-      <c r="G711" s="12"/>
-      <c r="H711" s="12"/>
+      <c r="F711" s="13"/>
+      <c r="G711" s="13"/>
+      <c r="H711" s="13"/>
     </row>
     <row r="712">
-      <c r="F712" s="12"/>
-      <c r="G712" s="12"/>
-      <c r="H712" s="12"/>
+      <c r="F712" s="13"/>
+      <c r="G712" s="13"/>
+      <c r="H712" s="13"/>
     </row>
     <row r="713">
-      <c r="F713" s="12"/>
-      <c r="G713" s="12"/>
-      <c r="H713" s="12"/>
+      <c r="F713" s="13"/>
+      <c r="G713" s="13"/>
+      <c r="H713" s="13"/>
     </row>
     <row r="714">
-      <c r="F714" s="12"/>
-      <c r="G714" s="12"/>
-      <c r="H714" s="12"/>
+      <c r="F714" s="13"/>
+      <c r="G714" s="13"/>
+      <c r="H714" s="13"/>
     </row>
     <row r="715">
-      <c r="F715" s="12"/>
-      <c r="G715" s="12"/>
-      <c r="H715" s="12"/>
+      <c r="F715" s="13"/>
+      <c r="G715" s="13"/>
+      <c r="H715" s="13"/>
     </row>
     <row r="716">
-      <c r="F716" s="12"/>
-      <c r="G716" s="12"/>
-      <c r="H716" s="12"/>
+      <c r="F716" s="13"/>
+      <c r="G716" s="13"/>
+      <c r="H716" s="13"/>
     </row>
     <row r="717">
-      <c r="F717" s="12"/>
-      <c r="G717" s="12"/>
-      <c r="H717" s="12"/>
+      <c r="F717" s="13"/>
+      <c r="G717" s="13"/>
+      <c r="H717" s="13"/>
     </row>
     <row r="718">
-      <c r="F718" s="12"/>
-      <c r="G718" s="12"/>
-      <c r="H718" s="12"/>
+      <c r="F718" s="13"/>
+      <c r="G718" s="13"/>
+      <c r="H718" s="13"/>
     </row>
     <row r="719">
-      <c r="F719" s="12"/>
-      <c r="G719" s="12"/>
-      <c r="H719" s="12"/>
+      <c r="F719" s="13"/>
+      <c r="G719" s="13"/>
+      <c r="H719" s="13"/>
     </row>
     <row r="720">
-      <c r="F720" s="12"/>
-      <c r="G720" s="12"/>
-      <c r="H720" s="12"/>
+      <c r="F720" s="13"/>
+      <c r="G720" s="13"/>
+      <c r="H720" s="13"/>
     </row>
     <row r="721">
-      <c r="F721" s="12"/>
-      <c r="G721" s="12"/>
-      <c r="H721" s="12"/>
+      <c r="F721" s="13"/>
+      <c r="G721" s="13"/>
+      <c r="H721" s="13"/>
     </row>
     <row r="722">
-      <c r="F722" s="12"/>
-      <c r="G722" s="12"/>
-      <c r="H722" s="12"/>
+      <c r="F722" s="13"/>
+      <c r="G722" s="13"/>
+      <c r="H722" s="13"/>
     </row>
     <row r="723">
-      <c r="F723" s="12"/>
-      <c r="G723" s="12"/>
-      <c r="H723" s="12"/>
+      <c r="F723" s="13"/>
+      <c r="G723" s="13"/>
+      <c r="H723" s="13"/>
     </row>
     <row r="724">
-      <c r="F724" s="12"/>
-      <c r="G724" s="12"/>
-      <c r="H724" s="12"/>
+      <c r="F724" s="13"/>
+      <c r="G724" s="13"/>
+      <c r="H724" s="13"/>
     </row>
     <row r="725">
-      <c r="F725" s="12"/>
-      <c r="G725" s="12"/>
-      <c r="H725" s="12"/>
+      <c r="F725" s="13"/>
+      <c r="G725" s="13"/>
+      <c r="H725" s="13"/>
     </row>
     <row r="726">
-      <c r="F726" s="12"/>
-      <c r="G726" s="12"/>
-      <c r="H726" s="12"/>
+      <c r="F726" s="13"/>
+      <c r="G726" s="13"/>
+      <c r="H726" s="13"/>
     </row>
     <row r="727">
-      <c r="F727" s="12"/>
-      <c r="G727" s="12"/>
-      <c r="H727" s="12"/>
+      <c r="F727" s="13"/>
+      <c r="G727" s="13"/>
+      <c r="H727" s="13"/>
     </row>
     <row r="728">
-      <c r="F728" s="12"/>
-      <c r="G728" s="12"/>
-      <c r="H728" s="12"/>
+      <c r="F728" s="13"/>
+      <c r="G728" s="13"/>
+      <c r="H728" s="13"/>
     </row>
     <row r="729">
-      <c r="F729" s="12"/>
-      <c r="G729" s="12"/>
-      <c r="H729" s="12"/>
+      <c r="F729" s="13"/>
+      <c r="G729" s="13"/>
+      <c r="H729" s="13"/>
     </row>
     <row r="730">
-      <c r="F730" s="12"/>
-      <c r="G730" s="12"/>
-      <c r="H730" s="12"/>
+      <c r="F730" s="13"/>
+      <c r="G730" s="13"/>
+      <c r="H730" s="13"/>
     </row>
     <row r="731">
-      <c r="F731" s="12"/>
-      <c r="G731" s="12"/>
-      <c r="H731" s="12"/>
+      <c r="F731" s="13"/>
+      <c r="G731" s="13"/>
+      <c r="H731" s="13"/>
     </row>
     <row r="732">
-      <c r="F732" s="12"/>
-      <c r="G732" s="12"/>
-      <c r="H732" s="12"/>
+      <c r="F732" s="13"/>
+      <c r="G732" s="13"/>
+      <c r="H732" s="13"/>
     </row>
     <row r="733">
-      <c r="F733" s="12"/>
-      <c r="G733" s="12"/>
-      <c r="H733" s="12"/>
+      <c r="F733" s="13"/>
+      <c r="G733" s="13"/>
+      <c r="H733" s="13"/>
     </row>
     <row r="734">
-      <c r="F734" s="12"/>
-      <c r="G734" s="12"/>
-      <c r="H734" s="12"/>
+      <c r="F734" s="13"/>
+      <c r="G734" s="13"/>
+      <c r="H734" s="13"/>
     </row>
     <row r="735">
-      <c r="F735" s="12"/>
-      <c r="G735" s="12"/>
-      <c r="H735" s="12"/>
+      <c r="F735" s="13"/>
+      <c r="G735" s="13"/>
+      <c r="H735" s="13"/>
     </row>
     <row r="736">
-      <c r="F736" s="12"/>
-      <c r="G736" s="12"/>
-      <c r="H736" s="12"/>
+      <c r="F736" s="13"/>
+      <c r="G736" s="13"/>
+      <c r="H736" s="13"/>
     </row>
     <row r="737">
-      <c r="F737" s="12"/>
-      <c r="G737" s="12"/>
-      <c r="H737" s="12"/>
+      <c r="F737" s="13"/>
+      <c r="G737" s="13"/>
+      <c r="H737" s="13"/>
     </row>
     <row r="738">
-      <c r="F738" s="12"/>
-      <c r="G738" s="12"/>
-      <c r="H738" s="12"/>
+      <c r="F738" s="13"/>
+      <c r="G738" s="13"/>
+      <c r="H738" s="13"/>
     </row>
     <row r="739">
-      <c r="F739" s="12"/>
-      <c r="G739" s="12"/>
-      <c r="H739" s="12"/>
+      <c r="F739" s="13"/>
+      <c r="G739" s="13"/>
+      <c r="H739" s="13"/>
     </row>
     <row r="740">
-      <c r="F740" s="12"/>
-      <c r="G740" s="12"/>
-      <c r="H740" s="12"/>
+      <c r="F740" s="13"/>
+      <c r="G740" s="13"/>
+      <c r="H740" s="13"/>
     </row>
     <row r="741">
-      <c r="F741" s="12"/>
-      <c r="G741" s="12"/>
-      <c r="H741" s="12"/>
+      <c r="F741" s="13"/>
+      <c r="G741" s="13"/>
+      <c r="H741" s="13"/>
     </row>
     <row r="742">
-      <c r="F742" s="12"/>
-      <c r="G742" s="12"/>
-      <c r="H742" s="12"/>
+      <c r="F742" s="13"/>
+      <c r="G742" s="13"/>
+      <c r="H742" s="13"/>
     </row>
     <row r="743">
-      <c r="F743" s="12"/>
-      <c r="G743" s="12"/>
-      <c r="H743" s="12"/>
+      <c r="F743" s="13"/>
+      <c r="G743" s="13"/>
+      <c r="H743" s="13"/>
     </row>
     <row r="744">
-      <c r="F744" s="12"/>
-      <c r="G744" s="12"/>
-      <c r="H744" s="12"/>
+      <c r="F744" s="13"/>
+      <c r="G744" s="13"/>
+      <c r="H744" s="13"/>
     </row>
     <row r="745">
-      <c r="F745" s="12"/>
-      <c r="G745" s="12"/>
-      <c r="H745" s="12"/>
+      <c r="F745" s="13"/>
+      <c r="G745" s="13"/>
+      <c r="H745" s="13"/>
     </row>
     <row r="746">
-      <c r="F746" s="12"/>
-      <c r="G746" s="12"/>
-      <c r="H746" s="12"/>
+      <c r="F746" s="13"/>
+      <c r="G746" s="13"/>
+      <c r="H746" s="13"/>
     </row>
     <row r="747">
-      <c r="F747" s="12"/>
-      <c r="G747" s="12"/>
-      <c r="H747" s="12"/>
+      <c r="F747" s="13"/>
+      <c r="G747" s="13"/>
+      <c r="H747" s="13"/>
     </row>
     <row r="748">
-      <c r="F748" s="12"/>
-      <c r="G748" s="12"/>
-      <c r="H748" s="12"/>
+      <c r="F748" s="13"/>
+      <c r="G748" s="13"/>
+      <c r="H748" s="13"/>
     </row>
     <row r="749">
-      <c r="F749" s="12"/>
-      <c r="G749" s="12"/>
-      <c r="H749" s="12"/>
+      <c r="F749" s="13"/>
+      <c r="G749" s="13"/>
+      <c r="H749" s="13"/>
     </row>
     <row r="750">
-      <c r="F750" s="12"/>
-      <c r="G750" s="12"/>
-      <c r="H750" s="12"/>
+      <c r="F750" s="13"/>
+      <c r="G750" s="13"/>
+      <c r="H750" s="13"/>
     </row>
     <row r="751">
-      <c r="F751" s="12"/>
-      <c r="G751" s="12"/>
-      <c r="H751" s="12"/>
+      <c r="F751" s="13"/>
+      <c r="G751" s="13"/>
+      <c r="H751" s="13"/>
     </row>
     <row r="752">
-      <c r="F752" s="12"/>
-      <c r="G752" s="12"/>
-      <c r="H752" s="12"/>
+      <c r="F752" s="13"/>
+      <c r="G752" s="13"/>
+      <c r="H752" s="13"/>
     </row>
     <row r="753">
-      <c r="F753" s="12"/>
-      <c r="G753" s="12"/>
-      <c r="H753" s="12"/>
+      <c r="F753" s="13"/>
+      <c r="G753" s="13"/>
+      <c r="H753" s="13"/>
     </row>
     <row r="754">
-      <c r="F754" s="12"/>
-      <c r="G754" s="12"/>
-      <c r="H754" s="12"/>
+      <c r="F754" s="13"/>
+      <c r="G754" s="13"/>
+      <c r="H754" s="13"/>
     </row>
     <row r="755">
-      <c r="F755" s="12"/>
-      <c r="G755" s="12"/>
-      <c r="H755" s="12"/>
+      <c r="F755" s="13"/>
+      <c r="G755" s="13"/>
+      <c r="H755" s="13"/>
     </row>
     <row r="756">
-      <c r="F756" s="12"/>
-      <c r="G756" s="12"/>
-      <c r="H756" s="12"/>
+      <c r="F756" s="13"/>
+      <c r="G756" s="13"/>
+      <c r="H756" s="13"/>
     </row>
     <row r="757">
-      <c r="F757" s="12"/>
-      <c r="G757" s="12"/>
-      <c r="H757" s="12"/>
+      <c r="F757" s="13"/>
+      <c r="G757" s="13"/>
+      <c r="H757" s="13"/>
     </row>
     <row r="758">
-      <c r="F758" s="12"/>
-      <c r="G758" s="12"/>
-      <c r="H758" s="12"/>
+      <c r="F758" s="13"/>
+      <c r="G758" s="13"/>
+      <c r="H758" s="13"/>
     </row>
     <row r="759">
-      <c r="F759" s="12"/>
-      <c r="G759" s="12"/>
-      <c r="H759" s="12"/>
+      <c r="F759" s="13"/>
+      <c r="G759" s="13"/>
+      <c r="H759" s="13"/>
     </row>
     <row r="760">
-      <c r="F760" s="12"/>
-      <c r="G760" s="12"/>
-      <c r="H760" s="12"/>
+      <c r="F760" s="13"/>
+      <c r="G760" s="13"/>
+      <c r="H760" s="13"/>
     </row>
     <row r="761">
-      <c r="F761" s="12"/>
-      <c r="G761" s="12"/>
-      <c r="H761" s="12"/>
+      <c r="F761" s="13"/>
+      <c r="G761" s="13"/>
+      <c r="H761" s="13"/>
     </row>
     <row r="762">
-      <c r="F762" s="12"/>
-      <c r="G762" s="12"/>
-      <c r="H762" s="12"/>
+      <c r="F762" s="13"/>
+      <c r="G762" s="13"/>
+      <c r="H762" s="13"/>
     </row>
     <row r="763">
-      <c r="F763" s="12"/>
-      <c r="G763" s="12"/>
-      <c r="H763" s="12"/>
+      <c r="F763" s="13"/>
+      <c r="G763" s="13"/>
+      <c r="H763" s="13"/>
     </row>
     <row r="764">
-      <c r="F764" s="12"/>
-      <c r="G764" s="12"/>
-      <c r="H764" s="12"/>
+      <c r="F764" s="13"/>
+      <c r="G764" s="13"/>
+      <c r="H764" s="13"/>
     </row>
     <row r="765">
-      <c r="F765" s="12"/>
-      <c r="G765" s="12"/>
-      <c r="H765" s="12"/>
+      <c r="F765" s="13"/>
+      <c r="G765" s="13"/>
+      <c r="H765" s="13"/>
     </row>
     <row r="766">
-      <c r="F766" s="12"/>
-      <c r="G766" s="12"/>
-      <c r="H766" s="12"/>
+      <c r="F766" s="13"/>
+      <c r="G766" s="13"/>
+      <c r="H766" s="13"/>
     </row>
     <row r="767">
-      <c r="F767" s="12"/>
-      <c r="G767" s="12"/>
-      <c r="H767" s="12"/>
+      <c r="F767" s="13"/>
+      <c r="G767" s="13"/>
+      <c r="H767" s="13"/>
     </row>
     <row r="768">
-      <c r="F768" s="12"/>
-      <c r="G768" s="12"/>
-      <c r="H768" s="12"/>
+      <c r="F768" s="13"/>
+      <c r="G768" s="13"/>
+      <c r="H768" s="13"/>
     </row>
     <row r="769">
-      <c r="F769" s="12"/>
-      <c r="G769" s="12"/>
-      <c r="H769" s="12"/>
+      <c r="F769" s="13"/>
+      <c r="G769" s="13"/>
+      <c r="H769" s="13"/>
     </row>
     <row r="770">
-      <c r="F770" s="12"/>
-      <c r="G770" s="12"/>
-      <c r="H770" s="12"/>
+      <c r="F770" s="13"/>
+      <c r="G770" s="13"/>
+      <c r="H770" s="13"/>
     </row>
     <row r="771">
-      <c r="F771" s="12"/>
-      <c r="G771" s="12"/>
-      <c r="H771" s="12"/>
+      <c r="F771" s="13"/>
+      <c r="G771" s="13"/>
+      <c r="H771" s="13"/>
     </row>
     <row r="772">
-      <c r="F772" s="12"/>
-      <c r="G772" s="12"/>
-      <c r="H772" s="12"/>
+      <c r="F772" s="13"/>
+      <c r="G772" s="13"/>
+      <c r="H772" s="13"/>
     </row>
     <row r="773">
-      <c r="F773" s="12"/>
-      <c r="G773" s="12"/>
-      <c r="H773" s="12"/>
+      <c r="F773" s="13"/>
+      <c r="G773" s="13"/>
+      <c r="H773" s="13"/>
     </row>
     <row r="774">
-      <c r="F774" s="12"/>
-      <c r="G774" s="12"/>
-      <c r="H774" s="12"/>
+      <c r="F774" s="13"/>
+      <c r="G774" s="13"/>
+      <c r="H774" s="13"/>
     </row>
     <row r="775">
-      <c r="F775" s="12"/>
-      <c r="G775" s="12"/>
-      <c r="H775" s="12"/>
+      <c r="F775" s="13"/>
+      <c r="G775" s="13"/>
+      <c r="H775" s="13"/>
     </row>
     <row r="776">
-      <c r="F776" s="12"/>
-      <c r="G776" s="12"/>
-      <c r="H776" s="12"/>
+      <c r="F776" s="13"/>
+      <c r="G776" s="13"/>
+      <c r="H776" s="13"/>
     </row>
     <row r="777">
-      <c r="F777" s="12"/>
-      <c r="G777" s="12"/>
-      <c r="H777" s="12"/>
+      <c r="F777" s="13"/>
+      <c r="G777" s="13"/>
+      <c r="H777" s="13"/>
     </row>
     <row r="778">
-      <c r="F778" s="12"/>
-      <c r="G778" s="12"/>
-      <c r="H778" s="12"/>
+      <c r="F778" s="13"/>
+      <c r="G778" s="13"/>
+      <c r="H778" s="13"/>
     </row>
     <row r="779">
-      <c r="F779" s="12"/>
-      <c r="G779" s="12"/>
-      <c r="H779" s="12"/>
+      <c r="F779" s="13"/>
+      <c r="G779" s="13"/>
+      <c r="H779" s="13"/>
     </row>
     <row r="780">
-      <c r="F780" s="12"/>
-      <c r="G780" s="12"/>
-      <c r="H780" s="12"/>
+      <c r="F780" s="13"/>
+      <c r="G780" s="13"/>
+      <c r="H780" s="13"/>
     </row>
     <row r="781">
-      <c r="F781" s="12"/>
-      <c r="G781" s="12"/>
-      <c r="H781" s="12"/>
+      <c r="F781" s="13"/>
+      <c r="G781" s="13"/>
+      <c r="H781" s="13"/>
     </row>
     <row r="782">
-      <c r="F782" s="12"/>
-      <c r="G782" s="12"/>
-      <c r="H782" s="12"/>
+      <c r="F782" s="13"/>
+      <c r="G782" s="13"/>
+      <c r="H782" s="13"/>
     </row>
     <row r="783">
-      <c r="F783" s="12"/>
-      <c r="G783" s="12"/>
-      <c r="H783" s="12"/>
+      <c r="F783" s="13"/>
+      <c r="G783" s="13"/>
+      <c r="H783" s="13"/>
     </row>
     <row r="784">
-      <c r="F784" s="12"/>
-      <c r="G784" s="12"/>
-      <c r="H784" s="12"/>
+      <c r="F784" s="13"/>
+      <c r="G784" s="13"/>
+      <c r="H784" s="13"/>
     </row>
     <row r="785">
-      <c r="F785" s="12"/>
-      <c r="G785" s="12"/>
-      <c r="H785" s="12"/>
+      <c r="F785" s="13"/>
+      <c r="G785" s="13"/>
+      <c r="H785" s="13"/>
     </row>
     <row r="786">
-      <c r="F786" s="12"/>
-      <c r="G786" s="12"/>
-      <c r="H786" s="12"/>
+      <c r="F786" s="13"/>
+      <c r="G786" s="13"/>
+      <c r="H786" s="13"/>
     </row>
     <row r="787">
-      <c r="F787" s="12"/>
-      <c r="G787" s="12"/>
-      <c r="H787" s="12"/>
+      <c r="F787" s="13"/>
+      <c r="G787" s="13"/>
+      <c r="H787" s="13"/>
     </row>
     <row r="788">
-      <c r="F788" s="12"/>
-      <c r="G788" s="12"/>
-      <c r="H788" s="12"/>
+      <c r="F788" s="13"/>
+      <c r="G788" s="13"/>
+      <c r="H788" s="13"/>
     </row>
     <row r="789">
-      <c r="F789" s="12"/>
-      <c r="G789" s="12"/>
-      <c r="H789" s="12"/>
+      <c r="F789" s="13"/>
+      <c r="G789" s="13"/>
+      <c r="H789" s="13"/>
     </row>
     <row r="790">
-      <c r="F790" s="12"/>
-      <c r="G790" s="12"/>
-      <c r="H790" s="12"/>
+      <c r="F790" s="13"/>
+      <c r="G790" s="13"/>
+      <c r="H790" s="13"/>
     </row>
     <row r="791">
-      <c r="F791" s="12"/>
-      <c r="G791" s="12"/>
-      <c r="H791" s="12"/>
+      <c r="F791" s="13"/>
+      <c r="G791" s="13"/>
+      <c r="H791" s="13"/>
     </row>
     <row r="792">
-      <c r="F792" s="12"/>
-      <c r="G792" s="12"/>
-      <c r="H792" s="12"/>
+      <c r="F792" s="13"/>
+      <c r="G792" s="13"/>
+      <c r="H792" s="13"/>
     </row>
     <row r="793">
-      <c r="F793" s="12"/>
-      <c r="G793" s="12"/>
-      <c r="H793" s="12"/>
+      <c r="F793" s="13"/>
+      <c r="G793" s="13"/>
+      <c r="H793" s="13"/>
     </row>
     <row r="794">
-      <c r="F794" s="12"/>
-      <c r="G794" s="12"/>
-      <c r="H794" s="12"/>
+      <c r="F794" s="13"/>
+      <c r="G794" s="13"/>
+      <c r="H794" s="13"/>
     </row>
     <row r="795">
-      <c r="F795" s="12"/>
-      <c r="G795" s="12"/>
-      <c r="H795" s="12"/>
+      <c r="F795" s="13"/>
+      <c r="G795" s="13"/>
+      <c r="H795" s="13"/>
     </row>
     <row r="796">
-      <c r="F796" s="12"/>
-      <c r="G796" s="12"/>
-      <c r="H796" s="12"/>
+      <c r="F796" s="13"/>
+      <c r="G796" s="13"/>
+      <c r="H796" s="13"/>
     </row>
     <row r="797">
-      <c r="F797" s="12"/>
-      <c r="G797" s="12"/>
-      <c r="H797" s="12"/>
+      <c r="F797" s="13"/>
+      <c r="G797" s="13"/>
+      <c r="H797" s="13"/>
     </row>
     <row r="798">
-      <c r="F798" s="12"/>
-      <c r="G798" s="12"/>
-      <c r="H798" s="12"/>
+      <c r="F798" s="13"/>
+      <c r="G798" s="13"/>
+      <c r="H798" s="13"/>
     </row>
     <row r="799">
-      <c r="F799" s="12"/>
-      <c r="G799" s="12"/>
-      <c r="H799" s="12"/>
+      <c r="F799" s="13"/>
+      <c r="G799" s="13"/>
+      <c r="H799" s="13"/>
     </row>
     <row r="800">
-      <c r="F800" s="12"/>
-      <c r="G800" s="12"/>
-      <c r="H800" s="12"/>
+      <c r="F800" s="13"/>
+      <c r="G800" s="13"/>
+      <c r="H800" s="13"/>
     </row>
     <row r="801">
-      <c r="F801" s="12"/>
-      <c r="G801" s="12"/>
-      <c r="H801" s="12"/>
+      <c r="F801" s="13"/>
+      <c r="G801" s="13"/>
+      <c r="H801" s="13"/>
     </row>
     <row r="802">
-      <c r="F802" s="12"/>
-      <c r="G802" s="12"/>
-      <c r="H802" s="12"/>
+      <c r="F802" s="13"/>
+      <c r="G802" s="13"/>
+      <c r="H802" s="13"/>
     </row>
     <row r="803">
-      <c r="F803" s="12"/>
-      <c r="G803" s="12"/>
-      <c r="H803" s="12"/>
+      <c r="F803" s="13"/>
+      <c r="G803" s="13"/>
+      <c r="H803" s="13"/>
     </row>
     <row r="804">
-      <c r="F804" s="12"/>
-      <c r="G804" s="12"/>
-      <c r="H804" s="12"/>
+      <c r="F804" s="13"/>
+      <c r="G804" s="13"/>
+      <c r="H804" s="13"/>
     </row>
     <row r="805">
-      <c r="F805" s="12"/>
-      <c r="G805" s="12"/>
-      <c r="H805" s="12"/>
+      <c r="F805" s="13"/>
+      <c r="G805" s="13"/>
+      <c r="H805" s="13"/>
     </row>
     <row r="806">
-      <c r="F806" s="12"/>
-      <c r="G806" s="12"/>
-      <c r="H806" s="12"/>
+      <c r="F806" s="13"/>
+      <c r="G806" s="13"/>
+      <c r="H806" s="13"/>
     </row>
     <row r="807">
-      <c r="F807" s="12"/>
-      <c r="G807" s="12"/>
-      <c r="H807" s="12"/>
+      <c r="F807" s="13"/>
+      <c r="G807" s="13"/>
+      <c r="H807" s="13"/>
     </row>
     <row r="808">
-      <c r="F808" s="12"/>
-      <c r="G808" s="12"/>
-      <c r="H808" s="12"/>
+      <c r="F808" s="13"/>
+      <c r="G808" s="13"/>
+      <c r="H808" s="13"/>
     </row>
     <row r="809">
-      <c r="F809" s="12"/>
-      <c r="G809" s="12"/>
-      <c r="H809" s="12"/>
+      <c r="F809" s="13"/>
+      <c r="G809" s="13"/>
+      <c r="H809" s="13"/>
     </row>
     <row r="810">
-      <c r="F810" s="12"/>
-      <c r="G810" s="12"/>
-      <c r="H810" s="12"/>
+      <c r="F810" s="13"/>
+      <c r="G810" s="13"/>
+      <c r="H810" s="13"/>
     </row>
     <row r="811">
-      <c r="F811" s="12"/>
-      <c r="G811" s="12"/>
-      <c r="H811" s="12"/>
+      <c r="F811" s="13"/>
+      <c r="G811" s="13"/>
+      <c r="H811" s="13"/>
     </row>
     <row r="812">
-      <c r="F812" s="12"/>
-      <c r="G812" s="12"/>
-      <c r="H812" s="12"/>
+      <c r="F812" s="13"/>
+      <c r="G812" s="13"/>
+      <c r="H812" s="13"/>
     </row>
     <row r="813">
-      <c r="F813" s="12"/>
-      <c r="G813" s="12"/>
-      <c r="H813" s="12"/>
+      <c r="F813" s="13"/>
+      <c r="G813" s="13"/>
+      <c r="H813" s="13"/>
     </row>
     <row r="814">
-      <c r="F814" s="12"/>
-      <c r="G814" s="12"/>
-      <c r="H814" s="12"/>
+      <c r="F814" s="13"/>
+      <c r="G814" s="13"/>
+      <c r="H814" s="13"/>
     </row>
     <row r="815">
-      <c r="F815" s="12"/>
-      <c r="G815" s="12"/>
-      <c r="H815" s="12"/>
+      <c r="F815" s="13"/>
+      <c r="G815" s="13"/>
+      <c r="H815" s="13"/>
     </row>
     <row r="816">
-      <c r="F816" s="12"/>
-      <c r="G816" s="12"/>
-      <c r="H816" s="12"/>
+      <c r="F816" s="13"/>
+      <c r="G816" s="13"/>
+      <c r="H816" s="13"/>
     </row>
     <row r="817">
-      <c r="F817" s="12"/>
-      <c r="G817" s="12"/>
-      <c r="H817" s="12"/>
+      <c r="F817" s="13"/>
+      <c r="G817" s="13"/>
+      <c r="H817" s="13"/>
     </row>
     <row r="818">
-      <c r="F818" s="12"/>
-      <c r="G818" s="12"/>
-      <c r="H818" s="12"/>
+      <c r="F818" s="13"/>
+      <c r="G818" s="13"/>
+      <c r="H818" s="13"/>
     </row>
     <row r="819">
-      <c r="F819" s="12"/>
-      <c r="G819" s="12"/>
-      <c r="H819" s="12"/>
+      <c r="F819" s="13"/>
+      <c r="G819" s="13"/>
+      <c r="H819" s="13"/>
     </row>
     <row r="820">
-      <c r="F820" s="12"/>
-      <c r="G820" s="12"/>
-      <c r="H820" s="12"/>
+      <c r="F820" s="13"/>
+      <c r="G820" s="13"/>
+      <c r="H820" s="13"/>
     </row>
     <row r="821">
-      <c r="F821" s="12"/>
-      <c r="G821" s="12"/>
-      <c r="H821" s="12"/>
+      <c r="F821" s="13"/>
+      <c r="G821" s="13"/>
+      <c r="H821" s="13"/>
     </row>
     <row r="822">
-      <c r="F822" s="12"/>
-      <c r="G822" s="12"/>
-      <c r="H822" s="12"/>
+      <c r="F822" s="13"/>
+      <c r="G822" s="13"/>
+      <c r="H822" s="13"/>
     </row>
     <row r="823">
-      <c r="F823" s="12"/>
-      <c r="G823" s="12"/>
-      <c r="H823" s="12"/>
+      <c r="F823" s="13"/>
+      <c r="G823" s="13"/>
+      <c r="H823" s="13"/>
     </row>
     <row r="824">
-      <c r="F824" s="12"/>
-      <c r="G824" s="12"/>
-      <c r="H824" s="12"/>
+      <c r="F824" s="13"/>
+      <c r="G824" s="13"/>
+      <c r="H824" s="13"/>
     </row>
     <row r="825">
-      <c r="F825" s="12"/>
-      <c r="G825" s="12"/>
-      <c r="H825" s="12"/>
+      <c r="F825" s="13"/>
+      <c r="G825" s="13"/>
+      <c r="H825" s="13"/>
     </row>
     <row r="826">
-      <c r="F826" s="12"/>
-      <c r="G826" s="12"/>
-      <c r="H826" s="12"/>
+      <c r="F826" s="13"/>
+      <c r="G826" s="13"/>
+      <c r="H826" s="13"/>
     </row>
     <row r="827">
-      <c r="F827" s="12"/>
-      <c r="G827" s="12"/>
-      <c r="H827" s="12"/>
+      <c r="F827" s="13"/>
+      <c r="G827" s="13"/>
+      <c r="H827" s="13"/>
     </row>
     <row r="828">
-      <c r="F828" s="12"/>
-      <c r="G828" s="12"/>
-      <c r="H828" s="12"/>
+      <c r="F828" s="13"/>
+      <c r="G828" s="13"/>
+      <c r="H828" s="13"/>
     </row>
     <row r="829">
-      <c r="F829" s="12"/>
-      <c r="G829" s="12"/>
-      <c r="H829" s="12"/>
+      <c r="F829" s="13"/>
+      <c r="G829" s="13"/>
+      <c r="H829" s="13"/>
     </row>
     <row r="830">
-      <c r="F830" s="12"/>
-      <c r="G830" s="12"/>
-      <c r="H830" s="12"/>
+      <c r="F830" s="13"/>
+      <c r="G830" s="13"/>
+      <c r="H830" s="13"/>
     </row>
     <row r="831">
-      <c r="F831" s="12"/>
-      <c r="G831" s="12"/>
-      <c r="H831" s="12"/>
+      <c r="F831" s="13"/>
+      <c r="G831" s="13"/>
+      <c r="H831" s="13"/>
     </row>
     <row r="832">
-      <c r="F832" s="12"/>
-      <c r="G832" s="12"/>
-      <c r="H832" s="12"/>
+      <c r="F832" s="13"/>
+      <c r="G832" s="13"/>
+      <c r="H832" s="13"/>
     </row>
     <row r="833">
-      <c r="F833" s="12"/>
-      <c r="G833" s="12"/>
-      <c r="H833" s="12"/>
+      <c r="F833" s="13"/>
+      <c r="G833" s="13"/>
+      <c r="H833" s="13"/>
     </row>
     <row r="834">
-      <c r="F834" s="12"/>
-      <c r="G834" s="12"/>
-      <c r="H834" s="12"/>
+      <c r="F834" s="13"/>
+      <c r="G834" s="13"/>
+      <c r="H834" s="13"/>
     </row>
     <row r="835">
-      <c r="F835" s="12"/>
-      <c r="G835" s="12"/>
-      <c r="H835" s="12"/>
+      <c r="F835" s="13"/>
+      <c r="G835" s="13"/>
+      <c r="H835" s="13"/>
     </row>
     <row r="836">
-      <c r="F836" s="12"/>
-      <c r="G836" s="12"/>
-      <c r="H836" s="12"/>
+      <c r="F836" s="13"/>
+      <c r="G836" s="13"/>
+      <c r="H836" s="13"/>
     </row>
     <row r="837">
-      <c r="F837" s="12"/>
-      <c r="G837" s="12"/>
-      <c r="H837" s="12"/>
+      <c r="F837" s="13"/>
+      <c r="G837" s="13"/>
+      <c r="H837" s="13"/>
     </row>
     <row r="838">
-      <c r="F838" s="12"/>
-      <c r="G838" s="12"/>
-      <c r="H838" s="12"/>
+      <c r="F838" s="13"/>
+      <c r="G838" s="13"/>
+      <c r="H838" s="13"/>
     </row>
     <row r="839">
-      <c r="F839" s="12"/>
-      <c r="G839" s="12"/>
-      <c r="H839" s="12"/>
+      <c r="F839" s="13"/>
+      <c r="G839" s="13"/>
+      <c r="H839" s="13"/>
     </row>
     <row r="840">
-      <c r="F840" s="12"/>
-      <c r="G840" s="12"/>
-      <c r="H840" s="12"/>
+      <c r="F840" s="13"/>
+      <c r="G840" s="13"/>
+      <c r="H840" s="13"/>
     </row>
     <row r="841">
-      <c r="F841" s="12"/>
-      <c r="G841" s="12"/>
-      <c r="H841" s="12"/>
+      <c r="F841" s="13"/>
+      <c r="G841" s="13"/>
+      <c r="H841" s="13"/>
     </row>
     <row r="842">
-      <c r="F842" s="12"/>
-      <c r="G842" s="12"/>
-      <c r="H842" s="12"/>
+      <c r="F842" s="13"/>
+      <c r="G842" s="13"/>
+      <c r="H842" s="13"/>
     </row>
     <row r="843">
-      <c r="F843" s="12"/>
-      <c r="G843" s="12"/>
-      <c r="H843" s="12"/>
+      <c r="F843" s="13"/>
+      <c r="G843" s="13"/>
+      <c r="H843" s="13"/>
     </row>
     <row r="844">
-      <c r="F844" s="12"/>
-      <c r="G844" s="12"/>
-      <c r="H844" s="12"/>
+      <c r="F844" s="13"/>
+      <c r="G844" s="13"/>
+      <c r="H844" s="13"/>
     </row>
     <row r="845">
-      <c r="F845" s="12"/>
-      <c r="G845" s="12"/>
-      <c r="H845" s="12"/>
+      <c r="F845" s="13"/>
+      <c r="G845" s="13"/>
+      <c r="H845" s="13"/>
     </row>
     <row r="846">
-      <c r="F846" s="12"/>
-      <c r="G846" s="12"/>
-      <c r="H846" s="12"/>
+      <c r="F846" s="13"/>
+      <c r="G846" s="13"/>
+      <c r="H846" s="13"/>
     </row>
     <row r="847">
-      <c r="F847" s="12"/>
-      <c r="G847" s="12"/>
-      <c r="H847" s="12"/>
+      <c r="F847" s="13"/>
+      <c r="G847" s="13"/>
+      <c r="H847" s="13"/>
     </row>
     <row r="848">
-      <c r="F848" s="12"/>
-      <c r="G848" s="12"/>
-      <c r="H848" s="12"/>
+      <c r="F848" s="13"/>
+      <c r="G848" s="13"/>
+      <c r="H848" s="13"/>
     </row>
     <row r="849">
-      <c r="F849" s="12"/>
-      <c r="G849" s="12"/>
-      <c r="H849" s="12"/>
+      <c r="F849" s="13"/>
+      <c r="G849" s="13"/>
+      <c r="H849" s="13"/>
     </row>
     <row r="850">
-      <c r="F850" s="12"/>
-      <c r="G850" s="12"/>
-      <c r="H850" s="12"/>
+      <c r="F850" s="13"/>
+      <c r="G850" s="13"/>
+      <c r="H850" s="13"/>
     </row>
     <row r="851">
-      <c r="F851" s="12"/>
-      <c r="G851" s="12"/>
-      <c r="H851" s="12"/>
+      <c r="F851" s="13"/>
+      <c r="G851" s="13"/>
+      <c r="H851" s="13"/>
     </row>
     <row r="852">
-      <c r="F852" s="12"/>
-      <c r="G852" s="12"/>
-      <c r="H852" s="12"/>
+      <c r="F852" s="13"/>
+      <c r="G852" s="13"/>
+      <c r="H852" s="13"/>
     </row>
     <row r="853">
-      <c r="F853" s="12"/>
-      <c r="G853" s="12"/>
-      <c r="H853" s="12"/>
+      <c r="F853" s="13"/>
+      <c r="G853" s="13"/>
+      <c r="H853" s="13"/>
     </row>
     <row r="854">
-      <c r="F854" s="12"/>
-      <c r="G854" s="12"/>
-      <c r="H854" s="12"/>
+      <c r="F854" s="13"/>
+      <c r="G854" s="13"/>
+      <c r="H854" s="13"/>
     </row>
     <row r="855">
-      <c r="F855" s="12"/>
-      <c r="G855" s="12"/>
-      <c r="H855" s="12"/>
+      <c r="F855" s="13"/>
+      <c r="G855" s="13"/>
+      <c r="H855" s="13"/>
     </row>
     <row r="856">
-      <c r="F856" s="12"/>
-      <c r="G856" s="12"/>
-      <c r="H856" s="12"/>
+      <c r="F856" s="13"/>
+      <c r="G856" s="13"/>
+      <c r="H856" s="13"/>
     </row>
     <row r="857">
-      <c r="F857" s="12"/>
-      <c r="G857" s="12"/>
-      <c r="H857" s="12"/>
+      <c r="F857" s="13"/>
+      <c r="G857" s="13"/>
+      <c r="H857" s="13"/>
     </row>
     <row r="858">
-      <c r="F858" s="12"/>
-      <c r="G858" s="12"/>
-      <c r="H858" s="12"/>
+      <c r="F858" s="13"/>
+      <c r="G858" s="13"/>
+      <c r="H858" s="13"/>
     </row>
     <row r="859">
-      <c r="F859" s="12"/>
-      <c r="G859" s="12"/>
-      <c r="H859" s="12"/>
+      <c r="F859" s="13"/>
+      <c r="G859" s="13"/>
+      <c r="H859" s="13"/>
     </row>
     <row r="860">
-      <c r="F860" s="12"/>
-      <c r="G860" s="12"/>
-      <c r="H860" s="12"/>
+      <c r="F860" s="13"/>
+      <c r="G860" s="13"/>
+      <c r="H860" s="13"/>
     </row>
     <row r="861">
-      <c r="F861" s="12"/>
-      <c r="G861" s="12"/>
-      <c r="H861" s="12"/>
+      <c r="F861" s="13"/>
+      <c r="G861" s="13"/>
+      <c r="H861" s="13"/>
     </row>
     <row r="862">
-      <c r="F862" s="12"/>
-      <c r="G862" s="12"/>
-      <c r="H862" s="12"/>
+      <c r="F862" s="13"/>
+      <c r="G862" s="13"/>
+      <c r="H862" s="13"/>
     </row>
     <row r="863">
-      <c r="F863" s="12"/>
-      <c r="G863" s="12"/>
-      <c r="H863" s="12"/>
+      <c r="F863" s="13"/>
+      <c r="G863" s="13"/>
+      <c r="H863" s="13"/>
     </row>
     <row r="864">
-      <c r="F864" s="12"/>
-      <c r="G864" s="12"/>
-      <c r="H864" s="12"/>
+      <c r="F864" s="13"/>
+      <c r="G864" s="13"/>
+      <c r="H864" s="13"/>
     </row>
     <row r="865">
-      <c r="F865" s="12"/>
-      <c r="G865" s="12"/>
-      <c r="H865" s="12"/>
+      <c r="F865" s="13"/>
+      <c r="G865" s="13"/>
+      <c r="H865" s="13"/>
     </row>
     <row r="866">
-      <c r="F866" s="12"/>
-      <c r="G866" s="12"/>
-      <c r="H866" s="12"/>
+      <c r="F866" s="13"/>
+      <c r="G866" s="13"/>
+      <c r="H866" s="13"/>
     </row>
     <row r="867">
-      <c r="F867" s="12"/>
-      <c r="G867" s="12"/>
-      <c r="H867" s="12"/>
+      <c r="F867" s="13"/>
+      <c r="G867" s="13"/>
+      <c r="H867" s="13"/>
     </row>
     <row r="868">
-      <c r="F868" s="12"/>
-      <c r="G868" s="12"/>
-      <c r="H868" s="12"/>
+      <c r="F868" s="13"/>
+      <c r="G868" s="13"/>
+      <c r="H868" s="13"/>
     </row>
     <row r="869">
-      <c r="F869" s="12"/>
-      <c r="G869" s="12"/>
-      <c r="H869" s="12"/>
+      <c r="F869" s="13"/>
+      <c r="G869" s="13"/>
+      <c r="H869" s="13"/>
     </row>
     <row r="870">
-      <c r="F870" s="12"/>
-      <c r="G870" s="12"/>
-      <c r="H870" s="12"/>
+      <c r="F870" s="13"/>
+      <c r="G870" s="13"/>
+      <c r="H870" s="13"/>
     </row>
     <row r="871">
-      <c r="F871" s="12"/>
-      <c r="G871" s="12"/>
-      <c r="H871" s="12"/>
+      <c r="F871" s="13"/>
+      <c r="G871" s="13"/>
+      <c r="H871" s="13"/>
     </row>
     <row r="872">
-      <c r="F872" s="12"/>
-      <c r="G872" s="12"/>
-      <c r="H872" s="12"/>
+      <c r="F872" s="13"/>
+      <c r="G872" s="13"/>
+      <c r="H872" s="13"/>
     </row>
     <row r="873">
-      <c r="F873" s="12"/>
-      <c r="G873" s="12"/>
-      <c r="H873" s="12"/>
+      <c r="F873" s="13"/>
+      <c r="G873" s="13"/>
+      <c r="H873" s="13"/>
     </row>
     <row r="874">
-      <c r="F874" s="12"/>
-      <c r="G874" s="12"/>
-      <c r="H874" s="12"/>
+      <c r="F874" s="13"/>
+      <c r="G874" s="13"/>
+      <c r="H874" s="13"/>
     </row>
     <row r="875">
-      <c r="F875" s="12"/>
-      <c r="G875" s="12"/>
-      <c r="H875" s="12"/>
+      <c r="F875" s="13"/>
+      <c r="G875" s="13"/>
+      <c r="H875" s="13"/>
     </row>
     <row r="876">
-      <c r="F876" s="12"/>
-      <c r="G876" s="12"/>
-      <c r="H876" s="12"/>
+      <c r="F876" s="13"/>
+      <c r="G876" s="13"/>
+      <c r="H876" s="13"/>
     </row>
     <row r="877">
-      <c r="F877" s="12"/>
-      <c r="G877" s="12"/>
-      <c r="H877" s="12"/>
+      <c r="F877" s="13"/>
+      <c r="G877" s="13"/>
+      <c r="H877" s="13"/>
     </row>
     <row r="878">
-      <c r="F878" s="12"/>
-      <c r="G878" s="12"/>
-      <c r="H878" s="12"/>
+      <c r="F878" s="13"/>
+      <c r="G878" s="13"/>
+      <c r="H878" s="13"/>
     </row>
     <row r="879">
-      <c r="F879" s="12"/>
-      <c r="G879" s="12"/>
-      <c r="H879" s="12"/>
+      <c r="F879" s="13"/>
+      <c r="G879" s="13"/>
+      <c r="H879" s="13"/>
     </row>
     <row r="880">
-      <c r="F880" s="12"/>
-      <c r="G880" s="12"/>
-      <c r="H880" s="12"/>
+      <c r="F880" s="13"/>
+      <c r="G880" s="13"/>
+      <c r="H880" s="13"/>
     </row>
     <row r="881">
-      <c r="F881" s="12"/>
-      <c r="G881" s="12"/>
-      <c r="H881" s="12"/>
+      <c r="F881" s="13"/>
+      <c r="G881" s="13"/>
+      <c r="H881" s="13"/>
     </row>
     <row r="882">
-      <c r="F882" s="12"/>
-      <c r="G882" s="12"/>
-      <c r="H882" s="12"/>
+      <c r="F882" s="13"/>
+      <c r="G882" s="13"/>
+      <c r="H882" s="13"/>
     </row>
     <row r="883">
-      <c r="F883" s="12"/>
-      <c r="G883" s="12"/>
-      <c r="H883" s="12"/>
+      <c r="F883" s="13"/>
+      <c r="G883" s="13"/>
+      <c r="H883" s="13"/>
     </row>
     <row r="884">
-      <c r="F884" s="12"/>
-      <c r="G884" s="12"/>
-      <c r="H884" s="12"/>
+      <c r="F884" s="13"/>
+      <c r="G884" s="13"/>
+      <c r="H884" s="13"/>
     </row>
     <row r="885">
-      <c r="F885" s="12"/>
-      <c r="G885" s="12"/>
-      <c r="H885" s="12"/>
+      <c r="F885" s="13"/>
+      <c r="G885" s="13"/>
+      <c r="H885" s="13"/>
     </row>
     <row r="886">
-      <c r="F886" s="12"/>
-      <c r="G886" s="12"/>
-      <c r="H886" s="12"/>
+      <c r="F886" s="13"/>
+      <c r="G886" s="13"/>
+      <c r="H886" s="13"/>
     </row>
     <row r="887">
-      <c r="F887" s="12"/>
-      <c r="G887" s="12"/>
-      <c r="H887" s="12"/>
+      <c r="F887" s="13"/>
+      <c r="G887" s="13"/>
+      <c r="H887" s="13"/>
     </row>
     <row r="888">
-      <c r="F888" s="12"/>
-      <c r="G888" s="12"/>
-      <c r="H888" s="12"/>
+      <c r="F888" s="13"/>
+      <c r="G888" s="13"/>
+      <c r="H888" s="13"/>
     </row>
     <row r="889">
-      <c r="F889" s="12"/>
-      <c r="G889" s="12"/>
-      <c r="H889" s="12"/>
+      <c r="F889" s="13"/>
+      <c r="G889" s="13"/>
+      <c r="H889" s="13"/>
     </row>
     <row r="890">
-      <c r="F890" s="12"/>
-      <c r="G890" s="12"/>
-      <c r="H890" s="12"/>
+      <c r="F890" s="13"/>
+      <c r="G890" s="13"/>
+      <c r="H890" s="13"/>
     </row>
     <row r="891">
-      <c r="F891" s="12"/>
-      <c r="G891" s="12"/>
-      <c r="H891" s="12"/>
+      <c r="F891" s="13"/>
+      <c r="G891" s="13"/>
+      <c r="H891" s="13"/>
     </row>
     <row r="892">
-      <c r="F892" s="12"/>
-      <c r="G892" s="12"/>
-      <c r="H892" s="12"/>
+      <c r="F892" s="13"/>
+      <c r="G892" s="13"/>
+      <c r="H892" s="13"/>
     </row>
     <row r="893">
-      <c r="F893" s="12"/>
-      <c r="G893" s="12"/>
-      <c r="H893" s="12"/>
+      <c r="F893" s="13"/>
+      <c r="G893" s="13"/>
+      <c r="H893" s="13"/>
     </row>
     <row r="894">
-      <c r="F894" s="12"/>
-      <c r="G894" s="12"/>
-      <c r="H894" s="12"/>
+      <c r="F894" s="13"/>
+      <c r="G894" s="13"/>
+      <c r="H894" s="13"/>
     </row>
     <row r="895">
-      <c r="F895" s="12"/>
-      <c r="G895" s="12"/>
-      <c r="H895" s="12"/>
+      <c r="F895" s="13"/>
+      <c r="G895" s="13"/>
+      <c r="H895" s="13"/>
     </row>
     <row r="896">
-      <c r="F896" s="12"/>
-      <c r="G896" s="12"/>
-      <c r="H896" s="12"/>
+      <c r="F896" s="13"/>
+      <c r="G896" s="13"/>
+      <c r="H896" s="13"/>
     </row>
     <row r="897">
-      <c r="F897" s="12"/>
-      <c r="G897" s="12"/>
-      <c r="H897" s="12"/>
+      <c r="F897" s="13"/>
+      <c r="G897" s="13"/>
+      <c r="H897" s="13"/>
     </row>
     <row r="898">
-      <c r="F898" s="12"/>
-      <c r="G898" s="12"/>
-      <c r="H898" s="12"/>
+      <c r="F898" s="13"/>
+      <c r="G898" s="13"/>
+      <c r="H898" s="13"/>
     </row>
     <row r="899">
-      <c r="F899" s="12"/>
-      <c r="G899" s="12"/>
-      <c r="H899" s="12"/>
+      <c r="F899" s="13"/>
+      <c r="G899" s="13"/>
+      <c r="H899" s="13"/>
     </row>
     <row r="900">
-      <c r="F900" s="12"/>
-      <c r="G900" s="12"/>
-      <c r="H900" s="12"/>
+      <c r="F900" s="13"/>
+      <c r="G900" s="13"/>
+      <c r="H900" s="13"/>
     </row>
     <row r="901">
-      <c r="F901" s="12"/>
-      <c r="G901" s="12"/>
-      <c r="H901" s="12"/>
+      <c r="F901" s="13"/>
+      <c r="G901" s="13"/>
+      <c r="H901" s="13"/>
     </row>
     <row r="902">
-      <c r="F902" s="12"/>
-      <c r="G902" s="12"/>
-      <c r="H902" s="12"/>
+      <c r="F902" s="13"/>
+      <c r="G902" s="13"/>
+      <c r="H902" s="13"/>
     </row>
     <row r="903">
-      <c r="F903" s="12"/>
-      <c r="G903" s="12"/>
-      <c r="H903" s="12"/>
+      <c r="F903" s="13"/>
+      <c r="G903" s="13"/>
+      <c r="H903" s="13"/>
     </row>
     <row r="904">
-      <c r="F904" s="12"/>
-      <c r="G904" s="12"/>
-      <c r="H904" s="12"/>
+      <c r="F904" s="13"/>
+      <c r="G904" s="13"/>
+      <c r="H904" s="13"/>
     </row>
     <row r="905">
-      <c r="F905" s="12"/>
-      <c r="G905" s="12"/>
-      <c r="H905" s="12"/>
+      <c r="F905" s="13"/>
+      <c r="G905" s="13"/>
+      <c r="H905" s="13"/>
     </row>
     <row r="906">
-      <c r="F906" s="12"/>
-      <c r="G906" s="12"/>
-      <c r="H906" s="12"/>
+      <c r="F906" s="13"/>
+      <c r="G906" s="13"/>
+      <c r="H906" s="13"/>
     </row>
     <row r="907">
-      <c r="F907" s="12"/>
-      <c r="G907" s="12"/>
-      <c r="H907" s="12"/>
+      <c r="F907" s="13"/>
+      <c r="G907" s="13"/>
+      <c r="H907" s="13"/>
     </row>
     <row r="908">
-      <c r="F908" s="12"/>
-      <c r="G908" s="12"/>
-      <c r="H908" s="12"/>
+      <c r="F908" s="13"/>
+      <c r="G908" s="13"/>
+      <c r="H908" s="13"/>
     </row>
     <row r="909">
-      <c r="F909" s="12"/>
-      <c r="G909" s="12"/>
-      <c r="H909" s="12"/>
+      <c r="F909" s="13"/>
+      <c r="G909" s="13"/>
+      <c r="H909" s="13"/>
     </row>
     <row r="910">
-      <c r="F910" s="12"/>
-      <c r="G910" s="12"/>
-      <c r="H910" s="12"/>
+      <c r="F910" s="13"/>
+      <c r="G910" s="13"/>
+      <c r="H910" s="13"/>
     </row>
     <row r="911">
-      <c r="F911" s="12"/>
-      <c r="G911" s="12"/>
-      <c r="H911" s="12"/>
+      <c r="F911" s="13"/>
+      <c r="G911" s="13"/>
+      <c r="H911" s="13"/>
     </row>
     <row r="912">
-      <c r="F912" s="12"/>
-      <c r="G912" s="12"/>
-      <c r="H912" s="12"/>
+      <c r="F912" s="13"/>
+      <c r="G912" s="13"/>
+      <c r="H912" s="13"/>
     </row>
     <row r="913">
-      <c r="F913" s="12"/>
-      <c r="G913" s="12"/>
-      <c r="H913" s="12"/>
+      <c r="F913" s="13"/>
+      <c r="G913" s="13"/>
+      <c r="H913" s="13"/>
     </row>
     <row r="914">
-      <c r="F914" s="12"/>
-      <c r="G914" s="12"/>
-      <c r="H914" s="12"/>
+      <c r="F914" s="13"/>
+      <c r="G914" s="13"/>
+      <c r="H914" s="13"/>
     </row>
     <row r="915">
-      <c r="F915" s="12"/>
-      <c r="G915" s="12"/>
-      <c r="H915" s="12"/>
+      <c r="F915" s="13"/>
+      <c r="G915" s="13"/>
+      <c r="H915" s="13"/>
     </row>
     <row r="916">
-      <c r="F916" s="12"/>
-      <c r="G916" s="12"/>
-      <c r="H916" s="12"/>
+      <c r="F916" s="13"/>
+      <c r="G916" s="13"/>
+      <c r="H916" s="13"/>
     </row>
     <row r="917">
-      <c r="F917" s="12"/>
-      <c r="G917" s="12"/>
-      <c r="H917" s="12"/>
+      <c r="F917" s="13"/>
+      <c r="G917" s="13"/>
+      <c r="H917" s="13"/>
     </row>
     <row r="918">
-      <c r="F918" s="12"/>
-      <c r="G918" s="12"/>
-      <c r="H918" s="12"/>
+      <c r="F918" s="13"/>
+      <c r="G918" s="13"/>
+      <c r="H918" s="13"/>
     </row>
     <row r="919">
-      <c r="F919" s="12"/>
-      <c r="G919" s="12"/>
-      <c r="H919" s="12"/>
+      <c r="F919" s="13"/>
+      <c r="G919" s="13"/>
+      <c r="H919" s="13"/>
     </row>
     <row r="920">
-      <c r="F920" s="12"/>
-      <c r="G920" s="12"/>
-      <c r="H920" s="12"/>
+      <c r="F920" s="13"/>
+      <c r="G920" s="13"/>
+      <c r="H920" s="13"/>
     </row>
     <row r="921">
-      <c r="F921" s="12"/>
-      <c r="G921" s="12"/>
-      <c r="H921" s="12"/>
+      <c r="F921" s="13"/>
+      <c r="G921" s="13"/>
+      <c r="H921" s="13"/>
     </row>
     <row r="922">
-      <c r="F922" s="12"/>
-      <c r="G922" s="12"/>
-      <c r="H922" s="12"/>
+      <c r="F922" s="13"/>
+      <c r="G922" s="13"/>
+      <c r="H922" s="13"/>
     </row>
     <row r="923">
-      <c r="F923" s="12"/>
-      <c r="G923" s="12"/>
-      <c r="H923" s="12"/>
+      <c r="F923" s="13"/>
+      <c r="G923" s="13"/>
+      <c r="H923" s="13"/>
     </row>
     <row r="924">
-      <c r="F924" s="12"/>
-      <c r="G924" s="12"/>
-      <c r="H924" s="12"/>
+      <c r="F924" s="13"/>
+      <c r="G924" s="13"/>
+      <c r="H924" s="13"/>
     </row>
     <row r="925">
-      <c r="F925" s="12"/>
-      <c r="G925" s="12"/>
-      <c r="H925" s="12"/>
+      <c r="F925" s="13"/>
+      <c r="G925" s="13"/>
+      <c r="H925" s="13"/>
     </row>
     <row r="926">
-      <c r="F926" s="12"/>
-      <c r="G926" s="12"/>
-      <c r="H926" s="12"/>
+      <c r="F926" s="13"/>
+      <c r="G926" s="13"/>
+      <c r="H926" s="13"/>
     </row>
     <row r="927">
-      <c r="F927" s="12"/>
-      <c r="G927" s="12"/>
-      <c r="H927" s="12"/>
+      <c r="F927" s="13"/>
+      <c r="G927" s="13"/>
+      <c r="H927" s="13"/>
     </row>
     <row r="928">
-      <c r="F928" s="12"/>
-      <c r="G928" s="12"/>
-      <c r="H928" s="12"/>
+      <c r="F928" s="13"/>
+      <c r="G928" s="13"/>
+      <c r="H928" s="13"/>
     </row>
     <row r="929">
-      <c r="F929" s="12"/>
-      <c r="G929" s="12"/>
-      <c r="H929" s="12"/>
+      <c r="F929" s="13"/>
+      <c r="G929" s="13"/>
+      <c r="H929" s="13"/>
     </row>
     <row r="930">
-      <c r="F930" s="12"/>
-      <c r="G930" s="12"/>
-      <c r="H930" s="12"/>
+      <c r="F930" s="13"/>
+      <c r="G930" s="13"/>
+      <c r="H930" s="13"/>
     </row>
     <row r="931">
-      <c r="F931" s="12"/>
-      <c r="G931" s="12"/>
-      <c r="H931" s="12"/>
+      <c r="F931" s="13"/>
+      <c r="G931" s="13"/>
+      <c r="H931" s="13"/>
     </row>
     <row r="932">
-      <c r="F932" s="12"/>
-      <c r="G932" s="12"/>
-      <c r="H932" s="12"/>
+      <c r="F932" s="13"/>
+      <c r="G932" s="13"/>
+      <c r="H932" s="13"/>
     </row>
     <row r="933">
-      <c r="F933" s="12"/>
-      <c r="G933" s="12"/>
-      <c r="H933" s="12"/>
+      <c r="F933" s="13"/>
+      <c r="G933" s="13"/>
+      <c r="H933" s="13"/>
     </row>
     <row r="934">
-      <c r="F934" s="12"/>
-      <c r="G934" s="12"/>
-      <c r="H934" s="12"/>
+      <c r="F934" s="13"/>
+      <c r="G934" s="13"/>
+      <c r="H934" s="13"/>
     </row>
     <row r="935">
-      <c r="F935" s="12"/>
-      <c r="G935" s="12"/>
-      <c r="H935" s="12"/>
+      <c r="F935" s="13"/>
+      <c r="G935" s="13"/>
+      <c r="H935" s="13"/>
     </row>
     <row r="936">
-      <c r="F936" s="12"/>
-      <c r="G936" s="12"/>
-      <c r="H936" s="12"/>
+      <c r="F936" s="13"/>
+      <c r="G936" s="13"/>
+      <c r="H936" s="13"/>
     </row>
     <row r="937">
-      <c r="F937" s="12"/>
-      <c r="G937" s="12"/>
-      <c r="H937" s="12"/>
+      <c r="F937" s="13"/>
+      <c r="G937" s="13"/>
+      <c r="H937" s="13"/>
     </row>
     <row r="938">
-      <c r="F938" s="12"/>
-      <c r="G938" s="12"/>
-      <c r="H938" s="12"/>
+      <c r="F938" s="13"/>
+      <c r="G938" s="13"/>
+      <c r="H938" s="13"/>
     </row>
     <row r="939">
-      <c r="F939" s="12"/>
-      <c r="G939" s="12"/>
-      <c r="H939" s="12"/>
+      <c r="F939" s="13"/>
+      <c r="G939" s="13"/>
+      <c r="H939" s="13"/>
     </row>
     <row r="940">
-      <c r="F940" s="12"/>
-      <c r="G940" s="12"/>
-      <c r="H940" s="12"/>
+      <c r="F940" s="13"/>
+      <c r="G940" s="13"/>
+      <c r="H940" s="13"/>
     </row>
     <row r="941">
-      <c r="F941" s="12"/>
-      <c r="G941" s="12"/>
-      <c r="H941" s="12"/>
+      <c r="F941" s="13"/>
+      <c r="G941" s="13"/>
+      <c r="H941" s="13"/>
     </row>
     <row r="942">
-      <c r="F942" s="12"/>
-      <c r="G942" s="12"/>
-      <c r="H942" s="12"/>
+      <c r="F942" s="13"/>
+      <c r="G942" s="13"/>
+      <c r="H942" s="13"/>
     </row>
     <row r="943">
-      <c r="F943" s="12"/>
-      <c r="G943" s="12"/>
-      <c r="H943" s="12"/>
+      <c r="F943" s="13"/>
+      <c r="G943" s="13"/>
+      <c r="H943" s="13"/>
     </row>
     <row r="944">
-      <c r="F944" s="12"/>
-      <c r="G944" s="12"/>
-      <c r="H944" s="12"/>
+      <c r="F944" s="13"/>
+      <c r="G944" s="13"/>
+      <c r="H944" s="13"/>
     </row>
     <row r="945">
-      <c r="F945" s="12"/>
-      <c r="G945" s="12"/>
-      <c r="H945" s="12"/>
+      <c r="F945" s="13"/>
+      <c r="G945" s="13"/>
+      <c r="H945" s="13"/>
     </row>
     <row r="946">
-      <c r="F946" s="12"/>
-      <c r="G946" s="12"/>
-      <c r="H946" s="12"/>
+      <c r="F946" s="13"/>
+      <c r="G946" s="13"/>
+      <c r="H946" s="13"/>
     </row>
     <row r="947">
-      <c r="F947" s="12"/>
-      <c r="G947" s="12"/>
-      <c r="H947" s="12"/>
+      <c r="F947" s="13"/>
+      <c r="G947" s="13"/>
+      <c r="H947" s="13"/>
     </row>
     <row r="948">
-      <c r="F948" s="12"/>
-      <c r="G948" s="12"/>
-      <c r="H948" s="12"/>
+      <c r="F948" s="13"/>
+      <c r="G948" s="13"/>
+      <c r="H948" s="13"/>
     </row>
     <row r="949">
-      <c r="F949" s="12"/>
-      <c r="G949" s="12"/>
-      <c r="H949" s="12"/>
+      <c r="F949" s="13"/>
+      <c r="G949" s="13"/>
+      <c r="H949" s="13"/>
     </row>
     <row r="950">
-      <c r="F950" s="12"/>
-      <c r="G950" s="12"/>
-      <c r="H950" s="12"/>
+      <c r="F950" s="13"/>
+      <c r="G950" s="13"/>
+      <c r="H950" s="13"/>
     </row>
     <row r="951">
-      <c r="F951" s="12"/>
-      <c r="G951" s="12"/>
-      <c r="H951" s="12"/>
+      <c r="F951" s="13"/>
+      <c r="G951" s="13"/>
+      <c r="H951" s="13"/>
     </row>
     <row r="952">
-      <c r="F952" s="12"/>
-      <c r="G952" s="12"/>
-      <c r="H952" s="12"/>
+      <c r="F952" s="13"/>
+      <c r="G952" s="13"/>
+      <c r="H952" s="13"/>
     </row>
     <row r="953">
-      <c r="F953" s="12"/>
-      <c r="G953" s="12"/>
-      <c r="H953" s="12"/>
+      <c r="F953" s="13"/>
+      <c r="G953" s="13"/>
+      <c r="H953" s="13"/>
     </row>
     <row r="954">
-      <c r="F954" s="12"/>
-      <c r="G954" s="12"/>
-      <c r="H954" s="12"/>
+      <c r="F954" s="13"/>
+      <c r="G954" s="13"/>
+      <c r="H954" s="13"/>
     </row>
     <row r="955">
-      <c r="F955" s="12"/>
-      <c r="G955" s="12"/>
-      <c r="H955" s="12"/>
+      <c r="F955" s="13"/>
+      <c r="G955" s="13"/>
+      <c r="H955" s="13"/>
     </row>
     <row r="956">
-      <c r="F956" s="12"/>
-      <c r="G956" s="12"/>
-      <c r="H956" s="12"/>
+      <c r="F956" s="13"/>
+      <c r="G956" s="13"/>
+      <c r="H956" s="13"/>
     </row>
     <row r="957">
-      <c r="F957" s="12"/>
-      <c r="G957" s="12"/>
-      <c r="H957" s="12"/>
+      <c r="F957" s="13"/>
+      <c r="G957" s="13"/>
+      <c r="H957" s="13"/>
     </row>
     <row r="958">
-      <c r="F958" s="12"/>
-      <c r="G958" s="12"/>
-      <c r="H958" s="12"/>
+      <c r="F958" s="13"/>
+      <c r="G958" s="13"/>
+      <c r="H958" s="13"/>
     </row>
     <row r="959">
-      <c r="F959" s="12"/>
-      <c r="G959" s="12"/>
-      <c r="H959" s="12"/>
+      <c r="F959" s="13"/>
+      <c r="G959" s="13"/>
+      <c r="H959" s="13"/>
     </row>
     <row r="960">
-      <c r="F960" s="12"/>
-      <c r="G960" s="12"/>
-      <c r="H960" s="12"/>
+      <c r="F960" s="13"/>
+      <c r="G960" s="13"/>
+      <c r="H960" s="13"/>
     </row>
     <row r="961">
-      <c r="F961" s="12"/>
-      <c r="G961" s="12"/>
-      <c r="H961" s="12"/>
+      <c r="F961" s="13"/>
+      <c r="G961" s="13"/>
+      <c r="H961" s="13"/>
     </row>
     <row r="962">
-      <c r="F962" s="12"/>
-      <c r="G962" s="12"/>
-      <c r="H962" s="12"/>
+      <c r="F962" s="13"/>
+      <c r="G962" s="13"/>
+      <c r="H962" s="13"/>
     </row>
     <row r="963">
-      <c r="F963" s="12"/>
-      <c r="G963" s="12"/>
-      <c r="H963" s="12"/>
+      <c r="F963" s="13"/>
+      <c r="G963" s="13"/>
+      <c r="H963" s="13"/>
     </row>
     <row r="964">
-      <c r="F964" s="12"/>
-      <c r="G964" s="12"/>
-      <c r="H964" s="12"/>
+      <c r="F964" s="13"/>
+      <c r="G964" s="13"/>
+      <c r="H964" s="13"/>
     </row>
     <row r="965">
-      <c r="F965" s="12"/>
-      <c r="G965" s="12"/>
-      <c r="H965" s="12"/>
+      <c r="F965" s="13"/>
+      <c r="G965" s="13"/>
+      <c r="H965" s="13"/>
     </row>
     <row r="966">
-      <c r="F966" s="12"/>
-      <c r="G966" s="12"/>
-      <c r="H966" s="12"/>
+      <c r="F966" s="13"/>
+      <c r="G966" s="13"/>
+      <c r="H966" s="13"/>
     </row>
     <row r="967">
-      <c r="F967" s="12"/>
-      <c r="G967" s="12"/>
-      <c r="H967" s="12"/>
+      <c r="F967" s="13"/>
+      <c r="G967" s="13"/>
+      <c r="H967" s="13"/>
     </row>
     <row r="968">
-      <c r="F968" s="12"/>
-      <c r="G968" s="12"/>
-      <c r="H968" s="12"/>
+      <c r="F968" s="13"/>
+      <c r="G968" s="13"/>
+      <c r="H968" s="13"/>
     </row>
     <row r="969">
-      <c r="F969" s="12"/>
-      <c r="G969" s="12"/>
-      <c r="H969" s="12"/>
+      <c r="F969" s="13"/>
+      <c r="G969" s="13"/>
+      <c r="H969" s="13"/>
     </row>
     <row r="970">
-      <c r="F970" s="12"/>
-      <c r="G970" s="12"/>
-      <c r="H970" s="12"/>
+      <c r="F970" s="13"/>
+      <c r="G970" s="13"/>
+      <c r="H970" s="13"/>
     </row>
     <row r="971">
-      <c r="F971" s="12"/>
-      <c r="G971" s="12"/>
-      <c r="H971" s="12"/>
+      <c r="F971" s="13"/>
+      <c r="G971" s="13"/>
+      <c r="H971" s="13"/>
     </row>
     <row r="972">
-      <c r="F972" s="12"/>
-      <c r="G972" s="12"/>
-      <c r="H972" s="12"/>
+      <c r="F972" s="13"/>
+      <c r="G972" s="13"/>
+      <c r="H972" s="13"/>
     </row>
     <row r="973">
-      <c r="F973" s="12"/>
-      <c r="G973" s="12"/>
-      <c r="H973" s="12"/>
+      <c r="F973" s="13"/>
+      <c r="G973" s="13"/>
+      <c r="H973" s="13"/>
     </row>
     <row r="974">
-      <c r="F974" s="12"/>
-      <c r="G974" s="12"/>
-      <c r="H974" s="12"/>
+      <c r="F974" s="13"/>
+      <c r="G974" s="13"/>
+      <c r="H974" s="13"/>
     </row>
     <row r="975">
-      <c r="F975" s="12"/>
-      <c r="G975" s="12"/>
-      <c r="H975" s="12"/>
+      <c r="F975" s="13"/>
+      <c r="G975" s="13"/>
+      <c r="H975" s="13"/>
     </row>
     <row r="976">
-      <c r="F976" s="12"/>
-      <c r="G976" s="12"/>
-      <c r="H976" s="12"/>
+      <c r="F976" s="13"/>
+      <c r="G976" s="13"/>
+      <c r="H976" s="13"/>
     </row>
     <row r="977">
-      <c r="F977" s="12"/>
-      <c r="G977" s="12"/>
-      <c r="H977" s="12"/>
+      <c r="F977" s="13"/>
+      <c r="G977" s="13"/>
+      <c r="H977" s="13"/>
     </row>
     <row r="978">
-      <c r="F978" s="12"/>
-      <c r="G978" s="12"/>
-      <c r="H978" s="12"/>
+      <c r="F978" s="13"/>
+      <c r="G978" s="13"/>
+      <c r="H978" s="13"/>
     </row>
     <row r="979">
-      <c r="F979" s="12"/>
-      <c r="G979" s="12"/>
-      <c r="H979" s="12"/>
+      <c r="F979" s="13"/>
+      <c r="G979" s="13"/>
+      <c r="H979" s="13"/>
     </row>
     <row r="980">
-      <c r="F980" s="12"/>
-      <c r="G980" s="12"/>
-      <c r="H980" s="12"/>
+      <c r="F980" s="13"/>
+      <c r="G980" s="13"/>
+      <c r="H980" s="13"/>
     </row>
     <row r="981">
-      <c r="F981" s="12"/>
-      <c r="G981" s="12"/>
-      <c r="H981" s="12"/>
+      <c r="F981" s="13"/>
+      <c r="G981" s="13"/>
+      <c r="H981" s="13"/>
     </row>
     <row r="982">
-      <c r="F982" s="12"/>
-      <c r="G982" s="12"/>
-      <c r="H982" s="12"/>
+      <c r="F982" s="13"/>
+      <c r="G982" s="13"/>
+      <c r="H982" s="13"/>
     </row>
     <row r="983">
-      <c r="F983" s="12"/>
-      <c r="G983" s="12"/>
-      <c r="H983" s="12"/>
+      <c r="F983" s="13"/>
+      <c r="G983" s="13"/>
+      <c r="H983" s="13"/>
     </row>
     <row r="984">
-      <c r="F984" s="12"/>
-      <c r="G984" s="12"/>
-      <c r="H984" s="12"/>
+      <c r="F984" s="13"/>
+      <c r="G984" s="13"/>
+      <c r="H984" s="13"/>
     </row>
     <row r="985">
-      <c r="F985" s="12"/>
-      <c r="G985" s="12"/>
-      <c r="H985" s="12"/>
+      <c r="F985" s="13"/>
+      <c r="G985" s="13"/>
+      <c r="H985" s="13"/>
     </row>
     <row r="986">
-      <c r="F986" s="12"/>
-      <c r="G986" s="12"/>
-      <c r="H986" s="12"/>
+      <c r="F986" s="13"/>
+      <c r="G986" s="13"/>
+      <c r="H986" s="13"/>
     </row>
     <row r="987">
-      <c r="F987" s="12"/>
-      <c r="G987" s="12"/>
-      <c r="H987" s="12"/>
+      <c r="F987" s="13"/>
+      <c r="G987" s="13"/>
+      <c r="H987" s="13"/>
     </row>
     <row r="988">
-      <c r="F988" s="12"/>
-      <c r="G988" s="12"/>
-      <c r="H988" s="12"/>
+      <c r="F988" s="13"/>
+      <c r="G988" s="13"/>
+      <c r="H988" s="13"/>
     </row>
     <row r="989">
-      <c r="F989" s="12"/>
-      <c r="G989" s="12"/>
-      <c r="H989" s="12"/>
+      <c r="F989" s="13"/>
+      <c r="G989" s="13"/>
+      <c r="H989" s="13"/>
     </row>
     <row r="990">
-      <c r="F990" s="12"/>
-      <c r="G990" s="12"/>
-      <c r="H990" s="12"/>
+      <c r="F990" s="13"/>
+      <c r="G990" s="13"/>
+      <c r="H990" s="13"/>
     </row>
     <row r="991">
-      <c r="F991" s="12"/>
-      <c r="G991" s="12"/>
-      <c r="H991" s="12"/>
+      <c r="F991" s="13"/>
+      <c r="G991" s="13"/>
+      <c r="H991" s="13"/>
     </row>
     <row r="992">
-      <c r="F992" s="12"/>
-      <c r="G992" s="12"/>
-      <c r="H992" s="12"/>
+      <c r="F992" s="13"/>
+      <c r="G992" s="13"/>
+      <c r="H992" s="13"/>
     </row>
     <row r="993">
-      <c r="F993" s="12"/>
-      <c r="G993" s="12"/>
-      <c r="H993" s="12"/>
+      <c r="F993" s="13"/>
+      <c r="G993" s="13"/>
+      <c r="H993" s="13"/>
     </row>
     <row r="994">
-      <c r="F994" s="12"/>
-      <c r="G994" s="12"/>
-      <c r="H994" s="12"/>
+      <c r="F994" s="13"/>
+      <c r="G994" s="13"/>
+      <c r="H994" s="13"/>
     </row>
     <row r="995">
-      <c r="F995" s="12"/>
-      <c r="G995" s="12"/>
-      <c r="H995" s="12"/>
+      <c r="F995" s="13"/>
+      <c r="G995" s="13"/>
+      <c r="H995" s="13"/>
     </row>
     <row r="996">
-      <c r="F996" s="12"/>
-      <c r="G996" s="12"/>
-      <c r="H996" s="12"/>
+      <c r="F996" s="13"/>
+      <c r="G996" s="13"/>
+      <c r="H996" s="13"/>
     </row>
     <row r="997">
-      <c r="F997" s="12"/>
-      <c r="G997" s="12"/>
-      <c r="H997" s="12"/>
+      <c r="F997" s="13"/>
+      <c r="G997" s="13"/>
+      <c r="H997" s="13"/>
     </row>
     <row r="998">
-      <c r="F998" s="12"/>
-      <c r="G998" s="12"/>
-      <c r="H998" s="12"/>
+      <c r="F998" s="13"/>
+      <c r="G998" s="13"/>
+      <c r="H998" s="13"/>
     </row>
     <row r="999">
-      <c r="F999" s="12"/>
-      <c r="G999" s="12"/>
-      <c r="H999" s="12"/>
+      <c r="F999" s="13"/>
+      <c r="G999" s="13"/>
+      <c r="H999" s="13"/>
     </row>
     <row r="1000">
-      <c r="F1000" s="12"/>
-      <c r="G1000" s="12"/>
-      <c r="H1000" s="12"/>
+      <c r="F1000" s="13"/>
+      <c r="G1000" s="13"/>
+      <c r="H1000" s="13"/>
     </row>
     <row r="1001">
-      <c r="F1001" s="12"/>
-      <c r="G1001" s="12"/>
-      <c r="H1001" s="12"/>
+      <c r="F1001" s="13"/>
+      <c r="G1001" s="13"/>
+      <c r="H1001" s="13"/>
     </row>
     <row r="1002">
-      <c r="F1002" s="12"/>
-      <c r="G1002" s="12"/>
-      <c r="H1002" s="12"/>
+      <c r="F1002" s="13"/>
+      <c r="G1002" s="13"/>
+      <c r="H1002" s="13"/>
     </row>
     <row r="1003">
-      <c r="F1003" s="12"/>
-      <c r="G1003" s="12"/>
-      <c r="H1003" s="12"/>
+      <c r="F1003" s="13"/>
+      <c r="G1003" s="13"/>
+      <c r="H1003" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12109,19 +12534,19 @@
       <c r="A2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="14">
         <v>18.000937</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="15">
         <v>931.494</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <f>B2+B3</f>
         <v>19.008762</v>
       </c>
@@ -12130,13 +12555,13 @@
       <c r="A3" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="14">
         <v>1.007825</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="17">
         <f>B4+B5</f>
         <v>19.005669</v>
       </c>
@@ -12145,13 +12570,13 @@
       <c r="A4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="14">
         <v>4.002603</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="17">
         <f>H2-H3</f>
         <v>0.003093</v>
       </c>
@@ -12160,13 +12585,13 @@
       <c r="A5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>15.003066</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="17">
         <f>H4*E2</f>
         <v>2.881110942</v>
       </c>
@@ -12222,31 +12647,31 @@
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="18" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>91</v>
       </c>
       <c r="B3" s="6">
         <v>18.0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="18">
-        <f>B3*B7</f>
-        <v>8.82</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="D3" s="19">
+        <f>B3*B8</f>
+        <v>10.62</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>91</v>
       </c>
       <c r="G3" s="6">
         <v>18.0</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="15" t="s">
         <v>93</v>
       </c>
       <c r="I3" s="5">
@@ -12255,26 +12680,26 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="6">
         <v>9.0</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>95</v>
       </c>
       <c r="D4" s="5">
         <f>D3*(B5/(B5+B3))</f>
-        <v>0.4642105263</v>
-      </c>
-      <c r="F4" s="13" t="s">
+        <v>0.5589473684</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>94</v>
       </c>
       <c r="G4" s="6">
         <v>9.0</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="15" t="s">
         <v>96</v>
       </c>
       <c r="I4" s="5">
@@ -12283,26 +12708,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6">
         <v>1.0</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>93</v>
       </c>
       <c r="D5" s="5">
         <f>(B3*B5)/(B3+B5)</f>
         <v>0.9473684211</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="6">
         <v>1.0</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="15" t="s">
         <v>97</v>
       </c>
       <c r="I5" s="5">
@@ -12311,26 +12736,26 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="6">
         <v>1.0</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D6" s="5">
         <f>B4*B4*B6*B6*D5</f>
         <v>76.73684211</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>98</v>
       </c>
       <c r="G6" s="6">
         <v>1.0</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="15" t="s">
         <v>99</v>
       </c>
       <c r="I6" s="5">
@@ -12339,28 +12764,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>100</v>
       </c>
       <c r="B7" s="6">
-        <v>0.49</v>
-      </c>
-      <c r="C7" s="14" t="s">
+        <v>590.0</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="5">
         <f>D6^(1/3)</f>
         <v>4.249468761</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="G7" s="3">
-        <v>0.8472874403</v>
+      <c r="G7" s="11">
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="6">
+        <f>B7/1000</f>
+        <v>0.59</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="5">
@@ -12369,45 +12801,45 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="20">
+      <c r="C10" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="21">
         <f>(D4/D8)^(3/2)</f>
-        <v>0.8472874403</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="I10" s="20">
+        <v>1.119475688</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" s="21">
         <f>I6*G7^(2/3)</f>
-        <v>0.4642105263</v>
+        <v>0.281449922</v>
       </c>
     </row>
     <row r="11">
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="21">
         <f>((G3+G5)/G5)*I10</f>
-        <v>8.82</v>
+        <v>5.347548517</v>
       </c>
     </row>
     <row r="12">
-      <c r="H12" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I12" s="20">
+      <c r="H12" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="21">
         <f>I11/G3</f>
-        <v>0.49</v>
+        <v>0.2970860287</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:I1"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
   </mergeCells>
@@ -12439,12 +12871,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="10"/>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
@@ -12455,38 +12887,42 @@
       <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="E2" s="22"/>
+      <c r="H2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I2" s="6">
         <v>0.1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>91</v>
       </c>
       <c r="B3" s="6">
         <v>18.0</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="22">
+      <c r="D3" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="23">
         <f>8.617333*(10^(-11))</f>
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="F3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" s="6">
         <v>0.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="6">
@@ -12496,134 +12932,162 @@
       <c r="D4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6">
         <v>1.0</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>119</v>
+      <c r="D5" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="24">
+        <f>$I$2+(0*$I$3)</f>
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="19">
+        <f t="shared" ref="G5:G14" si="1">F5*1000</f>
+        <v>100</v>
+      </c>
+      <c r="H5" s="5">
+        <f t="shared" ref="H5:H14" si="2">SQRT(F5)*EXP((-F5)/$E$9)</f>
+        <v>0.01738022584</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" ref="I5:I14" si="3">H5/MAX($H$5:$H$14)</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" ref="J5:J14" si="4">EXP(-31.29*$B$4*$B$6*SQRT($E$10/G5))</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" ref="K5:K14" si="5">J5/MAX($J$5:$J$14)</f>
+        <v>0.000000007250961684</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" ref="L5:L14" si="6">H5*J5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <f t="shared" ref="M5:M14" si="7">L5/MAX($L$5:$L$14)</f>
+        <v>0.001778765444</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="6">
         <v>1.0</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" s="10">
-        <f>$G$2+(0*$G$3)</f>
-        <v>0.1</v>
-      </c>
-      <c r="G6" s="12">
-        <f t="shared" ref="G6:G15" si="1">F6*1000</f>
-        <v>100</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" ref="H6:H15" si="2">SQRT(F6)*EXP((-F6)/$E$9)</f>
-        <v>0.08038716363</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" ref="I6:I15" si="3">H6/MAX($H$6:$H$15)</f>
+      <c r="D6" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="24">
+        <f>$I$2+(1*$I$3)</f>
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="19">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="H6" s="5">
+        <f t="shared" si="2"/>
+        <v>0.001350908171</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="3"/>
+        <v>0.07772673287</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="4"/>
+        <v>0.000000003824915564</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="5"/>
+        <v>0.00002223247428</v>
+      </c>
+      <c r="L6" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <f t="shared" si="7"/>
+        <v>0.4239174416</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="24">
+        <f>$I$2+(2*$I$3)</f>
+        <v>0.3</v>
+      </c>
+      <c r="G7" s="19">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="2"/>
+        <v>0.00009093412105</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="3"/>
+        <v>0.005232044848</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="4"/>
+        <v>0.000000134041575</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="5"/>
+        <v>0.000779122001</v>
+      </c>
+      <c r="L7" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <f t="shared" si="7"/>
         <v>1</v>
-      </c>
-      <c r="J6" s="4">
-        <f t="shared" ref="J6:J15" si="4">EXP(-31.29*$B$4*$B$6*SQRT($E$10/G6))</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
-        <f t="shared" ref="K6:K15" si="5">J6/MAX($J$6:$J$15)</f>
-        <v>0.000000007250961684</v>
-      </c>
-      <c r="L6" s="4">
-        <f t="shared" ref="L6:L15" si="6">H6*J6</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <f t="shared" ref="M6:M15" si="7">L6/MAX($L$6:$L$15)</f>
-        <v>0.00002814590485</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.8472874403</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="10">
-        <f>$G$2+(1*$G$3)</f>
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="2"/>
-        <v>0.02889937221</v>
-      </c>
-      <c r="I7" s="4">
-        <f t="shared" si="3"/>
-        <v>0.3595023248</v>
-      </c>
-      <c r="J7" s="4">
-        <f t="shared" si="4"/>
-        <v>0.000000003824915564</v>
-      </c>
-      <c r="K7" s="4">
-        <f t="shared" si="5"/>
-        <v>0.00002223247428</v>
-      </c>
-      <c r="L7" s="4">
-        <f t="shared" si="6"/>
-        <v>0.0000000001105376586</v>
-      </c>
-      <c r="M7" s="4">
-        <f t="shared" si="7"/>
-        <v>0.0310248083</v>
       </c>
     </row>
     <row r="8">
@@ -12634,41 +13098,41 @@
       <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="10">
-        <f>$G$2+(2*$G$3)</f>
-        <v>0.3</v>
-      </c>
-      <c r="G8" s="12">
-        <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="H8" s="4">
-        <f t="shared" si="2"/>
-        <v>0.008997476965</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="3"/>
-        <v>0.1119267873</v>
-      </c>
-      <c r="J8" s="4">
-        <f t="shared" si="4"/>
-        <v>0.000000134041575</v>
-      </c>
-      <c r="K8" s="4">
-        <f t="shared" si="5"/>
-        <v>0.000779122001</v>
-      </c>
-      <c r="L8" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000001206035983</v>
-      </c>
-      <c r="M8" s="4">
-        <f t="shared" si="7"/>
-        <v>0.3385003416</v>
+      <c r="F8" s="24">
+        <f>$I$2+(3*$I$3)</f>
+        <v>0.4</v>
+      </c>
+      <c r="G8" s="19">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="H8" s="5">
+        <f t="shared" si="2"/>
+        <v>0.000005771007743</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="3"/>
+        <v>0.0003320444623</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="4"/>
+        <v>0.000001116901392</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="5"/>
+        <v>0.006492033887</v>
+      </c>
+      <c r="L8" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" si="7"/>
+        <v>0.5288105288</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>93</v>
       </c>
       <c r="B9" s="5">
@@ -12676,48 +13140,48 @@
         <v>0.9473684211</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="23">
+      <c r="D9" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="17">
         <f>E3*(1000000000)*B7</f>
-        <v>0.0730135802</v>
-      </c>
-      <c r="F9" s="10">
-        <f>$G$2+(3*$G$3)</f>
-        <v>0.4</v>
-      </c>
-      <c r="G9" s="12">
-        <f t="shared" si="1"/>
-        <v>400</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" si="2"/>
-        <v>0.002641051179</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" si="3"/>
-        <v>0.03285414063</v>
-      </c>
-      <c r="J9" s="4">
-        <f t="shared" si="4"/>
-        <v>0.000001116901392</v>
-      </c>
-      <c r="K9" s="4">
-        <f t="shared" si="5"/>
-        <v>0.006492033887</v>
-      </c>
-      <c r="L9" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000002949793737</v>
-      </c>
-      <c r="M9" s="4">
-        <f t="shared" si="7"/>
-        <v>0.8279240432</v>
+        <v>0.034469332</v>
+      </c>
+      <c r="F9" s="24">
+        <f>$I$2+(4*$I$3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="19">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="2"/>
+        <v>0.0000003546190637</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="3"/>
+        <v>0.00002040359355</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="4"/>
+        <v>0.000004746599896</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="5"/>
+        <v>0.02758980122</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <f t="shared" si="7"/>
+        <v>0.1380951127</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B10" s="5">
@@ -12725,321 +13189,625 @@
         <v>76.73684211</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="23">
+      <c r="D10" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="17">
         <f>(B3*B5)/(B3+B5)</f>
         <v>0.9473684211</v>
       </c>
-      <c r="F10" s="10">
-        <f>$G$2+(4*$G$3)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G10" s="12">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="H10" s="4">
-        <f t="shared" si="2"/>
-        <v>0.0007506172297</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="3"/>
-        <v>0.00933752599</v>
-      </c>
-      <c r="J10" s="4">
-        <f t="shared" si="4"/>
-        <v>0.000004746599896</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="5"/>
-        <v>0.02758980122</v>
-      </c>
-      <c r="L10" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000003562879664</v>
-      </c>
-      <c r="M10" s="4">
-        <f t="shared" si="7"/>
-        <v>1</v>
+      <c r="F10" s="24">
+        <f>$I$2+(5*$I$3)</f>
+        <v>0.6</v>
+      </c>
+      <c r="G10" s="19">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="2"/>
+        <v>0.0000000213505033</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="3"/>
+        <v>0.000001228436471</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="4"/>
+        <v>0.00001381097886</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="5"/>
+        <v>0.08027686551</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <f t="shared" si="7"/>
+        <v>0.02419168853</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="15" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="5">
         <f>B10^(1/3)</f>
         <v>4.249468761</v>
       </c>
-      <c r="F11" s="10">
-        <f>$G$2+(5*$G$3)</f>
-        <v>0.6</v>
-      </c>
-      <c r="G11" s="12">
-        <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="H11" s="4">
-        <f t="shared" si="2"/>
-        <v>0.0002090238571</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="3"/>
-        <v>0.002600214358</v>
-      </c>
-      <c r="J11" s="4">
-        <f t="shared" si="4"/>
-        <v>0.00001381097886</v>
-      </c>
-      <c r="K11" s="4">
-        <f t="shared" si="5"/>
-        <v>0.08027686551</v>
-      </c>
-      <c r="L11" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000002886824072</v>
-      </c>
-      <c r="M11" s="4">
-        <f t="shared" si="7"/>
-        <v>0.8102502313</v>
+      <c r="F11" s="24">
+        <f>$I$2+(6*$I$3)</f>
+        <v>0.7</v>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="2"/>
+        <v>0.000000001267467778</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="3"/>
+        <v>0.00000007292585205</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="4"/>
+        <v>0.00003167540127</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="5"/>
+        <v>0.1841145333</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <f t="shared" si="7"/>
+        <v>0.003293765355</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>124</v>
+      <c r="A12" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="B12" s="5">
         <f>0.122*B11</f>
         <v>0.5184351889</v>
       </c>
-      <c r="F12" s="10">
-        <f>$G$2+(6*$G$3)</f>
-        <v>0.7</v>
-      </c>
-      <c r="G12" s="12">
-        <f t="shared" si="1"/>
-        <v>700</v>
-      </c>
-      <c r="H12" s="4">
-        <f t="shared" si="2"/>
-        <v>0.00005739260766</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="3"/>
-        <v>0.0007139523907</v>
-      </c>
-      <c r="J12" s="4">
-        <f t="shared" si="4"/>
-        <v>0.00003167540127</v>
-      </c>
-      <c r="K12" s="4">
-        <f t="shared" si="5"/>
-        <v>0.1841145333</v>
-      </c>
-      <c r="L12" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000001817933878</v>
-      </c>
-      <c r="M12" s="4">
-        <f t="shared" si="7"/>
-        <v>0.5102428509</v>
+      <c r="F12" s="24">
+        <f>$I$2+(7*$I$3)</f>
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="19">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="H12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="3"/>
+        <v>0.000000004284823141</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="4"/>
+        <v>0.00006184590176</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="5"/>
+        <v>0.3594817707</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <f t="shared" si="7"/>
+        <v>0.0003778616763</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>125</v>
+      <c r="A13" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="B13" s="5">
         <f>B10^(1/6)</f>
         <v>2.061423964</v>
       </c>
-      <c r="F13" s="10">
-        <f>$G$2+(7*$G$3)</f>
-        <v>0.8</v>
-      </c>
-      <c r="G13" s="12">
-        <f t="shared" si="1"/>
-        <v>800</v>
-      </c>
-      <c r="H13" s="4">
-        <f t="shared" si="2"/>
-        <v>0.00001559691253</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="3"/>
-        <v>0.0001940224262</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" si="4"/>
-        <v>0.00006184590176</v>
-      </c>
-      <c r="K13" s="4">
-        <f t="shared" si="5"/>
-        <v>0.3594817707</v>
-      </c>
-      <c r="L13" s="4">
-        <f t="shared" si="6"/>
-        <v>0.0000000009646051198</v>
-      </c>
-      <c r="M13" s="4">
-        <f t="shared" si="7"/>
-        <v>0.2707374963</v>
+      <c r="F13" s="24">
+        <f>$I$2+(8*$I$3)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="19">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="3"/>
+        <v>0.0000000002497839778</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="4"/>
+        <v>0.0001076489723</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="5"/>
+        <v>0.6257139451</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <f t="shared" si="7"/>
+        <v>0.00003834100436</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>126</v>
+      <c r="A14" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="B14" s="5">
         <f>0.237*B13</f>
         <v>0.4885574796</v>
       </c>
-      <c r="F14" s="10">
-        <f>$G$2+(8*$G$3)</f>
-        <v>0.9</v>
-      </c>
-      <c r="G14" s="12">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-      <c r="H14" s="4">
-        <f t="shared" si="2"/>
-        <v>0.000004205344735</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="3"/>
-        <v>0.00005231363497</v>
-      </c>
-      <c r="J14" s="4">
-        <f t="shared" si="4"/>
-        <v>0.0001076489723</v>
-      </c>
-      <c r="K14" s="4">
-        <f t="shared" si="5"/>
-        <v>0.6257139451</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="6"/>
-        <v>0.0000000004527010388</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="7"/>
-        <v>0.1270604347</v>
+      <c r="F14" s="24">
+        <f>$I$2+(9*$I$3)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="19">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="4"/>
+        <v>0.0001720418302</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="7"/>
+        <v>0.000003549946531</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="12"/>
-      <c r="F15" s="10">
-        <f>$G$2+(9*$G$3)</f>
-        <v>1</v>
-      </c>
-      <c r="G15" s="12">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="H15" s="4">
-        <f t="shared" si="2"/>
-        <v>0.000001126852451</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="3"/>
-        <v>0.00001401781578</v>
-      </c>
-      <c r="J15" s="4">
-        <f t="shared" si="4"/>
-        <v>0.0001720418302</v>
-      </c>
-      <c r="K15" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="L15" s="4">
-        <f t="shared" si="6"/>
-        <v>0.000000000193865758</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="7"/>
-        <v>0.05441265951</v>
-      </c>
+      <c r="B15" s="13"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="s">
-        <v>103</v>
+      <c r="A16" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="B16" s="5">
         <f>B12*(B7^(2/3))</f>
-        <v>0.4642105263</v>
+        <v>0.281449922</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>92</v>
       </c>
       <c r="B17" s="5">
         <f>B16*((B3+B5)/B5)</f>
-        <v>8.82</v>
+        <v>5.347548517</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>127</v>
+      <c r="A18" s="15" t="s">
+        <v>128</v>
       </c>
       <c r="B18" s="5">
         <f>B17/B3</f>
-        <v>0.49</v>
+        <v>0.2970860287</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>128</v>
+      <c r="A19" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B19" s="5">
         <f>B14*(B7^(5/6))</f>
-        <v>0.4255408994</v>
+        <v>0.2276664274</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>129</v>
+      <c r="A20" s="15" t="s">
+        <v>130</v>
       </c>
       <c r="B20" s="5">
         <f>B16-(B19/2)</f>
-        <v>0.2514400766</v>
+        <v>0.1676167082</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>130</v>
+      <c r="A21" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="B21" s="5">
         <f>B16+(B19/2)</f>
-        <v>0.676980976</v>
+        <v>0.3952831357</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="25">
+        <f>B16*1000</f>
+        <v>281.449922</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="25">
+        <f t="shared" ref="B24:B25" si="8">B20*1000</f>
+        <v>167.6167082</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="25">
+        <f t="shared" si="8"/>
+        <v>395.2831357</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="17" t="s">
+    <row r="28">
+      <c r="A28" s="18" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="s">
-        <v>131</v>
+    <row r="29">
+      <c r="A29" s="18" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="D1:K1"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D4:E4"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D4:E4"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D1:K1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="29.38"/>
+    <col customWidth="1" min="2" max="2" width="3.38"/>
+    <col customWidth="1" min="3" max="3" width="14.63"/>
+    <col customWidth="1" min="4" max="4" width="3.38"/>
+    <col customWidth="1" min="5" max="5" width="10.75"/>
+    <col customWidth="1" min="6" max="6" width="3.88"/>
+    <col customWidth="1" min="7" max="7" width="7.13"/>
+    <col customWidth="1" min="9" max="9" width="15.25"/>
+    <col customWidth="1" min="10" max="10" width="3.75"/>
+    <col customWidth="1" min="11" max="11" width="4.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="19">
+        <f>B3-B4</f>
+        <v>9</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2" s="28" t="str">
+        <f t="shared" ref="F2:F5" si="1">IF(D13="", "",TEXT(D13, "#/?") &amp; $D$6)</f>
+        <v/>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K2" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6">
+        <v>18.0</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="19">
+        <f>B7-B8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>1/2+</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="29" t="str">
+        <f>IF(B10-B9 &lt; 0, "", B10-B9)</f>
+        <v/>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>3/2+</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="27">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="29">
+        <f>IF(B10+B9 &lt; 0, "", B10+B9)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K5" s="27">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="19" t="str">
+        <f>SWITCH((-1)^B10, 1, "+", -1, "-", "")</f>
+        <v>+</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K6" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="24">
+        <v>1.0</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K7" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="29" t="str">
+        <f>IF(D4="", "", ABS(B5-D4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="29">
+        <f>ABS(B5-D5)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="29" t="str">
+        <f>IF(D4="", "", ABS(B5+D4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="29">
+        <f>ABS(B5+D5)</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="24">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" s="29" t="str">
+        <f t="array" ref="D13:D15">UNIQUE(D8:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="29">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
